--- a/reports/FOOD mse.xlsx
+++ b/reports/FOOD mse.xlsx
@@ -26321,7 +26321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X151"/>
+  <dimension ref="A1:Y151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -26348,6 +26348,7 @@
     <col width="17" customWidth="1" min="22" max="22"/>
     <col width="17" customWidth="1" min="23" max="23"/>
     <col width="17" customWidth="1" min="24" max="24"/>
+    <col width="17" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26434,9 +26435,12 @@
         <v>45930</v>
       </c>
       <c r="W4" s="4" t="n">
+        <v>46022</v>
+      </c>
+      <c r="X4" s="4" t="n">
         <v>46112</v>
       </c>
-      <c r="X4" s="4" t="n">
+      <c r="Y4" s="4" t="n">
         <v>46203</v>
       </c>
     </row>
@@ -26553,10 +26557,15 @@
       </c>
       <c r="W5" s="5" t="inlineStr">
         <is>
+          <t>2025 Q4</t>
+        </is>
+      </c>
+      <c r="X5" s="5" t="inlineStr">
+        <is>
           <t>2026 Q1</t>
         </is>
       </c>
-      <c r="X5" s="5" t="inlineStr">
+      <c r="Y5" s="5" t="inlineStr">
         <is>
           <t>2026 Q2</t>
         </is>
@@ -26632,9 +26641,12 @@
         <v>9</v>
       </c>
       <c r="W6" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="X6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="X6" s="5" t="n">
+      <c r="Y6" s="5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -26665,8 +26677,11 @@
       <c r="T7" s="4" t="n"/>
       <c r="U7" s="4" t="n"/>
       <c r="V7" s="4" t="n"/>
-      <c r="W7" s="4" t="n"/>
+      <c r="W7" s="4" t="n">
+        <v>46059</v>
+      </c>
       <c r="X7" s="4" t="n"/>
+      <c r="Y7" s="4" t="n"/>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -26781,10 +26796,15 @@
       </c>
       <c r="W8" s="6" t="inlineStr">
         <is>
+          <t>97992290-_135_20254report.pdf</t>
+        </is>
+      </c>
+      <c r="X8" s="6" t="inlineStr">
+        <is>
           <t>SUU 135202601.xls</t>
         </is>
       </c>
-      <c r="X8" s="6" t="inlineStr">
+      <c r="Y8" s="6" t="inlineStr">
         <is>
           <t>SUU 13520262report.xls</t>
         </is>
@@ -26823,6 +26843,7 @@
       <c r="V9" s="6" t="inlineStr"/>
       <c r="W9" s="6" t="inlineStr"/>
       <c r="X9" s="6" t="inlineStr"/>
+      <c r="Y9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -26853,6 +26874,7 @@
       <c r="V10" s="7" t="n"/>
       <c r="W10" s="7" t="n"/>
       <c r="X10" s="7" t="n"/>
+      <c r="Y10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -26883,6 +26905,7 @@
       <c r="V11" s="7" t="n"/>
       <c r="W11" s="7" t="n"/>
       <c r="X11" s="7" t="n"/>
+      <c r="Y11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -26954,9 +26977,12 @@
         <v>1648050.32</v>
       </c>
       <c r="W12" s="8" t="n">
+        <v>5648167.15</v>
+      </c>
+      <c r="X12" s="8" t="n">
         <v>3115969.97</v>
       </c>
-      <c r="X12" s="8" t="n">
+      <c r="Y12" s="8" t="n">
         <v>3372524.12</v>
       </c>
     </row>
@@ -27030,9 +27056,12 @@
         <v>7732879.04</v>
       </c>
       <c r="W13" s="8" t="n">
+        <v>7716966.24</v>
+      </c>
+      <c r="X13" s="8" t="n">
         <v>10037947.9</v>
       </c>
-      <c r="X13" s="8" t="n">
+      <c r="Y13" s="8" t="n">
         <v>10500900.61</v>
       </c>
     </row>
@@ -27103,9 +27132,12 @@
         <v>0</v>
       </c>
       <c r="W14" s="8" t="n">
+        <v>8813.59</v>
+      </c>
+      <c r="X14" s="8" t="n">
         <v>12243.72</v>
       </c>
-      <c r="X14" s="8" t="n">
+      <c r="Y14" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27176,9 +27208,12 @@
         <v>5239049.28</v>
       </c>
       <c r="W15" s="8" t="n">
+        <v>7847123.71</v>
+      </c>
+      <c r="X15" s="8" t="n">
         <v>7196909.34</v>
       </c>
-      <c r="X15" s="8" t="n">
+      <c r="Y15" s="8" t="n">
         <v>7725297.09</v>
       </c>
     </row>
@@ -27251,6 +27286,9 @@
       <c r="X16" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -27319,9 +27357,12 @@
         <v>40402383.74</v>
       </c>
       <c r="W17" s="8" t="n">
+        <v>45970636.81</v>
+      </c>
+      <c r="X17" s="8" t="n">
         <v>36296516.44</v>
       </c>
-      <c r="X17" s="8" t="n">
+      <c r="Y17" s="8" t="n">
         <v>37786644.78</v>
       </c>
     </row>
@@ -27395,9 +27436,12 @@
         <v>12048186.97</v>
       </c>
       <c r="W18" s="8" t="n">
+        <v>15508544.93</v>
+      </c>
+      <c r="X18" s="8" t="n">
         <v>15733110.09</v>
       </c>
-      <c r="X18" s="8" t="n">
+      <c r="Y18" s="8" t="n">
         <v>19727290.74</v>
       </c>
     </row>
@@ -27470,6 +27514,9 @@
       <c r="X19" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -27535,9 +27582,12 @@
         <v>12600</v>
       </c>
       <c r="W20" s="8" t="n">
+        <v>4200</v>
+      </c>
+      <c r="X20" s="8" t="n">
         <v>4900</v>
       </c>
-      <c r="X20" s="8" t="n">
+      <c r="Y20" s="8" t="n">
         <v>1400</v>
       </c>
     </row>
@@ -27568,10 +27618,10 @@
       <c r="V21" s="8" t="n">
         <v>242235.34</v>
       </c>
-      <c r="W21" s="8" t="n">
+      <c r="X21" s="8" t="n">
         <v>236116.6</v>
       </c>
-      <c r="X21" s="8" t="n">
+      <c r="Y21" s="8" t="n">
         <v>221356.4</v>
       </c>
     </row>
@@ -27645,9 +27695,12 @@
         <v>67325384.7</v>
       </c>
       <c r="W22" s="10" t="n">
+        <v>82933659.31999999</v>
+      </c>
+      <c r="X22" s="10" t="n">
         <v>72633714.05</v>
       </c>
-      <c r="X22" s="10" t="n">
+      <c r="Y22" s="10" t="n">
         <v>79335413.73999999</v>
       </c>
     </row>
@@ -27680,6 +27733,7 @@
       <c r="V23" s="7" t="n"/>
       <c r="W23" s="7" t="n"/>
       <c r="X23" s="7" t="n"/>
+      <c r="Y23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -27751,9 +27805,12 @@
         <v>80796662.98</v>
       </c>
       <c r="W24" s="8" t="n">
+        <v>82396769.15000001</v>
+      </c>
+      <c r="X24" s="8" t="n">
         <v>81120213.04000001</v>
       </c>
-      <c r="X24" s="8" t="n">
+      <c r="Y24" s="8" t="n">
         <v>81758953.22</v>
       </c>
     </row>
@@ -27827,9 +27884,12 @@
         <v>834477.99</v>
       </c>
       <c r="W25" s="8" t="n">
+        <v>1189603.41</v>
+      </c>
+      <c r="X25" s="8" t="n">
         <v>1175725.63</v>
       </c>
-      <c r="X25" s="8" t="n">
+      <c r="Y25" s="8" t="n">
         <v>1131787.46</v>
       </c>
     </row>
@@ -27900,9 +27960,12 @@
         <v>976177.04</v>
       </c>
       <c r="W26" s="8" t="n">
+        <v>958151.62</v>
+      </c>
+      <c r="X26" s="8" t="n">
         <v>912465.12</v>
       </c>
-      <c r="X26" s="8" t="n">
+      <c r="Y26" s="8" t="n">
         <v>833250.9300000001</v>
       </c>
     </row>
@@ -27978,6 +28041,9 @@
       <c r="X27" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="Y27" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -28048,6 +28114,9 @@
       <c r="X28" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="Y28" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -28118,6 +28187,9 @@
       <c r="X29" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="Y29" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -28188,6 +28260,9 @@
       <c r="X30" s="8" t="n">
         <v>489680.03</v>
       </c>
+      <c r="Y30" s="8" t="n">
+        <v>489680.03</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -28215,6 +28290,9 @@
         <v>11959904.38</v>
       </c>
       <c r="X32" s="8" t="n">
+        <v>11959904.38</v>
+      </c>
+      <c r="Y32" s="8" t="n">
         <v>13443279.61</v>
       </c>
     </row>
@@ -28282,9 +28360,12 @@
         <v>20564852.16</v>
       </c>
       <c r="W33" s="8" t="n">
+        <v>21734447.95</v>
+      </c>
+      <c r="X33" s="8" t="n">
         <v>29290535.51</v>
       </c>
-      <c r="X33" s="8" t="n">
+      <c r="Y33" s="8" t="n">
         <v>30129035.78</v>
       </c>
     </row>
@@ -28365,9 +28446,12 @@
         <v>109515059.52</v>
       </c>
       <c r="W35" s="10" t="n">
+        <v>118728556.54</v>
+      </c>
+      <c r="X35" s="10" t="n">
         <v>124948523.72</v>
       </c>
-      <c r="X35" s="10" t="n">
+      <c r="Y35" s="10" t="n">
         <v>127785987.03</v>
       </c>
     </row>
@@ -28441,9 +28525,12 @@
         <v>176840444.21</v>
       </c>
       <c r="W36" s="10" t="n">
+        <v>201662215.86</v>
+      </c>
+      <c r="X36" s="10" t="n">
         <v>197582237.77</v>
       </c>
-      <c r="X36" s="10" t="n">
+      <c r="Y36" s="10" t="n">
         <v>207121400.77</v>
       </c>
     </row>
@@ -28476,6 +28563,7 @@
       <c r="V37" s="7" t="n"/>
       <c r="W37" s="7" t="n"/>
       <c r="X37" s="7" t="n"/>
+      <c r="Y37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -28547,9 +28635,12 @@
         <v>8723012.609999999</v>
       </c>
       <c r="W38" s="8" t="n">
+        <v>15896555.43</v>
+      </c>
+      <c r="X38" s="8" t="n">
         <v>8572163.859999999</v>
       </c>
-      <c r="X38" s="8" t="n">
+      <c r="Y38" s="8" t="n">
         <v>10090844.7</v>
       </c>
     </row>
@@ -28623,9 +28714,12 @@
         <v>1322635.52</v>
       </c>
       <c r="W39" s="8" t="n">
+        <v>1236335.57</v>
+      </c>
+      <c r="X39" s="8" t="n">
         <v>1302798.21</v>
       </c>
-      <c r="X39" s="8" t="n">
+      <c r="Y39" s="8" t="n">
         <v>1459095.32</v>
       </c>
     </row>
@@ -28699,9 +28793,12 @@
         <v>4120693.46</v>
       </c>
       <c r="W40" s="8" t="n">
+        <v>1527422.96</v>
+      </c>
+      <c r="X40" s="8" t="n">
         <v>1760902.87</v>
       </c>
-      <c r="X40" s="8" t="n">
+      <c r="Y40" s="8" t="n">
         <v>2772151.8</v>
       </c>
     </row>
@@ -28775,9 +28872,12 @@
         <v>677085.66</v>
       </c>
       <c r="W41" s="8" t="n">
+        <v>649619.9300000001</v>
+      </c>
+      <c r="X41" s="8" t="n">
         <v>660581.1800000001</v>
       </c>
-      <c r="X41" s="8" t="n">
+      <c r="Y41" s="8" t="n">
         <v>734230.47</v>
       </c>
     </row>
@@ -28851,9 +28951,12 @@
         <v>10664346.97</v>
       </c>
       <c r="W42" s="8" t="n">
+        <v>29234821.71</v>
+      </c>
+      <c r="X42" s="8" t="n">
         <v>26372338.72</v>
       </c>
-      <c r="X42" s="8" t="n">
+      <c r="Y42" s="8" t="n">
         <v>20614005.39</v>
       </c>
     </row>
@@ -28927,9 +29030,12 @@
         <v>78808.74000000001</v>
       </c>
       <c r="W43" s="8" t="n">
+        <v>300169.62</v>
+      </c>
+      <c r="X43" s="8" t="n">
         <v>333359.55</v>
       </c>
-      <c r="X43" s="8" t="n">
+      <c r="Y43" s="8" t="n">
         <v>1223402.49</v>
       </c>
     </row>
@@ -29000,9 +29106,12 @@
         <v>2065697.72</v>
       </c>
       <c r="W44" s="8" t="n">
+        <v>6904.78</v>
+      </c>
+      <c r="X44" s="8" t="n">
         <v>1753447.46</v>
       </c>
-      <c r="X44" s="8" t="n">
+      <c r="Y44" s="8" t="n">
         <v>1649515.76</v>
       </c>
     </row>
@@ -29070,9 +29179,12 @@
         <v>52028.9</v>
       </c>
       <c r="W45" s="8" t="n">
+        <v>70376.61</v>
+      </c>
+      <c r="X45" s="8" t="n">
         <v>62052.53</v>
       </c>
-      <c r="X45" s="8" t="n">
+      <c r="Y45" s="8" t="n">
         <v>83225.17999999999</v>
       </c>
     </row>
@@ -29145,6 +29257,9 @@
       <c r="X46" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="Y46" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -29213,9 +29328,12 @@
         <v>38238086.67</v>
       </c>
       <c r="W47" s="8" t="n">
+        <v>36588222.32</v>
+      </c>
+      <c r="X47" s="8" t="n">
         <v>38897410.9</v>
       </c>
-      <c r="X47" s="8" t="n">
+      <c r="Y47" s="8" t="n">
         <v>38421107.05</v>
       </c>
     </row>
@@ -29288,6 +29406,9 @@
       <c r="X48" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="Y48" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
@@ -29359,9 +29480,12 @@
         <v>65942396.24</v>
       </c>
       <c r="W49" s="10" t="n">
+        <v>85510428.92</v>
+      </c>
+      <c r="X49" s="10" t="n">
         <v>79715055.29000001</v>
       </c>
-      <c r="X49" s="10" t="n">
+      <c r="Y49" s="10" t="n">
         <v>77047578.16</v>
       </c>
     </row>
@@ -29394,6 +29518,7 @@
       <c r="V50" s="7" t="n"/>
       <c r="W50" s="7" t="n"/>
       <c r="X50" s="7" t="n"/>
+      <c r="Y50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -29465,9 +29590,12 @@
         <v>33712623.23</v>
       </c>
       <c r="W51" s="8" t="n">
+        <v>36586771.18</v>
+      </c>
+      <c r="X51" s="8" t="n">
         <v>37550167.93</v>
       </c>
-      <c r="X51" s="8" t="n">
+      <c r="Y51" s="8" t="n">
         <v>44458694.08</v>
       </c>
     </row>
@@ -29540,6 +29668,9 @@
       <c r="X52" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="Y52" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -29605,9 +29736,12 @@
         <v>346785.22</v>
       </c>
       <c r="W53" s="8" t="n">
+        <v>589184.92</v>
+      </c>
+      <c r="X53" s="8" t="n">
         <v>630597.34</v>
       </c>
-      <c r="X53" s="8" t="n">
+      <c r="Y53" s="8" t="n">
         <v>440552.01</v>
       </c>
     </row>
@@ -29626,10 +29760,10 @@
       <c r="V54" s="8" t="n">
         <v>8505829.92</v>
       </c>
-      <c r="W54" s="8" t="n">
+      <c r="X54" s="8" t="n">
         <v>6843689.54</v>
       </c>
-      <c r="X54" s="8" t="n">
+      <c r="Y54" s="8" t="n">
         <v>6015603.04</v>
       </c>
     </row>
@@ -29697,9 +29831,12 @@
         <v>1131890.82</v>
       </c>
       <c r="W55" s="8" t="n">
+        <v>1042465.3</v>
+      </c>
+      <c r="X55" s="8" t="n">
         <v>1246972.56</v>
       </c>
-      <c r="X55" s="8" t="n">
+      <c r="Y55" s="8" t="n">
         <v>1309908.98</v>
       </c>
     </row>
@@ -29773,9 +29910,12 @@
         <v>43697129.2</v>
       </c>
       <c r="W56" s="10" t="n">
+        <v>45890197.44</v>
+      </c>
+      <c r="X56" s="10" t="n">
         <v>46271427.36</v>
       </c>
-      <c r="X56" s="10" t="n">
+      <c r="Y56" s="10" t="n">
         <v>52224758.11</v>
       </c>
     </row>
@@ -29849,9 +29989,12 @@
         <v>109639525.44</v>
       </c>
       <c r="W57" s="10" t="n">
+        <v>131400626.36</v>
+      </c>
+      <c r="X57" s="10" t="n">
         <v>125986482.65</v>
       </c>
-      <c r="X57" s="10" t="n">
+      <c r="Y57" s="10" t="n">
         <v>129272336.27</v>
       </c>
     </row>
@@ -29884,6 +30027,7 @@
       <c r="V58" s="7" t="n"/>
       <c r="W58" s="7" t="n"/>
       <c r="X58" s="7" t="n"/>
+      <c r="Y58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -29957,6 +30101,9 @@
       <c r="X59" s="8" t="n">
         <v>34400</v>
       </c>
+      <c r="Y59" s="8" t="n">
+        <v>34400</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -30033,6 +30180,9 @@
       <c r="X60" s="8" t="n">
         <v>-86.78</v>
       </c>
+      <c r="Y60" s="8" t="n">
+        <v>-86.78</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -30103,6 +30253,9 @@
       <c r="X61" s="8" t="n">
         <v>60101.31</v>
       </c>
+      <c r="Y61" s="8" t="n">
+        <v>60101.31</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -30179,6 +30332,9 @@
       <c r="X62" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="Y62" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -30249,6 +30405,9 @@
       <c r="X63" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="Y63" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -30319,6 +30478,9 @@
       <c r="X64" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="Y64" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -30387,9 +30549,12 @@
         <v>67106504.24</v>
       </c>
       <c r="W65" s="8" t="n">
+        <v>70167174.97</v>
+      </c>
+      <c r="X65" s="8" t="n">
         <v>71501340.59</v>
       </c>
-      <c r="X65" s="8" t="n">
+      <c r="Y65" s="8" t="n">
         <v>77754649.98</v>
       </c>
     </row>
@@ -30507,9 +30672,12 @@
         <v>67200918.77</v>
       </c>
       <c r="W68" s="10" t="n">
+        <v>70261589.5</v>
+      </c>
+      <c r="X68" s="10" t="n">
         <v>71595755.12</v>
       </c>
-      <c r="X68" s="10" t="n">
+      <c r="Y68" s="10" t="n">
         <v>77849064.5</v>
       </c>
     </row>
@@ -30583,9 +30751,12 @@
         <v>176840444.21</v>
       </c>
       <c r="W69" s="10" t="n">
+        <v>201662215.86</v>
+      </c>
+      <c r="X69" s="10" t="n">
         <v>197582237.77</v>
       </c>
-      <c r="X69" s="10" t="n">
+      <c r="Y69" s="10" t="n">
         <v>207121400.77</v>
       </c>
     </row>
@@ -30618,6 +30789,7 @@
       <c r="V70" s="7" t="n"/>
       <c r="W70" s="7" t="n"/>
       <c r="X70" s="7" t="n"/>
+      <c r="Y70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -30689,9 +30861,12 @@
         <v>164671472.35</v>
       </c>
       <c r="W71" s="8" t="n">
+        <v>221437853.42</v>
+      </c>
+      <c r="X71" s="8" t="n">
         <v>61593641.97</v>
       </c>
-      <c r="X71" s="8" t="n">
+      <c r="Y71" s="8" t="n">
         <v>131119952.09</v>
       </c>
     </row>
@@ -30765,9 +30940,12 @@
         <v>116700406.23</v>
       </c>
       <c r="W72" s="8" t="n">
+        <v>155728115.13</v>
+      </c>
+      <c r="X72" s="8" t="n">
         <v>45122482.86</v>
       </c>
-      <c r="X72" s="8" t="n">
+      <c r="Y72" s="8" t="n">
         <v>92309385.73999999</v>
       </c>
     </row>
@@ -30841,9 +31019,12 @@
         <v>47971066.12</v>
       </c>
       <c r="W73" s="10" t="n">
+        <v>65709738.29</v>
+      </c>
+      <c r="X73" s="10" t="n">
         <v>16471159.12</v>
       </c>
-      <c r="X73" s="10" t="n">
+      <c r="Y73" s="10" t="n">
         <v>38810566.35</v>
       </c>
     </row>
@@ -30914,9 +31095,12 @@
         <v>45490.91</v>
       </c>
       <c r="W74" s="8" t="n">
+        <v>60654.55</v>
+      </c>
+      <c r="X74" s="8" t="n">
         <v>15163.64</v>
       </c>
-      <c r="X74" s="8" t="n">
+      <c r="Y74" s="8" t="n">
         <v>30327.27</v>
       </c>
     </row>
@@ -30987,9 +31171,12 @@
         <v>7417.64</v>
       </c>
       <c r="W75" s="8" t="n">
+        <v>15078.57</v>
+      </c>
+      <c r="X75" s="8" t="n">
         <v>10299.59</v>
       </c>
-      <c r="X75" s="8" t="n">
+      <c r="Y75" s="8" t="n">
         <v>20309.52</v>
       </c>
     </row>
@@ -31062,6 +31249,9 @@
       <c r="X76" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="Y76" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -31132,6 +31322,9 @@
       <c r="X77" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="Y77" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -31197,9 +31390,12 @@
         <v>2686921.88</v>
       </c>
       <c r="W78" s="8" t="n">
+        <v>3579407.36</v>
+      </c>
+      <c r="X78" s="8" t="n">
         <v>872339.4</v>
       </c>
-      <c r="X78" s="8" t="n">
+      <c r="Y78" s="8" t="n">
         <v>1792171.15</v>
       </c>
     </row>
@@ -31270,9 +31466,12 @@
         <v>9937424.49</v>
       </c>
       <c r="W79" s="8" t="n">
+        <v>14183178.77</v>
+      </c>
+      <c r="X79" s="8" t="n">
         <v>3495911.95</v>
       </c>
-      <c r="X79" s="8" t="n">
+      <c r="Y79" s="8" t="n">
         <v>7416245.35</v>
       </c>
     </row>
@@ -31346,9 +31545,12 @@
         <v>22305066.03</v>
       </c>
       <c r="W80" s="8" t="n">
+        <v>31187701.08</v>
+      </c>
+      <c r="X80" s="8" t="n">
         <v>7540530.82</v>
       </c>
-      <c r="X80" s="8" t="n">
+      <c r="Y80" s="8" t="n">
         <v>15660861.38</v>
       </c>
     </row>
@@ -31419,9 +31621,12 @@
         <v>5281170.93</v>
       </c>
       <c r="W81" s="8" t="n">
+        <v>7469238.88</v>
+      </c>
+      <c r="X81" s="8" t="n">
         <v>2220967.54</v>
       </c>
-      <c r="X81" s="8" t="n">
+      <c r="Y81" s="8" t="n">
         <v>5341312.05</v>
       </c>
     </row>
@@ -31492,9 +31697,12 @@
         <v>64111.28</v>
       </c>
       <c r="W82" s="8" t="n">
+        <v>110861.48</v>
+      </c>
+      <c r="X82" s="8" t="n">
         <v>40729.1</v>
       </c>
-      <c r="X82" s="8" t="n">
+      <c r="Y82" s="8" t="n">
         <v>60281.21</v>
       </c>
     </row>
@@ -31565,9 +31773,12 @@
         <v>-234012.71</v>
       </c>
       <c r="W83" s="8" t="n">
+        <v>-448564.38</v>
+      </c>
+      <c r="X83" s="8" t="n">
         <v>-85484.34</v>
       </c>
-      <c r="X83" s="8" t="n">
+      <c r="Y83" s="8" t="n">
         <v>-155354.69</v>
       </c>
     </row>
@@ -31635,9 +31846,12 @@
         <v>-1374424.07</v>
       </c>
       <c r="W84" s="8" t="n">
+        <v>-1614930.1</v>
+      </c>
+      <c r="X84" s="8" t="n">
         <v>-442836.45</v>
       </c>
-      <c r="X84" s="8" t="n">
+      <c r="Y84" s="8" t="n">
         <v>-732551.13</v>
       </c>
     </row>
@@ -31710,6 +31924,9 @@
       <c r="X85" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="Y85" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -31780,6 +31997,9 @@
       <c r="X86" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="Y86" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -31811,10 +32031,10 @@
       <c r="V87" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="W87" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="X87" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -31848,10 +32068,10 @@
       <c r="V88" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="W88" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="X88" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -31927,6 +32147,9 @@
       <c r="X89" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="Y89" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
@@ -31998,9 +32221,12 @@
         <v>11514687.02</v>
       </c>
       <c r="W90" s="10" t="n">
+        <v>14350404.06</v>
+      </c>
+      <c r="X90" s="10" t="n">
         <v>3542501.54</v>
       </c>
-      <c r="X90" s="10" t="n">
+      <c r="Y90" s="10" t="n">
         <v>11286768.47</v>
       </c>
     </row>
@@ -32074,9 +32300,12 @@
         <v>1918005.01</v>
       </c>
       <c r="W91" s="8" t="n">
+        <v>1667935.94</v>
+      </c>
+      <c r="X91" s="8" t="n">
         <v>357037.32</v>
       </c>
-      <c r="X91" s="8" t="n">
+      <c r="Y91" s="8" t="n">
         <v>1845662.23</v>
       </c>
     </row>
@@ -32150,9 +32379,12 @@
         <v>9596682.01</v>
       </c>
       <c r="W92" s="10" t="n">
+        <v>12682468.13</v>
+      </c>
+      <c r="X92" s="10" t="n">
         <v>3185464.22</v>
       </c>
-      <c r="X92" s="10" t="n">
+      <c r="Y92" s="10" t="n">
         <v>9441106.24</v>
       </c>
     </row>
@@ -32225,6 +32457,9 @@
       <c r="X93" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="Y93" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
@@ -32296,9 +32531,12 @@
         <v>9596682.01</v>
       </c>
       <c r="W94" s="10" t="n">
+        <v>12682468.13</v>
+      </c>
+      <c r="X94" s="10" t="n">
         <v>3185464.22</v>
       </c>
-      <c r="X94" s="10" t="n">
+      <c r="Y94" s="10" t="n">
         <v>9441106.24</v>
       </c>
     </row>
@@ -32371,6 +32609,9 @@
       <c r="X95" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="Y95" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -32441,6 +32682,9 @@
       <c r="X96" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="Y96" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -32509,6 +32753,9 @@
         <v>0</v>
       </c>
       <c r="X97" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -32562,10 +32809,11 @@
       <c r="V99" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="W99" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="W99" s="9" t="n"/>
       <c r="X99" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -32639,9 +32887,12 @@
         <v>9596682.01</v>
       </c>
       <c r="W100" s="10" t="n">
+        <v>12682468.13</v>
+      </c>
+      <c r="X100" s="10" t="n">
         <v>3185464.22</v>
       </c>
-      <c r="X100" s="10" t="n">
+      <c r="Y100" s="10" t="n">
         <v>9441106.24</v>
       </c>
     </row>
@@ -32741,6 +32992,10 @@
       </c>
       <c r="X102" s="12">
         <f>IF(AND(ISNUMBER(X36),ISNUMBER(X57),ISNUMBER(X68)),ROUND(X36-X57-X68,0),"")</f>
+        <v/>
+      </c>
+      <c r="Y102" s="12">
+        <f>IF(AND(ISNUMBER(Y36),ISNUMBER(Y57),ISNUMBER(Y68)),ROUND(Y36-Y57-Y68,0),"")</f>
         <v/>
       </c>
     </row>
@@ -32773,6 +33028,7 @@
       <c r="V104" s="7" t="n"/>
       <c r="W104" s="7" t="n"/>
       <c r="X104" s="7" t="n"/>
+      <c r="Y104" s="7" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="13" t="inlineStr">
@@ -32886,6 +33142,10 @@
         <f>IF(ISNUMBER(X$6),IFERROR(12/X$6,""),"")</f>
         <v/>
       </c>
+      <c r="Y107" s="15">
+        <f>IF(ISNUMBER(Y$6),IFERROR(12/Y$6,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -32894,95 +33154,99 @@
         </is>
       </c>
       <c r="B108" s="8">
-        <f>IF(ISNUMBER(B36),IFERROR(IF(INDEX($B36:$X36,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$X$4,0))="",B36,(B36+INDEX($B36:$X36,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$X$4,0)))/2),B36),"")</f>
+        <f>IF(ISNUMBER(B36),IFERROR(IF(INDEX($B36:$Y36,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$Y$4,0))="",B36,(B36+INDEX($B36:$Y36,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$Y$4,0)))/2),B36),"")</f>
         <v/>
       </c>
       <c r="C108" s="8">
-        <f>IF(ISNUMBER(C36),IFERROR(IF(INDEX($B36:$X36,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$X$4,0))="",C36,(C36+INDEX($B36:$X36,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$X$4,0)))/2),C36),"")</f>
+        <f>IF(ISNUMBER(C36),IFERROR(IF(INDEX($B36:$Y36,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$Y$4,0))="",C36,(C36+INDEX($B36:$Y36,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$Y$4,0)))/2),C36),"")</f>
         <v/>
       </c>
       <c r="D108" s="8">
-        <f>IF(ISNUMBER(D36),IFERROR(IF(INDEX($B36:$X36,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$X$4,0))="",D36,(D36+INDEX($B36:$X36,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$X$4,0)))/2),D36),"")</f>
+        <f>IF(ISNUMBER(D36),IFERROR(IF(INDEX($B36:$Y36,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$Y$4,0))="",D36,(D36+INDEX($B36:$Y36,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$Y$4,0)))/2),D36),"")</f>
         <v/>
       </c>
       <c r="E108" s="8">
-        <f>IF(ISNUMBER(E36),IFERROR(IF(INDEX($B36:$X36,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$X$4,0))="",E36,(E36+INDEX($B36:$X36,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$X$4,0)))/2),E36),"")</f>
+        <f>IF(ISNUMBER(E36),IFERROR(IF(INDEX($B36:$Y36,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$Y$4,0))="",E36,(E36+INDEX($B36:$Y36,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$Y$4,0)))/2),E36),"")</f>
         <v/>
       </c>
       <c r="F108" s="8">
-        <f>IF(ISNUMBER(F36),IFERROR(IF(INDEX($B36:$X36,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$X$4,0))="",F36,(F36+INDEX($B36:$X36,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$X$4,0)))/2),F36),"")</f>
+        <f>IF(ISNUMBER(F36),IFERROR(IF(INDEX($B36:$Y36,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$Y$4,0))="",F36,(F36+INDEX($B36:$Y36,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$Y$4,0)))/2),F36),"")</f>
         <v/>
       </c>
       <c r="G108" s="8">
-        <f>IF(ISNUMBER(G36),IFERROR(IF(INDEX($B36:$X36,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$X$4,0))="",G36,(G36+INDEX($B36:$X36,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$X$4,0)))/2),G36),"")</f>
+        <f>IF(ISNUMBER(G36),IFERROR(IF(INDEX($B36:$Y36,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$Y$4,0))="",G36,(G36+INDEX($B36:$Y36,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$Y$4,0)))/2),G36),"")</f>
         <v/>
       </c>
       <c r="H108" s="8">
-        <f>IF(ISNUMBER(H36),IFERROR(IF(INDEX($B36:$X36,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$X$4,0))="",H36,(H36+INDEX($B36:$X36,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$X$4,0)))/2),H36),"")</f>
+        <f>IF(ISNUMBER(H36),IFERROR(IF(INDEX($B36:$Y36,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$Y$4,0))="",H36,(H36+INDEX($B36:$Y36,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$Y$4,0)))/2),H36),"")</f>
         <v/>
       </c>
       <c r="I108" s="8">
-        <f>IF(ISNUMBER(I36),IFERROR(IF(INDEX($B36:$X36,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$X$4,0))="",I36,(I36+INDEX($B36:$X36,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$X$4,0)))/2),I36),"")</f>
+        <f>IF(ISNUMBER(I36),IFERROR(IF(INDEX($B36:$Y36,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$Y$4,0))="",I36,(I36+INDEX($B36:$Y36,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$Y$4,0)))/2),I36),"")</f>
         <v/>
       </c>
       <c r="J108" s="8">
-        <f>IF(ISNUMBER(J36),IFERROR(IF(INDEX($B36:$X36,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$X$4,0))="",J36,(J36+INDEX($B36:$X36,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$X$4,0)))/2),J36),"")</f>
+        <f>IF(ISNUMBER(J36),IFERROR(IF(INDEX($B36:$Y36,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$Y$4,0))="",J36,(J36+INDEX($B36:$Y36,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$Y$4,0)))/2),J36),"")</f>
         <v/>
       </c>
       <c r="K108" s="8">
-        <f>IF(ISNUMBER(K36),IFERROR(IF(INDEX($B36:$X36,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$X$4,0))="",K36,(K36+INDEX($B36:$X36,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$X$4,0)))/2),K36),"")</f>
+        <f>IF(ISNUMBER(K36),IFERROR(IF(INDEX($B36:$Y36,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$Y$4,0))="",K36,(K36+INDEX($B36:$Y36,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$Y$4,0)))/2),K36),"")</f>
         <v/>
       </c>
       <c r="L108" s="8">
-        <f>IF(ISNUMBER(L36),IFERROR(IF(INDEX($B36:$X36,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$X$4,0))="",L36,(L36+INDEX($B36:$X36,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$X$4,0)))/2),L36),"")</f>
+        <f>IF(ISNUMBER(L36),IFERROR(IF(INDEX($B36:$Y36,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$Y$4,0))="",L36,(L36+INDEX($B36:$Y36,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$Y$4,0)))/2),L36),"")</f>
         <v/>
       </c>
       <c r="M108" s="8">
-        <f>IF(ISNUMBER(M36),IFERROR(IF(INDEX($B36:$X36,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$X$4,0))="",M36,(M36+INDEX($B36:$X36,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$X$4,0)))/2),M36),"")</f>
+        <f>IF(ISNUMBER(M36),IFERROR(IF(INDEX($B36:$Y36,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$Y$4,0))="",M36,(M36+INDEX($B36:$Y36,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$Y$4,0)))/2),M36),"")</f>
         <v/>
       </c>
       <c r="N108" s="8">
-        <f>IF(ISNUMBER(N36),IFERROR(IF(INDEX($B36:$X36,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$X$4,0))="",N36,(N36+INDEX($B36:$X36,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$X$4,0)))/2),N36),"")</f>
+        <f>IF(ISNUMBER(N36),IFERROR(IF(INDEX($B36:$Y36,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$Y$4,0))="",N36,(N36+INDEX($B36:$Y36,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$Y$4,0)))/2),N36),"")</f>
         <v/>
       </c>
       <c r="O108" s="8">
-        <f>IF(ISNUMBER(O36),IFERROR(IF(INDEX($B36:$X36,MATCH(DATE(YEAR(O$4)-1,12,31),$B$4:$X$4,0))="",O36,(O36+INDEX($B36:$X36,MATCH(DATE(YEAR(O$4)-1,12,31),$B$4:$X$4,0)))/2),O36),"")</f>
+        <f>IF(ISNUMBER(O36),IFERROR(IF(INDEX($B36:$Y36,MATCH(DATE(YEAR(O$4)-1,12,31),$B$4:$Y$4,0))="",O36,(O36+INDEX($B36:$Y36,MATCH(DATE(YEAR(O$4)-1,12,31),$B$4:$Y$4,0)))/2),O36),"")</f>
         <v/>
       </c>
       <c r="P108" s="8">
-        <f>IF(ISNUMBER(P36),IFERROR(IF(INDEX($B36:$X36,MATCH(DATE(YEAR(P$4)-1,12,31),$B$4:$X$4,0))="",P36,(P36+INDEX($B36:$X36,MATCH(DATE(YEAR(P$4)-1,12,31),$B$4:$X$4,0)))/2),P36),"")</f>
+        <f>IF(ISNUMBER(P36),IFERROR(IF(INDEX($B36:$Y36,MATCH(DATE(YEAR(P$4)-1,12,31),$B$4:$Y$4,0))="",P36,(P36+INDEX($B36:$Y36,MATCH(DATE(YEAR(P$4)-1,12,31),$B$4:$Y$4,0)))/2),P36),"")</f>
         <v/>
       </c>
       <c r="Q108" s="8">
-        <f>IF(ISNUMBER(Q36),IFERROR(IF(INDEX($B36:$X36,MATCH(DATE(YEAR(Q$4)-1,12,31),$B$4:$X$4,0))="",Q36,(Q36+INDEX($B36:$X36,MATCH(DATE(YEAR(Q$4)-1,12,31),$B$4:$X$4,0)))/2),Q36),"")</f>
+        <f>IF(ISNUMBER(Q36),IFERROR(IF(INDEX($B36:$Y36,MATCH(DATE(YEAR(Q$4)-1,12,31),$B$4:$Y$4,0))="",Q36,(Q36+INDEX($B36:$Y36,MATCH(DATE(YEAR(Q$4)-1,12,31),$B$4:$Y$4,0)))/2),Q36),"")</f>
         <v/>
       </c>
       <c r="R108" s="8">
-        <f>IF(ISNUMBER(R36),IFERROR(IF(INDEX($B36:$X36,MATCH(DATE(YEAR(R$4)-1,12,31),$B$4:$X$4,0))="",R36,(R36+INDEX($B36:$X36,MATCH(DATE(YEAR(R$4)-1,12,31),$B$4:$X$4,0)))/2),R36),"")</f>
+        <f>IF(ISNUMBER(R36),IFERROR(IF(INDEX($B36:$Y36,MATCH(DATE(YEAR(R$4)-1,12,31),$B$4:$Y$4,0))="",R36,(R36+INDEX($B36:$Y36,MATCH(DATE(YEAR(R$4)-1,12,31),$B$4:$Y$4,0)))/2),R36),"")</f>
         <v/>
       </c>
       <c r="S108" s="8">
-        <f>IF(ISNUMBER(S36),IFERROR(IF(INDEX($B36:$X36,MATCH(DATE(YEAR(S$4)-1,12,31),$B$4:$X$4,0))="",S36,(S36+INDEX($B36:$X36,MATCH(DATE(YEAR(S$4)-1,12,31),$B$4:$X$4,0)))/2),S36),"")</f>
+        <f>IF(ISNUMBER(S36),IFERROR(IF(INDEX($B36:$Y36,MATCH(DATE(YEAR(S$4)-1,12,31),$B$4:$Y$4,0))="",S36,(S36+INDEX($B36:$Y36,MATCH(DATE(YEAR(S$4)-1,12,31),$B$4:$Y$4,0)))/2),S36),"")</f>
         <v/>
       </c>
       <c r="T108" s="8">
-        <f>IF(ISNUMBER(T36),IFERROR(IF(INDEX($B36:$X36,MATCH(DATE(YEAR(T$4)-1,12,31),$B$4:$X$4,0))="",T36,(T36+INDEX($B36:$X36,MATCH(DATE(YEAR(T$4)-1,12,31),$B$4:$X$4,0)))/2),T36),"")</f>
+        <f>IF(ISNUMBER(T36),IFERROR(IF(INDEX($B36:$Y36,MATCH(DATE(YEAR(T$4)-1,12,31),$B$4:$Y$4,0))="",T36,(T36+INDEX($B36:$Y36,MATCH(DATE(YEAR(T$4)-1,12,31),$B$4:$Y$4,0)))/2),T36),"")</f>
         <v/>
       </c>
       <c r="U108" s="8">
-        <f>IF(ISNUMBER(U36),IFERROR(IF(INDEX($B36:$X36,MATCH(DATE(YEAR(U$4)-1,12,31),$B$4:$X$4,0))="",U36,(U36+INDEX($B36:$X36,MATCH(DATE(YEAR(U$4)-1,12,31),$B$4:$X$4,0)))/2),U36),"")</f>
+        <f>IF(ISNUMBER(U36),IFERROR(IF(INDEX($B36:$Y36,MATCH(DATE(YEAR(U$4)-1,12,31),$B$4:$Y$4,0))="",U36,(U36+INDEX($B36:$Y36,MATCH(DATE(YEAR(U$4)-1,12,31),$B$4:$Y$4,0)))/2),U36),"")</f>
         <v/>
       </c>
       <c r="V108" s="8">
-        <f>IF(ISNUMBER(V36),IFERROR(IF(INDEX($B36:$X36,MATCH(DATE(YEAR(V$4)-1,12,31),$B$4:$X$4,0))="",V36,(V36+INDEX($B36:$X36,MATCH(DATE(YEAR(V$4)-1,12,31),$B$4:$X$4,0)))/2),V36),"")</f>
+        <f>IF(ISNUMBER(V36),IFERROR(IF(INDEX($B36:$Y36,MATCH(DATE(YEAR(V$4)-1,12,31),$B$4:$Y$4,0))="",V36,(V36+INDEX($B36:$Y36,MATCH(DATE(YEAR(V$4)-1,12,31),$B$4:$Y$4,0)))/2),V36),"")</f>
         <v/>
       </c>
       <c r="W108" s="8">
-        <f>IF(ISNUMBER(W36),IFERROR(IF(INDEX($B36:$X36,MATCH(DATE(YEAR(W$4)-1,12,31),$B$4:$X$4,0))="",W36,(W36+INDEX($B36:$X36,MATCH(DATE(YEAR(W$4)-1,12,31),$B$4:$X$4,0)))/2),W36),"")</f>
+        <f>IF(ISNUMBER(W36),IFERROR(IF(INDEX($B36:$Y36,MATCH(DATE(YEAR(W$4)-1,12,31),$B$4:$Y$4,0))="",W36,(W36+INDEX($B36:$Y36,MATCH(DATE(YEAR(W$4)-1,12,31),$B$4:$Y$4,0)))/2),W36),"")</f>
         <v/>
       </c>
       <c r="X108" s="8">
-        <f>IF(ISNUMBER(X36),IFERROR(IF(INDEX($B36:$X36,MATCH(DATE(YEAR(X$4)-1,12,31),$B$4:$X$4,0))="",X36,(X36+INDEX($B36:$X36,MATCH(DATE(YEAR(X$4)-1,12,31),$B$4:$X$4,0)))/2),X36),"")</f>
+        <f>IF(ISNUMBER(X36),IFERROR(IF(INDEX($B36:$Y36,MATCH(DATE(YEAR(X$4)-1,12,31),$B$4:$Y$4,0))="",X36,(X36+INDEX($B36:$Y36,MATCH(DATE(YEAR(X$4)-1,12,31),$B$4:$Y$4,0)))/2),X36),"")</f>
+        <v/>
+      </c>
+      <c r="Y108" s="8">
+        <f>IF(ISNUMBER(Y36),IFERROR(IF(INDEX($B36:$Y36,MATCH(DATE(YEAR(Y$4)-1,12,31),$B$4:$Y$4,0))="",Y36,(Y36+INDEX($B36:$Y36,MATCH(DATE(YEAR(Y$4)-1,12,31),$B$4:$Y$4,0)))/2),Y36),"")</f>
         <v/>
       </c>
     </row>
@@ -32993,95 +33257,99 @@
         </is>
       </c>
       <c r="B109" s="8">
-        <f>IF(ISNUMBER(B68),IFERROR(IF(INDEX($B68:$X68,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$X$4,0))="",B68,(B68+INDEX($B68:$X68,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$X$4,0)))/2),B68),"")</f>
+        <f>IF(ISNUMBER(B68),IFERROR(IF(INDEX($B68:$Y68,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$Y$4,0))="",B68,(B68+INDEX($B68:$Y68,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$Y$4,0)))/2),B68),"")</f>
         <v/>
       </c>
       <c r="C109" s="8">
-        <f>IF(ISNUMBER(C68),IFERROR(IF(INDEX($B68:$X68,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$X$4,0))="",C68,(C68+INDEX($B68:$X68,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$X$4,0)))/2),C68),"")</f>
+        <f>IF(ISNUMBER(C68),IFERROR(IF(INDEX($B68:$Y68,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$Y$4,0))="",C68,(C68+INDEX($B68:$Y68,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$Y$4,0)))/2),C68),"")</f>
         <v/>
       </c>
       <c r="D109" s="8">
-        <f>IF(ISNUMBER(D68),IFERROR(IF(INDEX($B68:$X68,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$X$4,0))="",D68,(D68+INDEX($B68:$X68,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$X$4,0)))/2),D68),"")</f>
+        <f>IF(ISNUMBER(D68),IFERROR(IF(INDEX($B68:$Y68,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$Y$4,0))="",D68,(D68+INDEX($B68:$Y68,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$Y$4,0)))/2),D68),"")</f>
         <v/>
       </c>
       <c r="E109" s="8">
-        <f>IF(ISNUMBER(E68),IFERROR(IF(INDEX($B68:$X68,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$X$4,0))="",E68,(E68+INDEX($B68:$X68,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$X$4,0)))/2),E68),"")</f>
+        <f>IF(ISNUMBER(E68),IFERROR(IF(INDEX($B68:$Y68,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$Y$4,0))="",E68,(E68+INDEX($B68:$Y68,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$Y$4,0)))/2),E68),"")</f>
         <v/>
       </c>
       <c r="F109" s="8">
-        <f>IF(ISNUMBER(F68),IFERROR(IF(INDEX($B68:$X68,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$X$4,0))="",F68,(F68+INDEX($B68:$X68,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$X$4,0)))/2),F68),"")</f>
+        <f>IF(ISNUMBER(F68),IFERROR(IF(INDEX($B68:$Y68,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$Y$4,0))="",F68,(F68+INDEX($B68:$Y68,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$Y$4,0)))/2),F68),"")</f>
         <v/>
       </c>
       <c r="G109" s="8">
-        <f>IF(ISNUMBER(G68),IFERROR(IF(INDEX($B68:$X68,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$X$4,0))="",G68,(G68+INDEX($B68:$X68,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$X$4,0)))/2),G68),"")</f>
+        <f>IF(ISNUMBER(G68),IFERROR(IF(INDEX($B68:$Y68,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$Y$4,0))="",G68,(G68+INDEX($B68:$Y68,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$Y$4,0)))/2),G68),"")</f>
         <v/>
       </c>
       <c r="H109" s="8">
-        <f>IF(ISNUMBER(H68),IFERROR(IF(INDEX($B68:$X68,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$X$4,0))="",H68,(H68+INDEX($B68:$X68,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$X$4,0)))/2),H68),"")</f>
+        <f>IF(ISNUMBER(H68),IFERROR(IF(INDEX($B68:$Y68,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$Y$4,0))="",H68,(H68+INDEX($B68:$Y68,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$Y$4,0)))/2),H68),"")</f>
         <v/>
       </c>
       <c r="I109" s="8">
-        <f>IF(ISNUMBER(I68),IFERROR(IF(INDEX($B68:$X68,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$X$4,0))="",I68,(I68+INDEX($B68:$X68,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$X$4,0)))/2),I68),"")</f>
+        <f>IF(ISNUMBER(I68),IFERROR(IF(INDEX($B68:$Y68,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$Y$4,0))="",I68,(I68+INDEX($B68:$Y68,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$Y$4,0)))/2),I68),"")</f>
         <v/>
       </c>
       <c r="J109" s="8">
-        <f>IF(ISNUMBER(J68),IFERROR(IF(INDEX($B68:$X68,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$X$4,0))="",J68,(J68+INDEX($B68:$X68,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$X$4,0)))/2),J68),"")</f>
+        <f>IF(ISNUMBER(J68),IFERROR(IF(INDEX($B68:$Y68,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$Y$4,0))="",J68,(J68+INDEX($B68:$Y68,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$Y$4,0)))/2),J68),"")</f>
         <v/>
       </c>
       <c r="K109" s="8">
-        <f>IF(ISNUMBER(K68),IFERROR(IF(INDEX($B68:$X68,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$X$4,0))="",K68,(K68+INDEX($B68:$X68,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$X$4,0)))/2),K68),"")</f>
+        <f>IF(ISNUMBER(K68),IFERROR(IF(INDEX($B68:$Y68,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$Y$4,0))="",K68,(K68+INDEX($B68:$Y68,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$Y$4,0)))/2),K68),"")</f>
         <v/>
       </c>
       <c r="L109" s="8">
-        <f>IF(ISNUMBER(L68),IFERROR(IF(INDEX($B68:$X68,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$X$4,0))="",L68,(L68+INDEX($B68:$X68,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$X$4,0)))/2),L68),"")</f>
+        <f>IF(ISNUMBER(L68),IFERROR(IF(INDEX($B68:$Y68,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$Y$4,0))="",L68,(L68+INDEX($B68:$Y68,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$Y$4,0)))/2),L68),"")</f>
         <v/>
       </c>
       <c r="M109" s="8">
-        <f>IF(ISNUMBER(M68),IFERROR(IF(INDEX($B68:$X68,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$X$4,0))="",M68,(M68+INDEX($B68:$X68,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$X$4,0)))/2),M68),"")</f>
+        <f>IF(ISNUMBER(M68),IFERROR(IF(INDEX($B68:$Y68,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$Y$4,0))="",M68,(M68+INDEX($B68:$Y68,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$Y$4,0)))/2),M68),"")</f>
         <v/>
       </c>
       <c r="N109" s="8">
-        <f>IF(ISNUMBER(N68),IFERROR(IF(INDEX($B68:$X68,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$X$4,0))="",N68,(N68+INDEX($B68:$X68,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$X$4,0)))/2),N68),"")</f>
+        <f>IF(ISNUMBER(N68),IFERROR(IF(INDEX($B68:$Y68,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$Y$4,0))="",N68,(N68+INDEX($B68:$Y68,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$Y$4,0)))/2),N68),"")</f>
         <v/>
       </c>
       <c r="O109" s="8">
-        <f>IF(ISNUMBER(O68),IFERROR(IF(INDEX($B68:$X68,MATCH(DATE(YEAR(O$4)-1,12,31),$B$4:$X$4,0))="",O68,(O68+INDEX($B68:$X68,MATCH(DATE(YEAR(O$4)-1,12,31),$B$4:$X$4,0)))/2),O68),"")</f>
+        <f>IF(ISNUMBER(O68),IFERROR(IF(INDEX($B68:$Y68,MATCH(DATE(YEAR(O$4)-1,12,31),$B$4:$Y$4,0))="",O68,(O68+INDEX($B68:$Y68,MATCH(DATE(YEAR(O$4)-1,12,31),$B$4:$Y$4,0)))/2),O68),"")</f>
         <v/>
       </c>
       <c r="P109" s="8">
-        <f>IF(ISNUMBER(P68),IFERROR(IF(INDEX($B68:$X68,MATCH(DATE(YEAR(P$4)-1,12,31),$B$4:$X$4,0))="",P68,(P68+INDEX($B68:$X68,MATCH(DATE(YEAR(P$4)-1,12,31),$B$4:$X$4,0)))/2),P68),"")</f>
+        <f>IF(ISNUMBER(P68),IFERROR(IF(INDEX($B68:$Y68,MATCH(DATE(YEAR(P$4)-1,12,31),$B$4:$Y$4,0))="",P68,(P68+INDEX($B68:$Y68,MATCH(DATE(YEAR(P$4)-1,12,31),$B$4:$Y$4,0)))/2),P68),"")</f>
         <v/>
       </c>
       <c r="Q109" s="8">
-        <f>IF(ISNUMBER(Q68),IFERROR(IF(INDEX($B68:$X68,MATCH(DATE(YEAR(Q$4)-1,12,31),$B$4:$X$4,0))="",Q68,(Q68+INDEX($B68:$X68,MATCH(DATE(YEAR(Q$4)-1,12,31),$B$4:$X$4,0)))/2),Q68),"")</f>
+        <f>IF(ISNUMBER(Q68),IFERROR(IF(INDEX($B68:$Y68,MATCH(DATE(YEAR(Q$4)-1,12,31),$B$4:$Y$4,0))="",Q68,(Q68+INDEX($B68:$Y68,MATCH(DATE(YEAR(Q$4)-1,12,31),$B$4:$Y$4,0)))/2),Q68),"")</f>
         <v/>
       </c>
       <c r="R109" s="8">
-        <f>IF(ISNUMBER(R68),IFERROR(IF(INDEX($B68:$X68,MATCH(DATE(YEAR(R$4)-1,12,31),$B$4:$X$4,0))="",R68,(R68+INDEX($B68:$X68,MATCH(DATE(YEAR(R$4)-1,12,31),$B$4:$X$4,0)))/2),R68),"")</f>
+        <f>IF(ISNUMBER(R68),IFERROR(IF(INDEX($B68:$Y68,MATCH(DATE(YEAR(R$4)-1,12,31),$B$4:$Y$4,0))="",R68,(R68+INDEX($B68:$Y68,MATCH(DATE(YEAR(R$4)-1,12,31),$B$4:$Y$4,0)))/2),R68),"")</f>
         <v/>
       </c>
       <c r="S109" s="8">
-        <f>IF(ISNUMBER(S68),IFERROR(IF(INDEX($B68:$X68,MATCH(DATE(YEAR(S$4)-1,12,31),$B$4:$X$4,0))="",S68,(S68+INDEX($B68:$X68,MATCH(DATE(YEAR(S$4)-1,12,31),$B$4:$X$4,0)))/2),S68),"")</f>
+        <f>IF(ISNUMBER(S68),IFERROR(IF(INDEX($B68:$Y68,MATCH(DATE(YEAR(S$4)-1,12,31),$B$4:$Y$4,0))="",S68,(S68+INDEX($B68:$Y68,MATCH(DATE(YEAR(S$4)-1,12,31),$B$4:$Y$4,0)))/2),S68),"")</f>
         <v/>
       </c>
       <c r="T109" s="8">
-        <f>IF(ISNUMBER(T68),IFERROR(IF(INDEX($B68:$X68,MATCH(DATE(YEAR(T$4)-1,12,31),$B$4:$X$4,0))="",T68,(T68+INDEX($B68:$X68,MATCH(DATE(YEAR(T$4)-1,12,31),$B$4:$X$4,0)))/2),T68),"")</f>
+        <f>IF(ISNUMBER(T68),IFERROR(IF(INDEX($B68:$Y68,MATCH(DATE(YEAR(T$4)-1,12,31),$B$4:$Y$4,0))="",T68,(T68+INDEX($B68:$Y68,MATCH(DATE(YEAR(T$4)-1,12,31),$B$4:$Y$4,0)))/2),T68),"")</f>
         <v/>
       </c>
       <c r="U109" s="8">
-        <f>IF(ISNUMBER(U68),IFERROR(IF(INDEX($B68:$X68,MATCH(DATE(YEAR(U$4)-1,12,31),$B$4:$X$4,0))="",U68,(U68+INDEX($B68:$X68,MATCH(DATE(YEAR(U$4)-1,12,31),$B$4:$X$4,0)))/2),U68),"")</f>
+        <f>IF(ISNUMBER(U68),IFERROR(IF(INDEX($B68:$Y68,MATCH(DATE(YEAR(U$4)-1,12,31),$B$4:$Y$4,0))="",U68,(U68+INDEX($B68:$Y68,MATCH(DATE(YEAR(U$4)-1,12,31),$B$4:$Y$4,0)))/2),U68),"")</f>
         <v/>
       </c>
       <c r="V109" s="8">
-        <f>IF(ISNUMBER(V68),IFERROR(IF(INDEX($B68:$X68,MATCH(DATE(YEAR(V$4)-1,12,31),$B$4:$X$4,0))="",V68,(V68+INDEX($B68:$X68,MATCH(DATE(YEAR(V$4)-1,12,31),$B$4:$X$4,0)))/2),V68),"")</f>
+        <f>IF(ISNUMBER(V68),IFERROR(IF(INDEX($B68:$Y68,MATCH(DATE(YEAR(V$4)-1,12,31),$B$4:$Y$4,0))="",V68,(V68+INDEX($B68:$Y68,MATCH(DATE(YEAR(V$4)-1,12,31),$B$4:$Y$4,0)))/2),V68),"")</f>
         <v/>
       </c>
       <c r="W109" s="8">
-        <f>IF(ISNUMBER(W68),IFERROR(IF(INDEX($B68:$X68,MATCH(DATE(YEAR(W$4)-1,12,31),$B$4:$X$4,0))="",W68,(W68+INDEX($B68:$X68,MATCH(DATE(YEAR(W$4)-1,12,31),$B$4:$X$4,0)))/2),W68),"")</f>
+        <f>IF(ISNUMBER(W68),IFERROR(IF(INDEX($B68:$Y68,MATCH(DATE(YEAR(W$4)-1,12,31),$B$4:$Y$4,0))="",W68,(W68+INDEX($B68:$Y68,MATCH(DATE(YEAR(W$4)-1,12,31),$B$4:$Y$4,0)))/2),W68),"")</f>
         <v/>
       </c>
       <c r="X109" s="8">
-        <f>IF(ISNUMBER(X68),IFERROR(IF(INDEX($B68:$X68,MATCH(DATE(YEAR(X$4)-1,12,31),$B$4:$X$4,0))="",X68,(X68+INDEX($B68:$X68,MATCH(DATE(YEAR(X$4)-1,12,31),$B$4:$X$4,0)))/2),X68),"")</f>
+        <f>IF(ISNUMBER(X68),IFERROR(IF(INDEX($B68:$Y68,MATCH(DATE(YEAR(X$4)-1,12,31),$B$4:$Y$4,0))="",X68,(X68+INDEX($B68:$Y68,MATCH(DATE(YEAR(X$4)-1,12,31),$B$4:$Y$4,0)))/2),X68),"")</f>
+        <v/>
+      </c>
+      <c r="Y109" s="8">
+        <f>IF(ISNUMBER(Y68),IFERROR(IF(INDEX($B68:$Y68,MATCH(DATE(YEAR(Y$4)-1,12,31),$B$4:$Y$4,0))="",Y68,(Y68+INDEX($B68:$Y68,MATCH(DATE(YEAR(Y$4)-1,12,31),$B$4:$Y$4,0)))/2),Y68),"")</f>
         <v/>
       </c>
     </row>
@@ -33092,95 +33360,99 @@
         </is>
       </c>
       <c r="B110" s="8">
-        <f>IF(ISNUMBER(B17),IFERROR(IF(INDEX($B17:$X17,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$X$4,0))="",B17,(B17+INDEX($B17:$X17,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$X$4,0)))/2),B17),"")</f>
+        <f>IF(ISNUMBER(B17),IFERROR(IF(INDEX($B17:$Y17,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$Y$4,0))="",B17,(B17+INDEX($B17:$Y17,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$Y$4,0)))/2),B17),"")</f>
         <v/>
       </c>
       <c r="C110" s="8">
-        <f>IF(ISNUMBER(C17),IFERROR(IF(INDEX($B17:$X17,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$X$4,0))="",C17,(C17+INDEX($B17:$X17,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$X$4,0)))/2),C17),"")</f>
+        <f>IF(ISNUMBER(C17),IFERROR(IF(INDEX($B17:$Y17,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$Y$4,0))="",C17,(C17+INDEX($B17:$Y17,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$Y$4,0)))/2),C17),"")</f>
         <v/>
       </c>
       <c r="D110" s="8">
-        <f>IF(ISNUMBER(D17),IFERROR(IF(INDEX($B17:$X17,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$X$4,0))="",D17,(D17+INDEX($B17:$X17,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$X$4,0)))/2),D17),"")</f>
+        <f>IF(ISNUMBER(D17),IFERROR(IF(INDEX($B17:$Y17,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$Y$4,0))="",D17,(D17+INDEX($B17:$Y17,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$Y$4,0)))/2),D17),"")</f>
         <v/>
       </c>
       <c r="E110" s="8">
-        <f>IF(ISNUMBER(E17),IFERROR(IF(INDEX($B17:$X17,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$X$4,0))="",E17,(E17+INDEX($B17:$X17,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$X$4,0)))/2),E17),"")</f>
+        <f>IF(ISNUMBER(E17),IFERROR(IF(INDEX($B17:$Y17,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$Y$4,0))="",E17,(E17+INDEX($B17:$Y17,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$Y$4,0)))/2),E17),"")</f>
         <v/>
       </c>
       <c r="F110" s="8">
-        <f>IF(ISNUMBER(F17),IFERROR(IF(INDEX($B17:$X17,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$X$4,0))="",F17,(F17+INDEX($B17:$X17,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$X$4,0)))/2),F17),"")</f>
+        <f>IF(ISNUMBER(F17),IFERROR(IF(INDEX($B17:$Y17,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$Y$4,0))="",F17,(F17+INDEX($B17:$Y17,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$Y$4,0)))/2),F17),"")</f>
         <v/>
       </c>
       <c r="G110" s="8">
-        <f>IF(ISNUMBER(G17),IFERROR(IF(INDEX($B17:$X17,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$X$4,0))="",G17,(G17+INDEX($B17:$X17,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$X$4,0)))/2),G17),"")</f>
+        <f>IF(ISNUMBER(G17),IFERROR(IF(INDEX($B17:$Y17,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$Y$4,0))="",G17,(G17+INDEX($B17:$Y17,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$Y$4,0)))/2),G17),"")</f>
         <v/>
       </c>
       <c r="H110" s="8">
-        <f>IF(ISNUMBER(H17),IFERROR(IF(INDEX($B17:$X17,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$X$4,0))="",H17,(H17+INDEX($B17:$X17,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$X$4,0)))/2),H17),"")</f>
+        <f>IF(ISNUMBER(H17),IFERROR(IF(INDEX($B17:$Y17,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$Y$4,0))="",H17,(H17+INDEX($B17:$Y17,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$Y$4,0)))/2),H17),"")</f>
         <v/>
       </c>
       <c r="I110" s="8">
-        <f>IF(ISNUMBER(I17),IFERROR(IF(INDEX($B17:$X17,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$X$4,0))="",I17,(I17+INDEX($B17:$X17,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$X$4,0)))/2),I17),"")</f>
+        <f>IF(ISNUMBER(I17),IFERROR(IF(INDEX($B17:$Y17,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$Y$4,0))="",I17,(I17+INDEX($B17:$Y17,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$Y$4,0)))/2),I17),"")</f>
         <v/>
       </c>
       <c r="J110" s="8">
-        <f>IF(ISNUMBER(J17),IFERROR(IF(INDEX($B17:$X17,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$X$4,0))="",J17,(J17+INDEX($B17:$X17,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$X$4,0)))/2),J17),"")</f>
+        <f>IF(ISNUMBER(J17),IFERROR(IF(INDEX($B17:$Y17,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$Y$4,0))="",J17,(J17+INDEX($B17:$Y17,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$Y$4,0)))/2),J17),"")</f>
         <v/>
       </c>
       <c r="K110" s="8">
-        <f>IF(ISNUMBER(K17),IFERROR(IF(INDEX($B17:$X17,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$X$4,0))="",K17,(K17+INDEX($B17:$X17,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$X$4,0)))/2),K17),"")</f>
+        <f>IF(ISNUMBER(K17),IFERROR(IF(INDEX($B17:$Y17,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$Y$4,0))="",K17,(K17+INDEX($B17:$Y17,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$Y$4,0)))/2),K17),"")</f>
         <v/>
       </c>
       <c r="L110" s="8">
-        <f>IF(ISNUMBER(L17),IFERROR(IF(INDEX($B17:$X17,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$X$4,0))="",L17,(L17+INDEX($B17:$X17,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$X$4,0)))/2),L17),"")</f>
+        <f>IF(ISNUMBER(L17),IFERROR(IF(INDEX($B17:$Y17,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$Y$4,0))="",L17,(L17+INDEX($B17:$Y17,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$Y$4,0)))/2),L17),"")</f>
         <v/>
       </c>
       <c r="M110" s="8">
-        <f>IF(ISNUMBER(M17),IFERROR(IF(INDEX($B17:$X17,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$X$4,0))="",M17,(M17+INDEX($B17:$X17,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$X$4,0)))/2),M17),"")</f>
+        <f>IF(ISNUMBER(M17),IFERROR(IF(INDEX($B17:$Y17,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$Y$4,0))="",M17,(M17+INDEX($B17:$Y17,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$Y$4,0)))/2),M17),"")</f>
         <v/>
       </c>
       <c r="N110" s="8">
-        <f>IF(ISNUMBER(N17),IFERROR(IF(INDEX($B17:$X17,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$X$4,0))="",N17,(N17+INDEX($B17:$X17,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$X$4,0)))/2),N17),"")</f>
+        <f>IF(ISNUMBER(N17),IFERROR(IF(INDEX($B17:$Y17,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$Y$4,0))="",N17,(N17+INDEX($B17:$Y17,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$Y$4,0)))/2),N17),"")</f>
         <v/>
       </c>
       <c r="O110" s="8">
-        <f>IF(ISNUMBER(O17),IFERROR(IF(INDEX($B17:$X17,MATCH(DATE(YEAR(O$4)-1,12,31),$B$4:$X$4,0))="",O17,(O17+INDEX($B17:$X17,MATCH(DATE(YEAR(O$4)-1,12,31),$B$4:$X$4,0)))/2),O17),"")</f>
+        <f>IF(ISNUMBER(O17),IFERROR(IF(INDEX($B17:$Y17,MATCH(DATE(YEAR(O$4)-1,12,31),$B$4:$Y$4,0))="",O17,(O17+INDEX($B17:$Y17,MATCH(DATE(YEAR(O$4)-1,12,31),$B$4:$Y$4,0)))/2),O17),"")</f>
         <v/>
       </c>
       <c r="P110" s="8">
-        <f>IF(ISNUMBER(P17),IFERROR(IF(INDEX($B17:$X17,MATCH(DATE(YEAR(P$4)-1,12,31),$B$4:$X$4,0))="",P17,(P17+INDEX($B17:$X17,MATCH(DATE(YEAR(P$4)-1,12,31),$B$4:$X$4,0)))/2),P17),"")</f>
+        <f>IF(ISNUMBER(P17),IFERROR(IF(INDEX($B17:$Y17,MATCH(DATE(YEAR(P$4)-1,12,31),$B$4:$Y$4,0))="",P17,(P17+INDEX($B17:$Y17,MATCH(DATE(YEAR(P$4)-1,12,31),$B$4:$Y$4,0)))/2),P17),"")</f>
         <v/>
       </c>
       <c r="Q110" s="8">
-        <f>IF(ISNUMBER(Q17),IFERROR(IF(INDEX($B17:$X17,MATCH(DATE(YEAR(Q$4)-1,12,31),$B$4:$X$4,0))="",Q17,(Q17+INDEX($B17:$X17,MATCH(DATE(YEAR(Q$4)-1,12,31),$B$4:$X$4,0)))/2),Q17),"")</f>
+        <f>IF(ISNUMBER(Q17),IFERROR(IF(INDEX($B17:$Y17,MATCH(DATE(YEAR(Q$4)-1,12,31),$B$4:$Y$4,0))="",Q17,(Q17+INDEX($B17:$Y17,MATCH(DATE(YEAR(Q$4)-1,12,31),$B$4:$Y$4,0)))/2),Q17),"")</f>
         <v/>
       </c>
       <c r="R110" s="8">
-        <f>IF(ISNUMBER(R17),IFERROR(IF(INDEX($B17:$X17,MATCH(DATE(YEAR(R$4)-1,12,31),$B$4:$X$4,0))="",R17,(R17+INDEX($B17:$X17,MATCH(DATE(YEAR(R$4)-1,12,31),$B$4:$X$4,0)))/2),R17),"")</f>
+        <f>IF(ISNUMBER(R17),IFERROR(IF(INDEX($B17:$Y17,MATCH(DATE(YEAR(R$4)-1,12,31),$B$4:$Y$4,0))="",R17,(R17+INDEX($B17:$Y17,MATCH(DATE(YEAR(R$4)-1,12,31),$B$4:$Y$4,0)))/2),R17),"")</f>
         <v/>
       </c>
       <c r="S110" s="8">
-        <f>IF(ISNUMBER(S17),IFERROR(IF(INDEX($B17:$X17,MATCH(DATE(YEAR(S$4)-1,12,31),$B$4:$X$4,0))="",S17,(S17+INDEX($B17:$X17,MATCH(DATE(YEAR(S$4)-1,12,31),$B$4:$X$4,0)))/2),S17),"")</f>
+        <f>IF(ISNUMBER(S17),IFERROR(IF(INDEX($B17:$Y17,MATCH(DATE(YEAR(S$4)-1,12,31),$B$4:$Y$4,0))="",S17,(S17+INDEX($B17:$Y17,MATCH(DATE(YEAR(S$4)-1,12,31),$B$4:$Y$4,0)))/2),S17),"")</f>
         <v/>
       </c>
       <c r="T110" s="8">
-        <f>IF(ISNUMBER(T17),IFERROR(IF(INDEX($B17:$X17,MATCH(DATE(YEAR(T$4)-1,12,31),$B$4:$X$4,0))="",T17,(T17+INDEX($B17:$X17,MATCH(DATE(YEAR(T$4)-1,12,31),$B$4:$X$4,0)))/2),T17),"")</f>
+        <f>IF(ISNUMBER(T17),IFERROR(IF(INDEX($B17:$Y17,MATCH(DATE(YEAR(T$4)-1,12,31),$B$4:$Y$4,0))="",T17,(T17+INDEX($B17:$Y17,MATCH(DATE(YEAR(T$4)-1,12,31),$B$4:$Y$4,0)))/2),T17),"")</f>
         <v/>
       </c>
       <c r="U110" s="8">
-        <f>IF(ISNUMBER(U17),IFERROR(IF(INDEX($B17:$X17,MATCH(DATE(YEAR(U$4)-1,12,31),$B$4:$X$4,0))="",U17,(U17+INDEX($B17:$X17,MATCH(DATE(YEAR(U$4)-1,12,31),$B$4:$X$4,0)))/2),U17),"")</f>
+        <f>IF(ISNUMBER(U17),IFERROR(IF(INDEX($B17:$Y17,MATCH(DATE(YEAR(U$4)-1,12,31),$B$4:$Y$4,0))="",U17,(U17+INDEX($B17:$Y17,MATCH(DATE(YEAR(U$4)-1,12,31),$B$4:$Y$4,0)))/2),U17),"")</f>
         <v/>
       </c>
       <c r="V110" s="8">
-        <f>IF(ISNUMBER(V17),IFERROR(IF(INDEX($B17:$X17,MATCH(DATE(YEAR(V$4)-1,12,31),$B$4:$X$4,0))="",V17,(V17+INDEX($B17:$X17,MATCH(DATE(YEAR(V$4)-1,12,31),$B$4:$X$4,0)))/2),V17),"")</f>
+        <f>IF(ISNUMBER(V17),IFERROR(IF(INDEX($B17:$Y17,MATCH(DATE(YEAR(V$4)-1,12,31),$B$4:$Y$4,0))="",V17,(V17+INDEX($B17:$Y17,MATCH(DATE(YEAR(V$4)-1,12,31),$B$4:$Y$4,0)))/2),V17),"")</f>
         <v/>
       </c>
       <c r="W110" s="8">
-        <f>IF(ISNUMBER(W17),IFERROR(IF(INDEX($B17:$X17,MATCH(DATE(YEAR(W$4)-1,12,31),$B$4:$X$4,0))="",W17,(W17+INDEX($B17:$X17,MATCH(DATE(YEAR(W$4)-1,12,31),$B$4:$X$4,0)))/2),W17),"")</f>
+        <f>IF(ISNUMBER(W17),IFERROR(IF(INDEX($B17:$Y17,MATCH(DATE(YEAR(W$4)-1,12,31),$B$4:$Y$4,0))="",W17,(W17+INDEX($B17:$Y17,MATCH(DATE(YEAR(W$4)-1,12,31),$B$4:$Y$4,0)))/2),W17),"")</f>
         <v/>
       </c>
       <c r="X110" s="8">
-        <f>IF(ISNUMBER(X17),IFERROR(IF(INDEX($B17:$X17,MATCH(DATE(YEAR(X$4)-1,12,31),$B$4:$X$4,0))="",X17,(X17+INDEX($B17:$X17,MATCH(DATE(YEAR(X$4)-1,12,31),$B$4:$X$4,0)))/2),X17),"")</f>
+        <f>IF(ISNUMBER(X17),IFERROR(IF(INDEX($B17:$Y17,MATCH(DATE(YEAR(X$4)-1,12,31),$B$4:$Y$4,0))="",X17,(X17+INDEX($B17:$Y17,MATCH(DATE(YEAR(X$4)-1,12,31),$B$4:$Y$4,0)))/2),X17),"")</f>
+        <v/>
+      </c>
+      <c r="Y110" s="8">
+        <f>IF(ISNUMBER(Y17),IFERROR(IF(INDEX($B17:$Y17,MATCH(DATE(YEAR(Y$4)-1,12,31),$B$4:$Y$4,0))="",Y17,(Y17+INDEX($B17:$Y17,MATCH(DATE(YEAR(Y$4)-1,12,31),$B$4:$Y$4,0)))/2),Y17),"")</f>
         <v/>
       </c>
     </row>
@@ -33191,95 +33463,99 @@
         </is>
       </c>
       <c r="B111" s="8">
-        <f>IF(ISNUMBER(B13),IFERROR(IF(INDEX($B13:$X13,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$X$4,0))="",B13,(B13+INDEX($B13:$X13,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$X$4,0)))/2),B13),"")</f>
+        <f>IF(ISNUMBER(B13),IFERROR(IF(INDEX($B13:$Y13,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$Y$4,0))="",B13,(B13+INDEX($B13:$Y13,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$Y$4,0)))/2),B13),"")</f>
         <v/>
       </c>
       <c r="C111" s="8">
-        <f>IF(ISNUMBER(C13),IFERROR(IF(INDEX($B13:$X13,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$X$4,0))="",C13,(C13+INDEX($B13:$X13,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$X$4,0)))/2),C13),"")</f>
+        <f>IF(ISNUMBER(C13),IFERROR(IF(INDEX($B13:$Y13,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$Y$4,0))="",C13,(C13+INDEX($B13:$Y13,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$Y$4,0)))/2),C13),"")</f>
         <v/>
       </c>
       <c r="D111" s="8">
-        <f>IF(ISNUMBER(D13),IFERROR(IF(INDEX($B13:$X13,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$X$4,0))="",D13,(D13+INDEX($B13:$X13,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$X$4,0)))/2),D13),"")</f>
+        <f>IF(ISNUMBER(D13),IFERROR(IF(INDEX($B13:$Y13,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$Y$4,0))="",D13,(D13+INDEX($B13:$Y13,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$Y$4,0)))/2),D13),"")</f>
         <v/>
       </c>
       <c r="E111" s="8">
-        <f>IF(ISNUMBER(E13),IFERROR(IF(INDEX($B13:$X13,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$X$4,0))="",E13,(E13+INDEX($B13:$X13,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$X$4,0)))/2),E13),"")</f>
+        <f>IF(ISNUMBER(E13),IFERROR(IF(INDEX($B13:$Y13,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$Y$4,0))="",E13,(E13+INDEX($B13:$Y13,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$Y$4,0)))/2),E13),"")</f>
         <v/>
       </c>
       <c r="F111" s="8">
-        <f>IF(ISNUMBER(F13),IFERROR(IF(INDEX($B13:$X13,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$X$4,0))="",F13,(F13+INDEX($B13:$X13,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$X$4,0)))/2),F13),"")</f>
+        <f>IF(ISNUMBER(F13),IFERROR(IF(INDEX($B13:$Y13,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$Y$4,0))="",F13,(F13+INDEX($B13:$Y13,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$Y$4,0)))/2),F13),"")</f>
         <v/>
       </c>
       <c r="G111" s="8">
-        <f>IF(ISNUMBER(G13),IFERROR(IF(INDEX($B13:$X13,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$X$4,0))="",G13,(G13+INDEX($B13:$X13,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$X$4,0)))/2),G13),"")</f>
+        <f>IF(ISNUMBER(G13),IFERROR(IF(INDEX($B13:$Y13,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$Y$4,0))="",G13,(G13+INDEX($B13:$Y13,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$Y$4,0)))/2),G13),"")</f>
         <v/>
       </c>
       <c r="H111" s="8">
-        <f>IF(ISNUMBER(H13),IFERROR(IF(INDEX($B13:$X13,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$X$4,0))="",H13,(H13+INDEX($B13:$X13,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$X$4,0)))/2),H13),"")</f>
+        <f>IF(ISNUMBER(H13),IFERROR(IF(INDEX($B13:$Y13,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$Y$4,0))="",H13,(H13+INDEX($B13:$Y13,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$Y$4,0)))/2),H13),"")</f>
         <v/>
       </c>
       <c r="I111" s="8">
-        <f>IF(ISNUMBER(I13),IFERROR(IF(INDEX($B13:$X13,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$X$4,0))="",I13,(I13+INDEX($B13:$X13,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$X$4,0)))/2),I13),"")</f>
+        <f>IF(ISNUMBER(I13),IFERROR(IF(INDEX($B13:$Y13,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$Y$4,0))="",I13,(I13+INDEX($B13:$Y13,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$Y$4,0)))/2),I13),"")</f>
         <v/>
       </c>
       <c r="J111" s="8">
-        <f>IF(ISNUMBER(J13),IFERROR(IF(INDEX($B13:$X13,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$X$4,0))="",J13,(J13+INDEX($B13:$X13,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$X$4,0)))/2),J13),"")</f>
+        <f>IF(ISNUMBER(J13),IFERROR(IF(INDEX($B13:$Y13,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$Y$4,0))="",J13,(J13+INDEX($B13:$Y13,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$Y$4,0)))/2),J13),"")</f>
         <v/>
       </c>
       <c r="K111" s="8">
-        <f>IF(ISNUMBER(K13),IFERROR(IF(INDEX($B13:$X13,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$X$4,0))="",K13,(K13+INDEX($B13:$X13,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$X$4,0)))/2),K13),"")</f>
+        <f>IF(ISNUMBER(K13),IFERROR(IF(INDEX($B13:$Y13,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$Y$4,0))="",K13,(K13+INDEX($B13:$Y13,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$Y$4,0)))/2),K13),"")</f>
         <v/>
       </c>
       <c r="L111" s="8">
-        <f>IF(ISNUMBER(L13),IFERROR(IF(INDEX($B13:$X13,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$X$4,0))="",L13,(L13+INDEX($B13:$X13,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$X$4,0)))/2),L13),"")</f>
+        <f>IF(ISNUMBER(L13),IFERROR(IF(INDEX($B13:$Y13,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$Y$4,0))="",L13,(L13+INDEX($B13:$Y13,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$Y$4,0)))/2),L13),"")</f>
         <v/>
       </c>
       <c r="M111" s="8">
-        <f>IF(ISNUMBER(M13),IFERROR(IF(INDEX($B13:$X13,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$X$4,0))="",M13,(M13+INDEX($B13:$X13,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$X$4,0)))/2),M13),"")</f>
+        <f>IF(ISNUMBER(M13),IFERROR(IF(INDEX($B13:$Y13,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$Y$4,0))="",M13,(M13+INDEX($B13:$Y13,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$Y$4,0)))/2),M13),"")</f>
         <v/>
       </c>
       <c r="N111" s="8">
-        <f>IF(ISNUMBER(N13),IFERROR(IF(INDEX($B13:$X13,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$X$4,0))="",N13,(N13+INDEX($B13:$X13,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$X$4,0)))/2),N13),"")</f>
+        <f>IF(ISNUMBER(N13),IFERROR(IF(INDEX($B13:$Y13,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$Y$4,0))="",N13,(N13+INDEX($B13:$Y13,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$Y$4,0)))/2),N13),"")</f>
         <v/>
       </c>
       <c r="O111" s="8">
-        <f>IF(ISNUMBER(O13),IFERROR(IF(INDEX($B13:$X13,MATCH(DATE(YEAR(O$4)-1,12,31),$B$4:$X$4,0))="",O13,(O13+INDEX($B13:$X13,MATCH(DATE(YEAR(O$4)-1,12,31),$B$4:$X$4,0)))/2),O13),"")</f>
+        <f>IF(ISNUMBER(O13),IFERROR(IF(INDEX($B13:$Y13,MATCH(DATE(YEAR(O$4)-1,12,31),$B$4:$Y$4,0))="",O13,(O13+INDEX($B13:$Y13,MATCH(DATE(YEAR(O$4)-1,12,31),$B$4:$Y$4,0)))/2),O13),"")</f>
         <v/>
       </c>
       <c r="P111" s="8">
-        <f>IF(ISNUMBER(P13),IFERROR(IF(INDEX($B13:$X13,MATCH(DATE(YEAR(P$4)-1,12,31),$B$4:$X$4,0))="",P13,(P13+INDEX($B13:$X13,MATCH(DATE(YEAR(P$4)-1,12,31),$B$4:$X$4,0)))/2),P13),"")</f>
+        <f>IF(ISNUMBER(P13),IFERROR(IF(INDEX($B13:$Y13,MATCH(DATE(YEAR(P$4)-1,12,31),$B$4:$Y$4,0))="",P13,(P13+INDEX($B13:$Y13,MATCH(DATE(YEAR(P$4)-1,12,31),$B$4:$Y$4,0)))/2),P13),"")</f>
         <v/>
       </c>
       <c r="Q111" s="8">
-        <f>IF(ISNUMBER(Q13),IFERROR(IF(INDEX($B13:$X13,MATCH(DATE(YEAR(Q$4)-1,12,31),$B$4:$X$4,0))="",Q13,(Q13+INDEX($B13:$X13,MATCH(DATE(YEAR(Q$4)-1,12,31),$B$4:$X$4,0)))/2),Q13),"")</f>
+        <f>IF(ISNUMBER(Q13),IFERROR(IF(INDEX($B13:$Y13,MATCH(DATE(YEAR(Q$4)-1,12,31),$B$4:$Y$4,0))="",Q13,(Q13+INDEX($B13:$Y13,MATCH(DATE(YEAR(Q$4)-1,12,31),$B$4:$Y$4,0)))/2),Q13),"")</f>
         <v/>
       </c>
       <c r="R111" s="8">
-        <f>IF(ISNUMBER(R13),IFERROR(IF(INDEX($B13:$X13,MATCH(DATE(YEAR(R$4)-1,12,31),$B$4:$X$4,0))="",R13,(R13+INDEX($B13:$X13,MATCH(DATE(YEAR(R$4)-1,12,31),$B$4:$X$4,0)))/2),R13),"")</f>
+        <f>IF(ISNUMBER(R13),IFERROR(IF(INDEX($B13:$Y13,MATCH(DATE(YEAR(R$4)-1,12,31),$B$4:$Y$4,0))="",R13,(R13+INDEX($B13:$Y13,MATCH(DATE(YEAR(R$4)-1,12,31),$B$4:$Y$4,0)))/2),R13),"")</f>
         <v/>
       </c>
       <c r="S111" s="8">
-        <f>IF(ISNUMBER(S13),IFERROR(IF(INDEX($B13:$X13,MATCH(DATE(YEAR(S$4)-1,12,31),$B$4:$X$4,0))="",S13,(S13+INDEX($B13:$X13,MATCH(DATE(YEAR(S$4)-1,12,31),$B$4:$X$4,0)))/2),S13),"")</f>
+        <f>IF(ISNUMBER(S13),IFERROR(IF(INDEX($B13:$Y13,MATCH(DATE(YEAR(S$4)-1,12,31),$B$4:$Y$4,0))="",S13,(S13+INDEX($B13:$Y13,MATCH(DATE(YEAR(S$4)-1,12,31),$B$4:$Y$4,0)))/2),S13),"")</f>
         <v/>
       </c>
       <c r="T111" s="8">
-        <f>IF(ISNUMBER(T13),IFERROR(IF(INDEX($B13:$X13,MATCH(DATE(YEAR(T$4)-1,12,31),$B$4:$X$4,0))="",T13,(T13+INDEX($B13:$X13,MATCH(DATE(YEAR(T$4)-1,12,31),$B$4:$X$4,0)))/2),T13),"")</f>
+        <f>IF(ISNUMBER(T13),IFERROR(IF(INDEX($B13:$Y13,MATCH(DATE(YEAR(T$4)-1,12,31),$B$4:$Y$4,0))="",T13,(T13+INDEX($B13:$Y13,MATCH(DATE(YEAR(T$4)-1,12,31),$B$4:$Y$4,0)))/2),T13),"")</f>
         <v/>
       </c>
       <c r="U111" s="8">
-        <f>IF(ISNUMBER(U13),IFERROR(IF(INDEX($B13:$X13,MATCH(DATE(YEAR(U$4)-1,12,31),$B$4:$X$4,0))="",U13,(U13+INDEX($B13:$X13,MATCH(DATE(YEAR(U$4)-1,12,31),$B$4:$X$4,0)))/2),U13),"")</f>
+        <f>IF(ISNUMBER(U13),IFERROR(IF(INDEX($B13:$Y13,MATCH(DATE(YEAR(U$4)-1,12,31),$B$4:$Y$4,0))="",U13,(U13+INDEX($B13:$Y13,MATCH(DATE(YEAR(U$4)-1,12,31),$B$4:$Y$4,0)))/2),U13),"")</f>
         <v/>
       </c>
       <c r="V111" s="8">
-        <f>IF(ISNUMBER(V13),IFERROR(IF(INDEX($B13:$X13,MATCH(DATE(YEAR(V$4)-1,12,31),$B$4:$X$4,0))="",V13,(V13+INDEX($B13:$X13,MATCH(DATE(YEAR(V$4)-1,12,31),$B$4:$X$4,0)))/2),V13),"")</f>
+        <f>IF(ISNUMBER(V13),IFERROR(IF(INDEX($B13:$Y13,MATCH(DATE(YEAR(V$4)-1,12,31),$B$4:$Y$4,0))="",V13,(V13+INDEX($B13:$Y13,MATCH(DATE(YEAR(V$4)-1,12,31),$B$4:$Y$4,0)))/2),V13),"")</f>
         <v/>
       </c>
       <c r="W111" s="8">
-        <f>IF(ISNUMBER(W13),IFERROR(IF(INDEX($B13:$X13,MATCH(DATE(YEAR(W$4)-1,12,31),$B$4:$X$4,0))="",W13,(W13+INDEX($B13:$X13,MATCH(DATE(YEAR(W$4)-1,12,31),$B$4:$X$4,0)))/2),W13),"")</f>
+        <f>IF(ISNUMBER(W13),IFERROR(IF(INDEX($B13:$Y13,MATCH(DATE(YEAR(W$4)-1,12,31),$B$4:$Y$4,0))="",W13,(W13+INDEX($B13:$Y13,MATCH(DATE(YEAR(W$4)-1,12,31),$B$4:$Y$4,0)))/2),W13),"")</f>
         <v/>
       </c>
       <c r="X111" s="8">
-        <f>IF(ISNUMBER(X13),IFERROR(IF(INDEX($B13:$X13,MATCH(DATE(YEAR(X$4)-1,12,31),$B$4:$X$4,0))="",X13,(X13+INDEX($B13:$X13,MATCH(DATE(YEAR(X$4)-1,12,31),$B$4:$X$4,0)))/2),X13),"")</f>
+        <f>IF(ISNUMBER(X13),IFERROR(IF(INDEX($B13:$Y13,MATCH(DATE(YEAR(X$4)-1,12,31),$B$4:$Y$4,0))="",X13,(X13+INDEX($B13:$Y13,MATCH(DATE(YEAR(X$4)-1,12,31),$B$4:$Y$4,0)))/2),X13),"")</f>
+        <v/>
+      </c>
+      <c r="Y111" s="8">
+        <f>IF(ISNUMBER(Y13),IFERROR(IF(INDEX($B13:$Y13,MATCH(DATE(YEAR(Y$4)-1,12,31),$B$4:$Y$4,0))="",Y13,(Y13+INDEX($B13:$Y13,MATCH(DATE(YEAR(Y$4)-1,12,31),$B$4:$Y$4,0)))/2),Y13),"")</f>
         <v/>
       </c>
     </row>
@@ -33290,95 +33566,99 @@
         </is>
       </c>
       <c r="B112" s="8">
-        <f>IF(ISNUMBER(B38),IFERROR(IF(INDEX($B38:$X38,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$X$4,0))="",B38,(B38+INDEX($B38:$X38,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$X$4,0)))/2),B38),"")</f>
+        <f>IF(ISNUMBER(B38),IFERROR(IF(INDEX($B38:$Y38,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$Y$4,0))="",B38,(B38+INDEX($B38:$Y38,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$Y$4,0)))/2),B38),"")</f>
         <v/>
       </c>
       <c r="C112" s="8">
-        <f>IF(ISNUMBER(C38),IFERROR(IF(INDEX($B38:$X38,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$X$4,0))="",C38,(C38+INDEX($B38:$X38,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$X$4,0)))/2),C38),"")</f>
+        <f>IF(ISNUMBER(C38),IFERROR(IF(INDEX($B38:$Y38,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$Y$4,0))="",C38,(C38+INDEX($B38:$Y38,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$Y$4,0)))/2),C38),"")</f>
         <v/>
       </c>
       <c r="D112" s="8">
-        <f>IF(ISNUMBER(D38),IFERROR(IF(INDEX($B38:$X38,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$X$4,0))="",D38,(D38+INDEX($B38:$X38,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$X$4,0)))/2),D38),"")</f>
+        <f>IF(ISNUMBER(D38),IFERROR(IF(INDEX($B38:$Y38,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$Y$4,0))="",D38,(D38+INDEX($B38:$Y38,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$Y$4,0)))/2),D38),"")</f>
         <v/>
       </c>
       <c r="E112" s="8">
-        <f>IF(ISNUMBER(E38),IFERROR(IF(INDEX($B38:$X38,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$X$4,0))="",E38,(E38+INDEX($B38:$X38,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$X$4,0)))/2),E38),"")</f>
+        <f>IF(ISNUMBER(E38),IFERROR(IF(INDEX($B38:$Y38,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$Y$4,0))="",E38,(E38+INDEX($B38:$Y38,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$Y$4,0)))/2),E38),"")</f>
         <v/>
       </c>
       <c r="F112" s="8">
-        <f>IF(ISNUMBER(F38),IFERROR(IF(INDEX($B38:$X38,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$X$4,0))="",F38,(F38+INDEX($B38:$X38,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$X$4,0)))/2),F38),"")</f>
+        <f>IF(ISNUMBER(F38),IFERROR(IF(INDEX($B38:$Y38,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$Y$4,0))="",F38,(F38+INDEX($B38:$Y38,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$Y$4,0)))/2),F38),"")</f>
         <v/>
       </c>
       <c r="G112" s="8">
-        <f>IF(ISNUMBER(G38),IFERROR(IF(INDEX($B38:$X38,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$X$4,0))="",G38,(G38+INDEX($B38:$X38,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$X$4,0)))/2),G38),"")</f>
+        <f>IF(ISNUMBER(G38),IFERROR(IF(INDEX($B38:$Y38,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$Y$4,0))="",G38,(G38+INDEX($B38:$Y38,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$Y$4,0)))/2),G38),"")</f>
         <v/>
       </c>
       <c r="H112" s="8">
-        <f>IF(ISNUMBER(H38),IFERROR(IF(INDEX($B38:$X38,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$X$4,0))="",H38,(H38+INDEX($B38:$X38,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$X$4,0)))/2),H38),"")</f>
+        <f>IF(ISNUMBER(H38),IFERROR(IF(INDEX($B38:$Y38,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$Y$4,0))="",H38,(H38+INDEX($B38:$Y38,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$Y$4,0)))/2),H38),"")</f>
         <v/>
       </c>
       <c r="I112" s="8">
-        <f>IF(ISNUMBER(I38),IFERROR(IF(INDEX($B38:$X38,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$X$4,0))="",I38,(I38+INDEX($B38:$X38,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$X$4,0)))/2),I38),"")</f>
+        <f>IF(ISNUMBER(I38),IFERROR(IF(INDEX($B38:$Y38,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$Y$4,0))="",I38,(I38+INDEX($B38:$Y38,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$Y$4,0)))/2),I38),"")</f>
         <v/>
       </c>
       <c r="J112" s="8">
-        <f>IF(ISNUMBER(J38),IFERROR(IF(INDEX($B38:$X38,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$X$4,0))="",J38,(J38+INDEX($B38:$X38,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$X$4,0)))/2),J38),"")</f>
+        <f>IF(ISNUMBER(J38),IFERROR(IF(INDEX($B38:$Y38,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$Y$4,0))="",J38,(J38+INDEX($B38:$Y38,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$Y$4,0)))/2),J38),"")</f>
         <v/>
       </c>
       <c r="K112" s="8">
-        <f>IF(ISNUMBER(K38),IFERROR(IF(INDEX($B38:$X38,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$X$4,0))="",K38,(K38+INDEX($B38:$X38,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$X$4,0)))/2),K38),"")</f>
+        <f>IF(ISNUMBER(K38),IFERROR(IF(INDEX($B38:$Y38,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$Y$4,0))="",K38,(K38+INDEX($B38:$Y38,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$Y$4,0)))/2),K38),"")</f>
         <v/>
       </c>
       <c r="L112" s="8">
-        <f>IF(ISNUMBER(L38),IFERROR(IF(INDEX($B38:$X38,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$X$4,0))="",L38,(L38+INDEX($B38:$X38,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$X$4,0)))/2),L38),"")</f>
+        <f>IF(ISNUMBER(L38),IFERROR(IF(INDEX($B38:$Y38,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$Y$4,0))="",L38,(L38+INDEX($B38:$Y38,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$Y$4,0)))/2),L38),"")</f>
         <v/>
       </c>
       <c r="M112" s="8">
-        <f>IF(ISNUMBER(M38),IFERROR(IF(INDEX($B38:$X38,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$X$4,0))="",M38,(M38+INDEX($B38:$X38,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$X$4,0)))/2),M38),"")</f>
+        <f>IF(ISNUMBER(M38),IFERROR(IF(INDEX($B38:$Y38,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$Y$4,0))="",M38,(M38+INDEX($B38:$Y38,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$Y$4,0)))/2),M38),"")</f>
         <v/>
       </c>
       <c r="N112" s="8">
-        <f>IF(ISNUMBER(N38),IFERROR(IF(INDEX($B38:$X38,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$X$4,0))="",N38,(N38+INDEX($B38:$X38,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$X$4,0)))/2),N38),"")</f>
+        <f>IF(ISNUMBER(N38),IFERROR(IF(INDEX($B38:$Y38,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$Y$4,0))="",N38,(N38+INDEX($B38:$Y38,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$Y$4,0)))/2),N38),"")</f>
         <v/>
       </c>
       <c r="O112" s="8">
-        <f>IF(ISNUMBER(O38),IFERROR(IF(INDEX($B38:$X38,MATCH(DATE(YEAR(O$4)-1,12,31),$B$4:$X$4,0))="",O38,(O38+INDEX($B38:$X38,MATCH(DATE(YEAR(O$4)-1,12,31),$B$4:$X$4,0)))/2),O38),"")</f>
+        <f>IF(ISNUMBER(O38),IFERROR(IF(INDEX($B38:$Y38,MATCH(DATE(YEAR(O$4)-1,12,31),$B$4:$Y$4,0))="",O38,(O38+INDEX($B38:$Y38,MATCH(DATE(YEAR(O$4)-1,12,31),$B$4:$Y$4,0)))/2),O38),"")</f>
         <v/>
       </c>
       <c r="P112" s="8">
-        <f>IF(ISNUMBER(P38),IFERROR(IF(INDEX($B38:$X38,MATCH(DATE(YEAR(P$4)-1,12,31),$B$4:$X$4,0))="",P38,(P38+INDEX($B38:$X38,MATCH(DATE(YEAR(P$4)-1,12,31),$B$4:$X$4,0)))/2),P38),"")</f>
+        <f>IF(ISNUMBER(P38),IFERROR(IF(INDEX($B38:$Y38,MATCH(DATE(YEAR(P$4)-1,12,31),$B$4:$Y$4,0))="",P38,(P38+INDEX($B38:$Y38,MATCH(DATE(YEAR(P$4)-1,12,31),$B$4:$Y$4,0)))/2),P38),"")</f>
         <v/>
       </c>
       <c r="Q112" s="8">
-        <f>IF(ISNUMBER(Q38),IFERROR(IF(INDEX($B38:$X38,MATCH(DATE(YEAR(Q$4)-1,12,31),$B$4:$X$4,0))="",Q38,(Q38+INDEX($B38:$X38,MATCH(DATE(YEAR(Q$4)-1,12,31),$B$4:$X$4,0)))/2),Q38),"")</f>
+        <f>IF(ISNUMBER(Q38),IFERROR(IF(INDEX($B38:$Y38,MATCH(DATE(YEAR(Q$4)-1,12,31),$B$4:$Y$4,0))="",Q38,(Q38+INDEX($B38:$Y38,MATCH(DATE(YEAR(Q$4)-1,12,31),$B$4:$Y$4,0)))/2),Q38),"")</f>
         <v/>
       </c>
       <c r="R112" s="8">
-        <f>IF(ISNUMBER(R38),IFERROR(IF(INDEX($B38:$X38,MATCH(DATE(YEAR(R$4)-1,12,31),$B$4:$X$4,0))="",R38,(R38+INDEX($B38:$X38,MATCH(DATE(YEAR(R$4)-1,12,31),$B$4:$X$4,0)))/2),R38),"")</f>
+        <f>IF(ISNUMBER(R38),IFERROR(IF(INDEX($B38:$Y38,MATCH(DATE(YEAR(R$4)-1,12,31),$B$4:$Y$4,0))="",R38,(R38+INDEX($B38:$Y38,MATCH(DATE(YEAR(R$4)-1,12,31),$B$4:$Y$4,0)))/2),R38),"")</f>
         <v/>
       </c>
       <c r="S112" s="8">
-        <f>IF(ISNUMBER(S38),IFERROR(IF(INDEX($B38:$X38,MATCH(DATE(YEAR(S$4)-1,12,31),$B$4:$X$4,0))="",S38,(S38+INDEX($B38:$X38,MATCH(DATE(YEAR(S$4)-1,12,31),$B$4:$X$4,0)))/2),S38),"")</f>
+        <f>IF(ISNUMBER(S38),IFERROR(IF(INDEX($B38:$Y38,MATCH(DATE(YEAR(S$4)-1,12,31),$B$4:$Y$4,0))="",S38,(S38+INDEX($B38:$Y38,MATCH(DATE(YEAR(S$4)-1,12,31),$B$4:$Y$4,0)))/2),S38),"")</f>
         <v/>
       </c>
       <c r="T112" s="8">
-        <f>IF(ISNUMBER(T38),IFERROR(IF(INDEX($B38:$X38,MATCH(DATE(YEAR(T$4)-1,12,31),$B$4:$X$4,0))="",T38,(T38+INDEX($B38:$X38,MATCH(DATE(YEAR(T$4)-1,12,31),$B$4:$X$4,0)))/2),T38),"")</f>
+        <f>IF(ISNUMBER(T38),IFERROR(IF(INDEX($B38:$Y38,MATCH(DATE(YEAR(T$4)-1,12,31),$B$4:$Y$4,0))="",T38,(T38+INDEX($B38:$Y38,MATCH(DATE(YEAR(T$4)-1,12,31),$B$4:$Y$4,0)))/2),T38),"")</f>
         <v/>
       </c>
       <c r="U112" s="8">
-        <f>IF(ISNUMBER(U38),IFERROR(IF(INDEX($B38:$X38,MATCH(DATE(YEAR(U$4)-1,12,31),$B$4:$X$4,0))="",U38,(U38+INDEX($B38:$X38,MATCH(DATE(YEAR(U$4)-1,12,31),$B$4:$X$4,0)))/2),U38),"")</f>
+        <f>IF(ISNUMBER(U38),IFERROR(IF(INDEX($B38:$Y38,MATCH(DATE(YEAR(U$4)-1,12,31),$B$4:$Y$4,0))="",U38,(U38+INDEX($B38:$Y38,MATCH(DATE(YEAR(U$4)-1,12,31),$B$4:$Y$4,0)))/2),U38),"")</f>
         <v/>
       </c>
       <c r="V112" s="8">
-        <f>IF(ISNUMBER(V38),IFERROR(IF(INDEX($B38:$X38,MATCH(DATE(YEAR(V$4)-1,12,31),$B$4:$X$4,0))="",V38,(V38+INDEX($B38:$X38,MATCH(DATE(YEAR(V$4)-1,12,31),$B$4:$X$4,0)))/2),V38),"")</f>
+        <f>IF(ISNUMBER(V38),IFERROR(IF(INDEX($B38:$Y38,MATCH(DATE(YEAR(V$4)-1,12,31),$B$4:$Y$4,0))="",V38,(V38+INDEX($B38:$Y38,MATCH(DATE(YEAR(V$4)-1,12,31),$B$4:$Y$4,0)))/2),V38),"")</f>
         <v/>
       </c>
       <c r="W112" s="8">
-        <f>IF(ISNUMBER(W38),IFERROR(IF(INDEX($B38:$X38,MATCH(DATE(YEAR(W$4)-1,12,31),$B$4:$X$4,0))="",W38,(W38+INDEX($B38:$X38,MATCH(DATE(YEAR(W$4)-1,12,31),$B$4:$X$4,0)))/2),W38),"")</f>
+        <f>IF(ISNUMBER(W38),IFERROR(IF(INDEX($B38:$Y38,MATCH(DATE(YEAR(W$4)-1,12,31),$B$4:$Y$4,0))="",W38,(W38+INDEX($B38:$Y38,MATCH(DATE(YEAR(W$4)-1,12,31),$B$4:$Y$4,0)))/2),W38),"")</f>
         <v/>
       </c>
       <c r="X112" s="8">
-        <f>IF(ISNUMBER(X38),IFERROR(IF(INDEX($B38:$X38,MATCH(DATE(YEAR(X$4)-1,12,31),$B$4:$X$4,0))="",X38,(X38+INDEX($B38:$X38,MATCH(DATE(YEAR(X$4)-1,12,31),$B$4:$X$4,0)))/2),X38),"")</f>
+        <f>IF(ISNUMBER(X38),IFERROR(IF(INDEX($B38:$Y38,MATCH(DATE(YEAR(X$4)-1,12,31),$B$4:$Y$4,0))="",X38,(X38+INDEX($B38:$Y38,MATCH(DATE(YEAR(X$4)-1,12,31),$B$4:$Y$4,0)))/2),X38),"")</f>
+        <v/>
+      </c>
+      <c r="Y112" s="8">
+        <f>IF(ISNUMBER(Y38),IFERROR(IF(INDEX($B38:$Y38,MATCH(DATE(YEAR(Y$4)-1,12,31),$B$4:$Y$4,0))="",Y38,(Y38+INDEX($B38:$Y38,MATCH(DATE(YEAR(Y$4)-1,12,31),$B$4:$Y$4,0)))/2),Y38),"")</f>
         <v/>
       </c>
     </row>
@@ -33487,6 +33767,10 @@
         <f>IF(AND(ISNUMBER(X73),ISNUMBER(X71)),IFERROR((X73)/(X71),""),"")</f>
         <v/>
       </c>
+      <c r="Y115" s="16">
+        <f>IF(AND(ISNUMBER(Y73),ISNUMBER(Y71)),IFERROR((Y73)/(Y71),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -33586,6 +33870,10 @@
         <f>IF(AND(ISNUMBER(X72),ISNUMBER(X71)),IFERROR((X72)/(X71),""),"")</f>
         <v/>
       </c>
+      <c r="Y116" s="16">
+        <f>IF(AND(ISNUMBER(Y72),ISNUMBER(Y71)),IFERROR((Y72)/(Y71),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -33685,6 +33973,10 @@
         <f>IF(AND(ISNUMBER(X79),ISNUMBER(X71)),IFERROR((X79)/(X71),""),"")</f>
         <v/>
       </c>
+      <c r="Y117" s="16">
+        <f>IF(AND(ISNUMBER(Y79),ISNUMBER(Y71)),IFERROR((Y79)/(Y71),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -33784,6 +34076,10 @@
         <f>IF(AND(ISNUMBER(X80),ISNUMBER(X71)),IFERROR((X80)/(X71),""),"")</f>
         <v/>
       </c>
+      <c r="Y118" s="16">
+        <f>IF(AND(ISNUMBER(Y80),ISNUMBER(Y71)),IFERROR((Y80)/(Y71),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -33883,6 +34179,10 @@
         <f>IF(AND(ISNUMBER(X94),ISNUMBER(X71)),IFERROR((X94)/(X71),""),"")</f>
         <v/>
       </c>
+      <c r="Y119" s="16">
+        <f>IF(AND(ISNUMBER(Y94),ISNUMBER(Y71)),IFERROR((Y94)/(Y71),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -33982,6 +34282,10 @@
         <f>IF(AND(ISNUMBER(X94),ISNUMBER(X107),ISNUMBER(X108)),IFERROR((X94*X107)/(X108),""),"")</f>
         <v/>
       </c>
+      <c r="Y120" s="16">
+        <f>IF(AND(ISNUMBER(Y94),ISNUMBER(Y107),ISNUMBER(Y108)),IFERROR((Y94*Y107)/(Y108),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -34081,6 +34385,10 @@
         <f>IF(AND(ISNUMBER(X94),ISNUMBER(X107),ISNUMBER(X109)),IFERROR((X94*X107)/(X109),""),"")</f>
         <v/>
       </c>
+      <c r="Y121" s="16">
+        <f>IF(AND(ISNUMBER(Y94),ISNUMBER(Y107),ISNUMBER(Y109)),IFERROR((Y94*Y107)/(Y109),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="14" t="inlineStr">
@@ -34187,6 +34495,10 @@
         <f>IF(AND(ISNUMBER(X108),ISNUMBER(X71),ISNUMBER(X107)),IFERROR(X71*X107/X108,""),"")</f>
         <v/>
       </c>
+      <c r="Y124" s="17">
+        <f>IF(AND(ISNUMBER(Y108),ISNUMBER(Y71),ISNUMBER(Y107)),IFERROR(Y71*Y107/Y108,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -34286,6 +34598,10 @@
         <f>IF(AND(ISNUMBER(X108),ISNUMBER(X109)),IFERROR((X108)/(X109),""),"")</f>
         <v/>
       </c>
+      <c r="Y125" s="17">
+        <f>IF(AND(ISNUMBER(Y108),ISNUMBER(Y109)),IFERROR((Y108)/(Y109),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -34385,6 +34701,10 @@
         <f>IF(AND(ISNUMBER(X119),ISNUMBER(X124),ISNUMBER(X125)),IFERROR(X119*X124*X125,""),"")</f>
         <v/>
       </c>
+      <c r="Y126" s="16">
+        <f>IF(AND(ISNUMBER(Y119),ISNUMBER(Y124),ISNUMBER(Y125)),IFERROR(Y119*Y124*Y125,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
@@ -34491,6 +34811,10 @@
         <f>IF(AND(ISNUMBER(X22),ISNUMBER(X49)),IFERROR((X22)/(X49),""),"")</f>
         <v/>
       </c>
+      <c r="Y129" s="17">
+        <f>IF(AND(ISNUMBER(Y22),ISNUMBER(Y49)),IFERROR((Y22)/(Y49),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -34590,6 +34914,10 @@
         <f>IF(AND(ISNUMBER(X22),ISNUMBER(X17),ISNUMBER(X49)),IFERROR((X22-X17)/X49,""),"")</f>
         <v/>
       </c>
+      <c r="Y130" s="17">
+        <f>IF(AND(ISNUMBER(Y22),ISNUMBER(Y17),ISNUMBER(Y49)),IFERROR((Y22-Y17)/Y49,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -34689,6 +35017,10 @@
         <f>IF(AND(ISNUMBER(X12),ISNUMBER(X49)),IFERROR((X12)/(X49),""),"")</f>
         <v/>
       </c>
+      <c r="Y131" s="17">
+        <f>IF(AND(ISNUMBER(Y12),ISNUMBER(Y49)),IFERROR((Y12)/(Y49),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -34788,6 +35120,10 @@
         <f>IF(AND(ISNUMBER(X22),ISNUMBER(X49)),IFERROR((X22-X49)/1000,""),"")</f>
         <v/>
       </c>
+      <c r="Y132" s="8">
+        <f>IF(AND(ISNUMBER(Y22),ISNUMBER(Y49)),IFERROR((Y22-Y49)/1000,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
@@ -34894,6 +35230,10 @@
         <f>IF(AND(ISNUMBER(X57),ISNUMBER(X68)),IFERROR((X57)/(X68),""),"")</f>
         <v/>
       </c>
+      <c r="Y135" s="17">
+        <f>IF(AND(ISNUMBER(Y57),ISNUMBER(Y68)),IFERROR((Y57)/(Y68),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -34993,6 +35333,10 @@
         <f>IF(AND(ISNUMBER(X57),ISNUMBER(X36)),IFERROR((X57)/(X36),""),"")</f>
         <v/>
       </c>
+      <c r="Y136" s="16">
+        <f>IF(AND(ISNUMBER(Y57),ISNUMBER(Y36)),IFERROR((Y57)/(Y36),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -35092,6 +35436,10 @@
         <f>IF(AND(ISNUMBER(X90),ISNUMBER(X81)),IFERROR((X90+ABS(X81))/ABS(X81),""),"")</f>
         <v/>
       </c>
+      <c r="Y137" s="17">
+        <f>IF(AND(ISNUMBER(Y90),ISNUMBER(Y81)),IFERROR((Y90+ABS(Y81))/ABS(Y81),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="14" t="inlineStr">
@@ -35198,6 +35546,10 @@
         <f>IF(AND(ISNUMBER(X110),ISNUMBER(X72),ISNUMBER(X107)),IFERROR(X72*X107/X110,""),"")</f>
         <v/>
       </c>
+      <c r="Y140" s="17">
+        <f>IF(AND(ISNUMBER(Y110),ISNUMBER(Y72),ISNUMBER(Y107)),IFERROR(Y72*Y107/Y110,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -35297,6 +35649,10 @@
         <f>IF(AND(ISNUMBER(X110),ISNUMBER(X72),ISNUMBER(X107)),IFERROR(X110/(X72*X107)*365,""),"")</f>
         <v/>
       </c>
+      <c r="Y141" s="18">
+        <f>IF(AND(ISNUMBER(Y110),ISNUMBER(Y72),ISNUMBER(Y107)),IFERROR(Y110/(Y72*Y107)*365,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -35396,6 +35752,10 @@
         <f>IF(AND(ISNUMBER(X111),ISNUMBER(X71),ISNUMBER(X107)),IFERROR(X71*X107/X111,""),"")</f>
         <v/>
       </c>
+      <c r="Y142" s="17">
+        <f>IF(AND(ISNUMBER(Y111),ISNUMBER(Y71),ISNUMBER(Y107)),IFERROR(Y71*Y107/Y111,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -35495,6 +35855,10 @@
         <f>IF(AND(ISNUMBER(X111),ISNUMBER(X71),ISNUMBER(X107)),IFERROR(X111/(X71*X107)*365,""),"")</f>
         <v/>
       </c>
+      <c r="Y143" s="18">
+        <f>IF(AND(ISNUMBER(Y111),ISNUMBER(Y71),ISNUMBER(Y107)),IFERROR(Y111/(Y71*Y107)*365,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -35594,6 +35958,10 @@
         <f>IF(AND(ISNUMBER(X112),ISNUMBER(X72),ISNUMBER(X107)),IFERROR(X72*X107/X112,""),"")</f>
         <v/>
       </c>
+      <c r="Y144" s="17">
+        <f>IF(AND(ISNUMBER(Y112),ISNUMBER(Y72),ISNUMBER(Y107)),IFERROR(Y72*Y107/Y112,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -35693,6 +36061,10 @@
         <f>IF(AND(ISNUMBER(X112),ISNUMBER(X72),ISNUMBER(X107)),IFERROR(X112/(X72*X107)*365,""),"")</f>
         <v/>
       </c>
+      <c r="Y145" s="18">
+        <f>IF(AND(ISNUMBER(Y112),ISNUMBER(Y72),ISNUMBER(Y107)),IFERROR(Y112/(Y72*Y107)*365,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -35792,6 +36164,10 @@
         <f>IF(AND(ISNUMBER(X141),ISNUMBER(X143),ISNUMBER(X145)),IFERROR(X141+X143-X145,""),"")</f>
         <v/>
       </c>
+      <c r="Y146" s="18">
+        <f>IF(AND(ISNUMBER(Y141),ISNUMBER(Y143),ISNUMBER(Y145)),IFERROR(Y141+Y143-Y145,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
@@ -35807,95 +36183,99 @@
         </is>
       </c>
       <c r="B149" s="16">
-        <f>IF(ISNUMBER(B71),IFERROR(IF(INDEX($B71:$X71,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$X$4,0))&gt;0,B71/INDEX($B71:$X71,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(B71),IFERROR(IF(INDEX($B71:$Y71,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$Y$4,0))&gt;0,B71/INDEX($B71:$Y71,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="C149" s="16">
-        <f>IF(ISNUMBER(C71),IFERROR(IF(INDEX($B71:$X71,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$X$4,0))&gt;0,C71/INDEX($B71:$X71,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(C71),IFERROR(IF(INDEX($B71:$Y71,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$Y$4,0))&gt;0,C71/INDEX($B71:$Y71,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="D149" s="16">
-        <f>IF(ISNUMBER(D71),IFERROR(IF(INDEX($B71:$X71,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$X$4,0))&gt;0,D71/INDEX($B71:$X71,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(D71),IFERROR(IF(INDEX($B71:$Y71,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$Y$4,0))&gt;0,D71/INDEX($B71:$Y71,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="E149" s="16">
-        <f>IF(ISNUMBER(E71),IFERROR(IF(INDEX($B71:$X71,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$X$4,0))&gt;0,E71/INDEX($B71:$X71,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(E71),IFERROR(IF(INDEX($B71:$Y71,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$Y$4,0))&gt;0,E71/INDEX($B71:$Y71,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="F149" s="16">
-        <f>IF(ISNUMBER(F71),IFERROR(IF(INDEX($B71:$X71,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$X$4,0))&gt;0,F71/INDEX($B71:$X71,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(F71),IFERROR(IF(INDEX($B71:$Y71,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$Y$4,0))&gt;0,F71/INDEX($B71:$Y71,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="G149" s="16">
-        <f>IF(ISNUMBER(G71),IFERROR(IF(INDEX($B71:$X71,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$X$4,0))&gt;0,G71/INDEX($B71:$X71,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(G71),IFERROR(IF(INDEX($B71:$Y71,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$Y$4,0))&gt;0,G71/INDEX($B71:$Y71,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="H149" s="16">
-        <f>IF(ISNUMBER(H71),IFERROR(IF(INDEX($B71:$X71,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$X$4,0))&gt;0,H71/INDEX($B71:$X71,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(H71),IFERROR(IF(INDEX($B71:$Y71,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$Y$4,0))&gt;0,H71/INDEX($B71:$Y71,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="I149" s="16">
-        <f>IF(ISNUMBER(I71),IFERROR(IF(INDEX($B71:$X71,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$X$4,0))&gt;0,I71/INDEX($B71:$X71,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(I71),IFERROR(IF(INDEX($B71:$Y71,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$Y$4,0))&gt;0,I71/INDEX($B71:$Y71,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="J149" s="16">
-        <f>IF(ISNUMBER(J71),IFERROR(IF(INDEX($B71:$X71,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$X$4,0))&gt;0,J71/INDEX($B71:$X71,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(J71),IFERROR(IF(INDEX($B71:$Y71,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$Y$4,0))&gt;0,J71/INDEX($B71:$Y71,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="K149" s="16">
-        <f>IF(ISNUMBER(K71),IFERROR(IF(INDEX($B71:$X71,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$X$4,0))&gt;0,K71/INDEX($B71:$X71,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(K71),IFERROR(IF(INDEX($B71:$Y71,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$Y$4,0))&gt;0,K71/INDEX($B71:$Y71,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="L149" s="16">
-        <f>IF(ISNUMBER(L71),IFERROR(IF(INDEX($B71:$X71,MATCH(DATE(YEAR(L$4)-1,MONTH(L$4),DAY(L$4)),$B$4:$X$4,0))&gt;0,L71/INDEX($B71:$X71,MATCH(DATE(YEAR(L$4)-1,MONTH(L$4),DAY(L$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(L71),IFERROR(IF(INDEX($B71:$Y71,MATCH(DATE(YEAR(L$4)-1,MONTH(L$4),DAY(L$4)),$B$4:$Y$4,0))&gt;0,L71/INDEX($B71:$Y71,MATCH(DATE(YEAR(L$4)-1,MONTH(L$4),DAY(L$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="M149" s="16">
-        <f>IF(ISNUMBER(M71),IFERROR(IF(INDEX($B71:$X71,MATCH(DATE(YEAR(M$4)-1,MONTH(M$4),DAY(M$4)),$B$4:$X$4,0))&gt;0,M71/INDEX($B71:$X71,MATCH(DATE(YEAR(M$4)-1,MONTH(M$4),DAY(M$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(M71),IFERROR(IF(INDEX($B71:$Y71,MATCH(DATE(YEAR(M$4)-1,MONTH(M$4),DAY(M$4)),$B$4:$Y$4,0))&gt;0,M71/INDEX($B71:$Y71,MATCH(DATE(YEAR(M$4)-1,MONTH(M$4),DAY(M$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="N149" s="16">
-        <f>IF(ISNUMBER(N71),IFERROR(IF(INDEX($B71:$X71,MATCH(DATE(YEAR(N$4)-1,MONTH(N$4),DAY(N$4)),$B$4:$X$4,0))&gt;0,N71/INDEX($B71:$X71,MATCH(DATE(YEAR(N$4)-1,MONTH(N$4),DAY(N$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(N71),IFERROR(IF(INDEX($B71:$Y71,MATCH(DATE(YEAR(N$4)-1,MONTH(N$4),DAY(N$4)),$B$4:$Y$4,0))&gt;0,N71/INDEX($B71:$Y71,MATCH(DATE(YEAR(N$4)-1,MONTH(N$4),DAY(N$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="O149" s="16">
-        <f>IF(ISNUMBER(O71),IFERROR(IF(INDEX($B71:$X71,MATCH(DATE(YEAR(O$4)-1,MONTH(O$4),DAY(O$4)),$B$4:$X$4,0))&gt;0,O71/INDEX($B71:$X71,MATCH(DATE(YEAR(O$4)-1,MONTH(O$4),DAY(O$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(O71),IFERROR(IF(INDEX($B71:$Y71,MATCH(DATE(YEAR(O$4)-1,MONTH(O$4),DAY(O$4)),$B$4:$Y$4,0))&gt;0,O71/INDEX($B71:$Y71,MATCH(DATE(YEAR(O$4)-1,MONTH(O$4),DAY(O$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="P149" s="16">
-        <f>IF(ISNUMBER(P71),IFERROR(IF(INDEX($B71:$X71,MATCH(DATE(YEAR(P$4)-1,MONTH(P$4),DAY(P$4)),$B$4:$X$4,0))&gt;0,P71/INDEX($B71:$X71,MATCH(DATE(YEAR(P$4)-1,MONTH(P$4),DAY(P$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(P71),IFERROR(IF(INDEX($B71:$Y71,MATCH(DATE(YEAR(P$4)-1,MONTH(P$4),DAY(P$4)),$B$4:$Y$4,0))&gt;0,P71/INDEX($B71:$Y71,MATCH(DATE(YEAR(P$4)-1,MONTH(P$4),DAY(P$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="Q149" s="16">
-        <f>IF(ISNUMBER(Q71),IFERROR(IF(INDEX($B71:$X71,MATCH(DATE(YEAR(Q$4)-1,MONTH(Q$4),DAY(Q$4)),$B$4:$X$4,0))&gt;0,Q71/INDEX($B71:$X71,MATCH(DATE(YEAR(Q$4)-1,MONTH(Q$4),DAY(Q$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(Q71),IFERROR(IF(INDEX($B71:$Y71,MATCH(DATE(YEAR(Q$4)-1,MONTH(Q$4),DAY(Q$4)),$B$4:$Y$4,0))&gt;0,Q71/INDEX($B71:$Y71,MATCH(DATE(YEAR(Q$4)-1,MONTH(Q$4),DAY(Q$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="R149" s="16">
-        <f>IF(ISNUMBER(R71),IFERROR(IF(INDEX($B71:$X71,MATCH(DATE(YEAR(R$4)-1,MONTH(R$4),DAY(R$4)),$B$4:$X$4,0))&gt;0,R71/INDEX($B71:$X71,MATCH(DATE(YEAR(R$4)-1,MONTH(R$4),DAY(R$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(R71),IFERROR(IF(INDEX($B71:$Y71,MATCH(DATE(YEAR(R$4)-1,MONTH(R$4),DAY(R$4)),$B$4:$Y$4,0))&gt;0,R71/INDEX($B71:$Y71,MATCH(DATE(YEAR(R$4)-1,MONTH(R$4),DAY(R$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="S149" s="16">
-        <f>IF(ISNUMBER(S71),IFERROR(IF(INDEX($B71:$X71,MATCH(DATE(YEAR(S$4)-1,MONTH(S$4),DAY(S$4)),$B$4:$X$4,0))&gt;0,S71/INDEX($B71:$X71,MATCH(DATE(YEAR(S$4)-1,MONTH(S$4),DAY(S$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(S71),IFERROR(IF(INDEX($B71:$Y71,MATCH(DATE(YEAR(S$4)-1,MONTH(S$4),DAY(S$4)),$B$4:$Y$4,0))&gt;0,S71/INDEX($B71:$Y71,MATCH(DATE(YEAR(S$4)-1,MONTH(S$4),DAY(S$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="T149" s="16">
-        <f>IF(ISNUMBER(T71),IFERROR(IF(INDEX($B71:$X71,MATCH(DATE(YEAR(T$4)-1,MONTH(T$4),DAY(T$4)),$B$4:$X$4,0))&gt;0,T71/INDEX($B71:$X71,MATCH(DATE(YEAR(T$4)-1,MONTH(T$4),DAY(T$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(T71),IFERROR(IF(INDEX($B71:$Y71,MATCH(DATE(YEAR(T$4)-1,MONTH(T$4),DAY(T$4)),$B$4:$Y$4,0))&gt;0,T71/INDEX($B71:$Y71,MATCH(DATE(YEAR(T$4)-1,MONTH(T$4),DAY(T$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="U149" s="16">
-        <f>IF(ISNUMBER(U71),IFERROR(IF(INDEX($B71:$X71,MATCH(DATE(YEAR(U$4)-1,MONTH(U$4),DAY(U$4)),$B$4:$X$4,0))&gt;0,U71/INDEX($B71:$X71,MATCH(DATE(YEAR(U$4)-1,MONTH(U$4),DAY(U$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(U71),IFERROR(IF(INDEX($B71:$Y71,MATCH(DATE(YEAR(U$4)-1,MONTH(U$4),DAY(U$4)),$B$4:$Y$4,0))&gt;0,U71/INDEX($B71:$Y71,MATCH(DATE(YEAR(U$4)-1,MONTH(U$4),DAY(U$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="V149" s="16">
-        <f>IF(ISNUMBER(V71),IFERROR(IF(INDEX($B71:$X71,MATCH(DATE(YEAR(V$4)-1,MONTH(V$4),DAY(V$4)),$B$4:$X$4,0))&gt;0,V71/INDEX($B71:$X71,MATCH(DATE(YEAR(V$4)-1,MONTH(V$4),DAY(V$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(V71),IFERROR(IF(INDEX($B71:$Y71,MATCH(DATE(YEAR(V$4)-1,MONTH(V$4),DAY(V$4)),$B$4:$Y$4,0))&gt;0,V71/INDEX($B71:$Y71,MATCH(DATE(YEAR(V$4)-1,MONTH(V$4),DAY(V$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="W149" s="16">
-        <f>IF(ISNUMBER(W71),IFERROR(IF(INDEX($B71:$X71,MATCH(DATE(YEAR(W$4)-1,MONTH(W$4),DAY(W$4)),$B$4:$X$4,0))&gt;0,W71/INDEX($B71:$X71,MATCH(DATE(YEAR(W$4)-1,MONTH(W$4),DAY(W$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(W71),IFERROR(IF(INDEX($B71:$Y71,MATCH(DATE(YEAR(W$4)-1,MONTH(W$4),DAY(W$4)),$B$4:$Y$4,0))&gt;0,W71/INDEX($B71:$Y71,MATCH(DATE(YEAR(W$4)-1,MONTH(W$4),DAY(W$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="X149" s="16">
-        <f>IF(ISNUMBER(X71),IFERROR(IF(INDEX($B71:$X71,MATCH(DATE(YEAR(X$4)-1,MONTH(X$4),DAY(X$4)),$B$4:$X$4,0))&gt;0,X71/INDEX($B71:$X71,MATCH(DATE(YEAR(X$4)-1,MONTH(X$4),DAY(X$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(X71),IFERROR(IF(INDEX($B71:$Y71,MATCH(DATE(YEAR(X$4)-1,MONTH(X$4),DAY(X$4)),$B$4:$Y$4,0))&gt;0,X71/INDEX($B71:$Y71,MATCH(DATE(YEAR(X$4)-1,MONTH(X$4),DAY(X$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
+        <v/>
+      </c>
+      <c r="Y149" s="16">
+        <f>IF(ISNUMBER(Y71),IFERROR(IF(INDEX($B71:$Y71,MATCH(DATE(YEAR(Y$4)-1,MONTH(Y$4),DAY(Y$4)),$B$4:$Y$4,0))&gt;0,Y71/INDEX($B71:$Y71,MATCH(DATE(YEAR(Y$4)-1,MONTH(Y$4),DAY(Y$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
     </row>
@@ -35906,95 +36286,99 @@
         </is>
       </c>
       <c r="B150" s="16">
-        <f>IF(ISNUMBER(B73),IFERROR(IF(INDEX($B73:$X73,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$X$4,0))&gt;0,B73/INDEX($B73:$X73,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(B73),IFERROR(IF(INDEX($B73:$Y73,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$Y$4,0))&gt;0,B73/INDEX($B73:$Y73,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="C150" s="16">
-        <f>IF(ISNUMBER(C73),IFERROR(IF(INDEX($B73:$X73,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$X$4,0))&gt;0,C73/INDEX($B73:$X73,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(C73),IFERROR(IF(INDEX($B73:$Y73,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$Y$4,0))&gt;0,C73/INDEX($B73:$Y73,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="D150" s="16">
-        <f>IF(ISNUMBER(D73),IFERROR(IF(INDEX($B73:$X73,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$X$4,0))&gt;0,D73/INDEX($B73:$X73,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(D73),IFERROR(IF(INDEX($B73:$Y73,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$Y$4,0))&gt;0,D73/INDEX($B73:$Y73,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="E150" s="16">
-        <f>IF(ISNUMBER(E73),IFERROR(IF(INDEX($B73:$X73,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$X$4,0))&gt;0,E73/INDEX($B73:$X73,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(E73),IFERROR(IF(INDEX($B73:$Y73,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$Y$4,0))&gt;0,E73/INDEX($B73:$Y73,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="F150" s="16">
-        <f>IF(ISNUMBER(F73),IFERROR(IF(INDEX($B73:$X73,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$X$4,0))&gt;0,F73/INDEX($B73:$X73,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(F73),IFERROR(IF(INDEX($B73:$Y73,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$Y$4,0))&gt;0,F73/INDEX($B73:$Y73,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="G150" s="16">
-        <f>IF(ISNUMBER(G73),IFERROR(IF(INDEX($B73:$X73,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$X$4,0))&gt;0,G73/INDEX($B73:$X73,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(G73),IFERROR(IF(INDEX($B73:$Y73,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$Y$4,0))&gt;0,G73/INDEX($B73:$Y73,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="H150" s="16">
-        <f>IF(ISNUMBER(H73),IFERROR(IF(INDEX($B73:$X73,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$X$4,0))&gt;0,H73/INDEX($B73:$X73,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(H73),IFERROR(IF(INDEX($B73:$Y73,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$Y$4,0))&gt;0,H73/INDEX($B73:$Y73,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="I150" s="16">
-        <f>IF(ISNUMBER(I73),IFERROR(IF(INDEX($B73:$X73,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$X$4,0))&gt;0,I73/INDEX($B73:$X73,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(I73),IFERROR(IF(INDEX($B73:$Y73,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$Y$4,0))&gt;0,I73/INDEX($B73:$Y73,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="J150" s="16">
-        <f>IF(ISNUMBER(J73),IFERROR(IF(INDEX($B73:$X73,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$X$4,0))&gt;0,J73/INDEX($B73:$X73,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(J73),IFERROR(IF(INDEX($B73:$Y73,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$Y$4,0))&gt;0,J73/INDEX($B73:$Y73,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="K150" s="16">
-        <f>IF(ISNUMBER(K73),IFERROR(IF(INDEX($B73:$X73,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$X$4,0))&gt;0,K73/INDEX($B73:$X73,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(K73),IFERROR(IF(INDEX($B73:$Y73,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$Y$4,0))&gt;0,K73/INDEX($B73:$Y73,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="L150" s="16">
-        <f>IF(ISNUMBER(L73),IFERROR(IF(INDEX($B73:$X73,MATCH(DATE(YEAR(L$4)-1,MONTH(L$4),DAY(L$4)),$B$4:$X$4,0))&gt;0,L73/INDEX($B73:$X73,MATCH(DATE(YEAR(L$4)-1,MONTH(L$4),DAY(L$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(L73),IFERROR(IF(INDEX($B73:$Y73,MATCH(DATE(YEAR(L$4)-1,MONTH(L$4),DAY(L$4)),$B$4:$Y$4,0))&gt;0,L73/INDEX($B73:$Y73,MATCH(DATE(YEAR(L$4)-1,MONTH(L$4),DAY(L$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="M150" s="16">
-        <f>IF(ISNUMBER(M73),IFERROR(IF(INDEX($B73:$X73,MATCH(DATE(YEAR(M$4)-1,MONTH(M$4),DAY(M$4)),$B$4:$X$4,0))&gt;0,M73/INDEX($B73:$X73,MATCH(DATE(YEAR(M$4)-1,MONTH(M$4),DAY(M$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(M73),IFERROR(IF(INDEX($B73:$Y73,MATCH(DATE(YEAR(M$4)-1,MONTH(M$4),DAY(M$4)),$B$4:$Y$4,0))&gt;0,M73/INDEX($B73:$Y73,MATCH(DATE(YEAR(M$4)-1,MONTH(M$4),DAY(M$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="N150" s="16">
-        <f>IF(ISNUMBER(N73),IFERROR(IF(INDEX($B73:$X73,MATCH(DATE(YEAR(N$4)-1,MONTH(N$4),DAY(N$4)),$B$4:$X$4,0))&gt;0,N73/INDEX($B73:$X73,MATCH(DATE(YEAR(N$4)-1,MONTH(N$4),DAY(N$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(N73),IFERROR(IF(INDEX($B73:$Y73,MATCH(DATE(YEAR(N$4)-1,MONTH(N$4),DAY(N$4)),$B$4:$Y$4,0))&gt;0,N73/INDEX($B73:$Y73,MATCH(DATE(YEAR(N$4)-1,MONTH(N$4),DAY(N$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="O150" s="16">
-        <f>IF(ISNUMBER(O73),IFERROR(IF(INDEX($B73:$X73,MATCH(DATE(YEAR(O$4)-1,MONTH(O$4),DAY(O$4)),$B$4:$X$4,0))&gt;0,O73/INDEX($B73:$X73,MATCH(DATE(YEAR(O$4)-1,MONTH(O$4),DAY(O$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(O73),IFERROR(IF(INDEX($B73:$Y73,MATCH(DATE(YEAR(O$4)-1,MONTH(O$4),DAY(O$4)),$B$4:$Y$4,0))&gt;0,O73/INDEX($B73:$Y73,MATCH(DATE(YEAR(O$4)-1,MONTH(O$4),DAY(O$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="P150" s="16">
-        <f>IF(ISNUMBER(P73),IFERROR(IF(INDEX($B73:$X73,MATCH(DATE(YEAR(P$4)-1,MONTH(P$4),DAY(P$4)),$B$4:$X$4,0))&gt;0,P73/INDEX($B73:$X73,MATCH(DATE(YEAR(P$4)-1,MONTH(P$4),DAY(P$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(P73),IFERROR(IF(INDEX($B73:$Y73,MATCH(DATE(YEAR(P$4)-1,MONTH(P$4),DAY(P$4)),$B$4:$Y$4,0))&gt;0,P73/INDEX($B73:$Y73,MATCH(DATE(YEAR(P$4)-1,MONTH(P$4),DAY(P$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="Q150" s="16">
-        <f>IF(ISNUMBER(Q73),IFERROR(IF(INDEX($B73:$X73,MATCH(DATE(YEAR(Q$4)-1,MONTH(Q$4),DAY(Q$4)),$B$4:$X$4,0))&gt;0,Q73/INDEX($B73:$X73,MATCH(DATE(YEAR(Q$4)-1,MONTH(Q$4),DAY(Q$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(Q73),IFERROR(IF(INDEX($B73:$Y73,MATCH(DATE(YEAR(Q$4)-1,MONTH(Q$4),DAY(Q$4)),$B$4:$Y$4,0))&gt;0,Q73/INDEX($B73:$Y73,MATCH(DATE(YEAR(Q$4)-1,MONTH(Q$4),DAY(Q$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="R150" s="16">
-        <f>IF(ISNUMBER(R73),IFERROR(IF(INDEX($B73:$X73,MATCH(DATE(YEAR(R$4)-1,MONTH(R$4),DAY(R$4)),$B$4:$X$4,0))&gt;0,R73/INDEX($B73:$X73,MATCH(DATE(YEAR(R$4)-1,MONTH(R$4),DAY(R$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(R73),IFERROR(IF(INDEX($B73:$Y73,MATCH(DATE(YEAR(R$4)-1,MONTH(R$4),DAY(R$4)),$B$4:$Y$4,0))&gt;0,R73/INDEX($B73:$Y73,MATCH(DATE(YEAR(R$4)-1,MONTH(R$4),DAY(R$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="S150" s="16">
-        <f>IF(ISNUMBER(S73),IFERROR(IF(INDEX($B73:$X73,MATCH(DATE(YEAR(S$4)-1,MONTH(S$4),DAY(S$4)),$B$4:$X$4,0))&gt;0,S73/INDEX($B73:$X73,MATCH(DATE(YEAR(S$4)-1,MONTH(S$4),DAY(S$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(S73),IFERROR(IF(INDEX($B73:$Y73,MATCH(DATE(YEAR(S$4)-1,MONTH(S$4),DAY(S$4)),$B$4:$Y$4,0))&gt;0,S73/INDEX($B73:$Y73,MATCH(DATE(YEAR(S$4)-1,MONTH(S$4),DAY(S$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="T150" s="16">
-        <f>IF(ISNUMBER(T73),IFERROR(IF(INDEX($B73:$X73,MATCH(DATE(YEAR(T$4)-1,MONTH(T$4),DAY(T$4)),$B$4:$X$4,0))&gt;0,T73/INDEX($B73:$X73,MATCH(DATE(YEAR(T$4)-1,MONTH(T$4),DAY(T$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(T73),IFERROR(IF(INDEX($B73:$Y73,MATCH(DATE(YEAR(T$4)-1,MONTH(T$4),DAY(T$4)),$B$4:$Y$4,0))&gt;0,T73/INDEX($B73:$Y73,MATCH(DATE(YEAR(T$4)-1,MONTH(T$4),DAY(T$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="U150" s="16">
-        <f>IF(ISNUMBER(U73),IFERROR(IF(INDEX($B73:$X73,MATCH(DATE(YEAR(U$4)-1,MONTH(U$4),DAY(U$4)),$B$4:$X$4,0))&gt;0,U73/INDEX($B73:$X73,MATCH(DATE(YEAR(U$4)-1,MONTH(U$4),DAY(U$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(U73),IFERROR(IF(INDEX($B73:$Y73,MATCH(DATE(YEAR(U$4)-1,MONTH(U$4),DAY(U$4)),$B$4:$Y$4,0))&gt;0,U73/INDEX($B73:$Y73,MATCH(DATE(YEAR(U$4)-1,MONTH(U$4),DAY(U$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="V150" s="16">
-        <f>IF(ISNUMBER(V73),IFERROR(IF(INDEX($B73:$X73,MATCH(DATE(YEAR(V$4)-1,MONTH(V$4),DAY(V$4)),$B$4:$X$4,0))&gt;0,V73/INDEX($B73:$X73,MATCH(DATE(YEAR(V$4)-1,MONTH(V$4),DAY(V$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(V73),IFERROR(IF(INDEX($B73:$Y73,MATCH(DATE(YEAR(V$4)-1,MONTH(V$4),DAY(V$4)),$B$4:$Y$4,0))&gt;0,V73/INDEX($B73:$Y73,MATCH(DATE(YEAR(V$4)-1,MONTH(V$4),DAY(V$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="W150" s="16">
-        <f>IF(ISNUMBER(W73),IFERROR(IF(INDEX($B73:$X73,MATCH(DATE(YEAR(W$4)-1,MONTH(W$4),DAY(W$4)),$B$4:$X$4,0))&gt;0,W73/INDEX($B73:$X73,MATCH(DATE(YEAR(W$4)-1,MONTH(W$4),DAY(W$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(W73),IFERROR(IF(INDEX($B73:$Y73,MATCH(DATE(YEAR(W$4)-1,MONTH(W$4),DAY(W$4)),$B$4:$Y$4,0))&gt;0,W73/INDEX($B73:$Y73,MATCH(DATE(YEAR(W$4)-1,MONTH(W$4),DAY(W$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="X150" s="16">
-        <f>IF(ISNUMBER(X73),IFERROR(IF(INDEX($B73:$X73,MATCH(DATE(YEAR(X$4)-1,MONTH(X$4),DAY(X$4)),$B$4:$X$4,0))&gt;0,X73/INDEX($B73:$X73,MATCH(DATE(YEAR(X$4)-1,MONTH(X$4),DAY(X$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(X73),IFERROR(IF(INDEX($B73:$Y73,MATCH(DATE(YEAR(X$4)-1,MONTH(X$4),DAY(X$4)),$B$4:$Y$4,0))&gt;0,X73/INDEX($B73:$Y73,MATCH(DATE(YEAR(X$4)-1,MONTH(X$4),DAY(X$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
+        <v/>
+      </c>
+      <c r="Y150" s="16">
+        <f>IF(ISNUMBER(Y73),IFERROR(IF(INDEX($B73:$Y73,MATCH(DATE(YEAR(Y$4)-1,MONTH(Y$4),DAY(Y$4)),$B$4:$Y$4,0))&gt;0,Y73/INDEX($B73:$Y73,MATCH(DATE(YEAR(Y$4)-1,MONTH(Y$4),DAY(Y$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
     </row>
@@ -36005,95 +36389,99 @@
         </is>
       </c>
       <c r="B151" s="16">
-        <f>IF(ISNUMBER(B94),IFERROR(IF(INDEX($B94:$X94,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$X$4,0))&gt;0,B94/INDEX($B94:$X94,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(B94),IFERROR(IF(INDEX($B94:$Y94,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$Y$4,0))&gt;0,B94/INDEX($B94:$Y94,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="C151" s="16">
-        <f>IF(ISNUMBER(C94),IFERROR(IF(INDEX($B94:$X94,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$X$4,0))&gt;0,C94/INDEX($B94:$X94,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(C94),IFERROR(IF(INDEX($B94:$Y94,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$Y$4,0))&gt;0,C94/INDEX($B94:$Y94,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="D151" s="16">
-        <f>IF(ISNUMBER(D94),IFERROR(IF(INDEX($B94:$X94,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$X$4,0))&gt;0,D94/INDEX($B94:$X94,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(D94),IFERROR(IF(INDEX($B94:$Y94,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$Y$4,0))&gt;0,D94/INDEX($B94:$Y94,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="E151" s="16">
-        <f>IF(ISNUMBER(E94),IFERROR(IF(INDEX($B94:$X94,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$X$4,0))&gt;0,E94/INDEX($B94:$X94,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(E94),IFERROR(IF(INDEX($B94:$Y94,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$Y$4,0))&gt;0,E94/INDEX($B94:$Y94,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="F151" s="16">
-        <f>IF(ISNUMBER(F94),IFERROR(IF(INDEX($B94:$X94,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$X$4,0))&gt;0,F94/INDEX($B94:$X94,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(F94),IFERROR(IF(INDEX($B94:$Y94,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$Y$4,0))&gt;0,F94/INDEX($B94:$Y94,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="G151" s="16">
-        <f>IF(ISNUMBER(G94),IFERROR(IF(INDEX($B94:$X94,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$X$4,0))&gt;0,G94/INDEX($B94:$X94,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(G94),IFERROR(IF(INDEX($B94:$Y94,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$Y$4,0))&gt;0,G94/INDEX($B94:$Y94,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="H151" s="16">
-        <f>IF(ISNUMBER(H94),IFERROR(IF(INDEX($B94:$X94,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$X$4,0))&gt;0,H94/INDEX($B94:$X94,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(H94),IFERROR(IF(INDEX($B94:$Y94,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$Y$4,0))&gt;0,H94/INDEX($B94:$Y94,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="I151" s="16">
-        <f>IF(ISNUMBER(I94),IFERROR(IF(INDEX($B94:$X94,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$X$4,0))&gt;0,I94/INDEX($B94:$X94,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(I94),IFERROR(IF(INDEX($B94:$Y94,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$Y$4,0))&gt;0,I94/INDEX($B94:$Y94,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="J151" s="16">
-        <f>IF(ISNUMBER(J94),IFERROR(IF(INDEX($B94:$X94,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$X$4,0))&gt;0,J94/INDEX($B94:$X94,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(J94),IFERROR(IF(INDEX($B94:$Y94,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$Y$4,0))&gt;0,J94/INDEX($B94:$Y94,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="K151" s="16">
-        <f>IF(ISNUMBER(K94),IFERROR(IF(INDEX($B94:$X94,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$X$4,0))&gt;0,K94/INDEX($B94:$X94,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(K94),IFERROR(IF(INDEX($B94:$Y94,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$Y$4,0))&gt;0,K94/INDEX($B94:$Y94,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="L151" s="16">
-        <f>IF(ISNUMBER(L94),IFERROR(IF(INDEX($B94:$X94,MATCH(DATE(YEAR(L$4)-1,MONTH(L$4),DAY(L$4)),$B$4:$X$4,0))&gt;0,L94/INDEX($B94:$X94,MATCH(DATE(YEAR(L$4)-1,MONTH(L$4),DAY(L$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(L94),IFERROR(IF(INDEX($B94:$Y94,MATCH(DATE(YEAR(L$4)-1,MONTH(L$4),DAY(L$4)),$B$4:$Y$4,0))&gt;0,L94/INDEX($B94:$Y94,MATCH(DATE(YEAR(L$4)-1,MONTH(L$4),DAY(L$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="M151" s="16">
-        <f>IF(ISNUMBER(M94),IFERROR(IF(INDEX($B94:$X94,MATCH(DATE(YEAR(M$4)-1,MONTH(M$4),DAY(M$4)),$B$4:$X$4,0))&gt;0,M94/INDEX($B94:$X94,MATCH(DATE(YEAR(M$4)-1,MONTH(M$4),DAY(M$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(M94),IFERROR(IF(INDEX($B94:$Y94,MATCH(DATE(YEAR(M$4)-1,MONTH(M$4),DAY(M$4)),$B$4:$Y$4,0))&gt;0,M94/INDEX($B94:$Y94,MATCH(DATE(YEAR(M$4)-1,MONTH(M$4),DAY(M$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="N151" s="16">
-        <f>IF(ISNUMBER(N94),IFERROR(IF(INDEX($B94:$X94,MATCH(DATE(YEAR(N$4)-1,MONTH(N$4),DAY(N$4)),$B$4:$X$4,0))&gt;0,N94/INDEX($B94:$X94,MATCH(DATE(YEAR(N$4)-1,MONTH(N$4),DAY(N$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(N94),IFERROR(IF(INDEX($B94:$Y94,MATCH(DATE(YEAR(N$4)-1,MONTH(N$4),DAY(N$4)),$B$4:$Y$4,0))&gt;0,N94/INDEX($B94:$Y94,MATCH(DATE(YEAR(N$4)-1,MONTH(N$4),DAY(N$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="O151" s="16">
-        <f>IF(ISNUMBER(O94),IFERROR(IF(INDEX($B94:$X94,MATCH(DATE(YEAR(O$4)-1,MONTH(O$4),DAY(O$4)),$B$4:$X$4,0))&gt;0,O94/INDEX($B94:$X94,MATCH(DATE(YEAR(O$4)-1,MONTH(O$4),DAY(O$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(O94),IFERROR(IF(INDEX($B94:$Y94,MATCH(DATE(YEAR(O$4)-1,MONTH(O$4),DAY(O$4)),$B$4:$Y$4,0))&gt;0,O94/INDEX($B94:$Y94,MATCH(DATE(YEAR(O$4)-1,MONTH(O$4),DAY(O$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="P151" s="16">
-        <f>IF(ISNUMBER(P94),IFERROR(IF(INDEX($B94:$X94,MATCH(DATE(YEAR(P$4)-1,MONTH(P$4),DAY(P$4)),$B$4:$X$4,0))&gt;0,P94/INDEX($B94:$X94,MATCH(DATE(YEAR(P$4)-1,MONTH(P$4),DAY(P$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(P94),IFERROR(IF(INDEX($B94:$Y94,MATCH(DATE(YEAR(P$4)-1,MONTH(P$4),DAY(P$4)),$B$4:$Y$4,0))&gt;0,P94/INDEX($B94:$Y94,MATCH(DATE(YEAR(P$4)-1,MONTH(P$4),DAY(P$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="Q151" s="16">
-        <f>IF(ISNUMBER(Q94),IFERROR(IF(INDEX($B94:$X94,MATCH(DATE(YEAR(Q$4)-1,MONTH(Q$4),DAY(Q$4)),$B$4:$X$4,0))&gt;0,Q94/INDEX($B94:$X94,MATCH(DATE(YEAR(Q$4)-1,MONTH(Q$4),DAY(Q$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(Q94),IFERROR(IF(INDEX($B94:$Y94,MATCH(DATE(YEAR(Q$4)-1,MONTH(Q$4),DAY(Q$4)),$B$4:$Y$4,0))&gt;0,Q94/INDEX($B94:$Y94,MATCH(DATE(YEAR(Q$4)-1,MONTH(Q$4),DAY(Q$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="R151" s="16">
-        <f>IF(ISNUMBER(R94),IFERROR(IF(INDEX($B94:$X94,MATCH(DATE(YEAR(R$4)-1,MONTH(R$4),DAY(R$4)),$B$4:$X$4,0))&gt;0,R94/INDEX($B94:$X94,MATCH(DATE(YEAR(R$4)-1,MONTH(R$4),DAY(R$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(R94),IFERROR(IF(INDEX($B94:$Y94,MATCH(DATE(YEAR(R$4)-1,MONTH(R$4),DAY(R$4)),$B$4:$Y$4,0))&gt;0,R94/INDEX($B94:$Y94,MATCH(DATE(YEAR(R$4)-1,MONTH(R$4),DAY(R$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="S151" s="16">
-        <f>IF(ISNUMBER(S94),IFERROR(IF(INDEX($B94:$X94,MATCH(DATE(YEAR(S$4)-1,MONTH(S$4),DAY(S$4)),$B$4:$X$4,0))&gt;0,S94/INDEX($B94:$X94,MATCH(DATE(YEAR(S$4)-1,MONTH(S$4),DAY(S$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(S94),IFERROR(IF(INDEX($B94:$Y94,MATCH(DATE(YEAR(S$4)-1,MONTH(S$4),DAY(S$4)),$B$4:$Y$4,0))&gt;0,S94/INDEX($B94:$Y94,MATCH(DATE(YEAR(S$4)-1,MONTH(S$4),DAY(S$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="T151" s="16">
-        <f>IF(ISNUMBER(T94),IFERROR(IF(INDEX($B94:$X94,MATCH(DATE(YEAR(T$4)-1,MONTH(T$4),DAY(T$4)),$B$4:$X$4,0))&gt;0,T94/INDEX($B94:$X94,MATCH(DATE(YEAR(T$4)-1,MONTH(T$4),DAY(T$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(T94),IFERROR(IF(INDEX($B94:$Y94,MATCH(DATE(YEAR(T$4)-1,MONTH(T$4),DAY(T$4)),$B$4:$Y$4,0))&gt;0,T94/INDEX($B94:$Y94,MATCH(DATE(YEAR(T$4)-1,MONTH(T$4),DAY(T$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="U151" s="16">
-        <f>IF(ISNUMBER(U94),IFERROR(IF(INDEX($B94:$X94,MATCH(DATE(YEAR(U$4)-1,MONTH(U$4),DAY(U$4)),$B$4:$X$4,0))&gt;0,U94/INDEX($B94:$X94,MATCH(DATE(YEAR(U$4)-1,MONTH(U$4),DAY(U$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(U94),IFERROR(IF(INDEX($B94:$Y94,MATCH(DATE(YEAR(U$4)-1,MONTH(U$4),DAY(U$4)),$B$4:$Y$4,0))&gt;0,U94/INDEX($B94:$Y94,MATCH(DATE(YEAR(U$4)-1,MONTH(U$4),DAY(U$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="V151" s="16">
-        <f>IF(ISNUMBER(V94),IFERROR(IF(INDEX($B94:$X94,MATCH(DATE(YEAR(V$4)-1,MONTH(V$4),DAY(V$4)),$B$4:$X$4,0))&gt;0,V94/INDEX($B94:$X94,MATCH(DATE(YEAR(V$4)-1,MONTH(V$4),DAY(V$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(V94),IFERROR(IF(INDEX($B94:$Y94,MATCH(DATE(YEAR(V$4)-1,MONTH(V$4),DAY(V$4)),$B$4:$Y$4,0))&gt;0,V94/INDEX($B94:$Y94,MATCH(DATE(YEAR(V$4)-1,MONTH(V$4),DAY(V$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="W151" s="16">
-        <f>IF(ISNUMBER(W94),IFERROR(IF(INDEX($B94:$X94,MATCH(DATE(YEAR(W$4)-1,MONTH(W$4),DAY(W$4)),$B$4:$X$4,0))&gt;0,W94/INDEX($B94:$X94,MATCH(DATE(YEAR(W$4)-1,MONTH(W$4),DAY(W$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(W94),IFERROR(IF(INDEX($B94:$Y94,MATCH(DATE(YEAR(W$4)-1,MONTH(W$4),DAY(W$4)),$B$4:$Y$4,0))&gt;0,W94/INDEX($B94:$Y94,MATCH(DATE(YEAR(W$4)-1,MONTH(W$4),DAY(W$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="X151" s="16">
-        <f>IF(ISNUMBER(X94),IFERROR(IF(INDEX($B94:$X94,MATCH(DATE(YEAR(X$4)-1,MONTH(X$4),DAY(X$4)),$B$4:$X$4,0))&gt;0,X94/INDEX($B94:$X94,MATCH(DATE(YEAR(X$4)-1,MONTH(X$4),DAY(X$4)),$B$4:$X$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(X94),IFERROR(IF(INDEX($B94:$Y94,MATCH(DATE(YEAR(X$4)-1,MONTH(X$4),DAY(X$4)),$B$4:$Y$4,0))&gt;0,X94/INDEX($B94:$Y94,MATCH(DATE(YEAR(X$4)-1,MONTH(X$4),DAY(X$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
+        <v/>
+      </c>
+      <c r="Y151" s="16">
+        <f>IF(ISNUMBER(Y94),IFERROR(IF(INDEX($B94:$Y94,MATCH(DATE(YEAR(Y$4)-1,MONTH(Y$4),DAY(Y$4)),$B$4:$Y$4,0))&gt;0,Y94/INDEX($B94:$Y94,MATCH(DATE(YEAR(Y$4)-1,MONTH(Y$4),DAY(Y$4)),$B$4:$Y$4,0))-1,""),""),"")</f>
         <v/>
       </c>
     </row>
@@ -36108,7 +36496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M151"/>
+  <dimension ref="A1:N151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -36124,6 +36512,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -36182,6 +36571,9 @@
       <c r="M4" s="4" t="n">
         <v>46203</v>
       </c>
+      <c r="N4" s="4" t="n">
+        <v>46295</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -36249,6 +36641,11 @@
           <t>2026 Q2</t>
         </is>
       </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>2026 Q3</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -36291,6 +36688,9 @@
       </c>
       <c r="M6" s="5" t="n">
         <v>6</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -36311,6 +36711,9 @@
       <c r="K7" s="4" t="n"/>
       <c r="L7" s="4" t="n"/>
       <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4" t="n">
+        <v>46315</v>
+      </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -36376,6 +36779,11 @@
       <c r="M8" s="6" t="inlineStr">
         <is>
           <t>MFC 55120262report.xlsx</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>30b2796f-551_finance_report_xls_6ad71569eed5c.xlsx</t>
         </is>
       </c>
     </row>
@@ -36409,6 +36817,7 @@
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr"/>
+      <c r="N9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -36428,6 +36837,7 @@
       <c r="K10" s="7" t="n"/>
       <c r="L10" s="7" t="n"/>
       <c r="M10" s="7" t="n"/>
+      <c r="N10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -36447,6 +36857,7 @@
       <c r="K11" s="7" t="n"/>
       <c r="L11" s="7" t="n"/>
       <c r="M11" s="7" t="n"/>
+      <c r="N11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -36490,6 +36901,9 @@
       <c r="M12" s="8" t="n">
         <v>235241.15</v>
       </c>
+      <c r="N12" s="8" t="n">
+        <v>229218.05</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -36533,6 +36947,9 @@
       <c r="M13" s="8" t="n">
         <v>8906497.789999999</v>
       </c>
+      <c r="N13" s="8" t="n">
+        <v>8535707.07</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -36576,6 +36993,9 @@
       <c r="M14" s="8" t="n">
         <v>636097.15</v>
       </c>
+      <c r="N14" s="8" t="n">
+        <v>614615.97</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -36619,6 +37039,9 @@
       <c r="M15" s="8" t="n">
         <v>389518.61</v>
       </c>
+      <c r="N15" s="8" t="n">
+        <v>227938.38</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -36662,6 +37085,9 @@
       <c r="M16" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="N16" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -36705,6 +37131,9 @@
       <c r="M17" s="8" t="n">
         <v>7834608.06</v>
       </c>
+      <c r="N17" s="8" t="n">
+        <v>7855902.92</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -36748,6 +37177,9 @@
       <c r="M18" s="8" t="n">
         <v>938755.1</v>
       </c>
+      <c r="N18" s="8" t="n">
+        <v>1525083.7</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -36779,6 +37211,9 @@
       <c r="M19" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="N19" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -36816,6 +37251,9 @@
       <c r="M20" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="N20" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -36865,6 +37303,9 @@
       </c>
       <c r="M22" s="10" t="n">
         <v>18940717.86</v>
+      </c>
+      <c r="N22" s="10" t="n">
+        <v>18988466.09</v>
       </c>
     </row>
     <row r="23">
@@ -36885,6 +37326,7 @@
       <c r="K23" s="7" t="n"/>
       <c r="L23" s="7" t="n"/>
       <c r="M23" s="7" t="n"/>
+      <c r="N23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -36928,6 +37370,9 @@
       <c r="M24" s="8" t="n">
         <v>48070955.16</v>
       </c>
+      <c r="N24" s="8" t="n">
+        <v>50158941.14</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -36971,6 +37416,9 @@
       <c r="M25" s="8" t="n">
         <v>384730.25</v>
       </c>
+      <c r="N25" s="8" t="n">
+        <v>353083.09</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -37002,6 +37450,9 @@
       <c r="M26" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="N26" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -37033,6 +37484,9 @@
       <c r="M27" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="N27" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -37064,6 +37518,9 @@
       <c r="M28" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="N28" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -37107,6 +37564,9 @@
       <c r="M29" s="8" t="n">
         <v>79616.33</v>
       </c>
+      <c r="N29" s="8" t="n">
+        <v>78970.12</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -37210,6 +37670,9 @@
       <c r="M33" s="8" t="n">
         <v>2820809.52</v>
       </c>
+      <c r="N33" s="8" t="n">
+        <v>2533167.44</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -37260,6 +37723,9 @@
       <c r="M35" s="10" t="n">
         <v>51356111.26</v>
       </c>
+      <c r="N35" s="10" t="n">
+        <v>53124161.78</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
@@ -37302,6 +37768,9 @@
       </c>
       <c r="M36" s="10" t="n">
         <v>70296829.12</v>
+      </c>
+      <c r="N36" s="10" t="n">
+        <v>72112627.87</v>
       </c>
     </row>
     <row r="37">
@@ -37322,6 +37791,7 @@
       <c r="K37" s="7" t="n"/>
       <c r="L37" s="7" t="n"/>
       <c r="M37" s="7" t="n"/>
+      <c r="N37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -37365,6 +37835,9 @@
       <c r="M38" s="8" t="n">
         <v>1415060.91</v>
       </c>
+      <c r="N38" s="8" t="n">
+        <v>2350712.47</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -37408,6 +37881,9 @@
       <c r="M39" s="8" t="n">
         <v>344999.68</v>
       </c>
+      <c r="N39" s="8" t="n">
+        <v>694999.6800000001</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -37451,6 +37927,9 @@
       <c r="M40" s="8" t="n">
         <v>1754561.24</v>
       </c>
+      <c r="N40" s="8" t="n">
+        <v>1558302.6</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -37494,6 +37973,9 @@
       <c r="M41" s="8" t="n">
         <v>109174.74</v>
       </c>
+      <c r="N41" s="8" t="n">
+        <v>147967.39</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -37537,6 +38019,9 @@
       <c r="M42" s="8" t="n">
         <v>4380150</v>
       </c>
+      <c r="N42" s="8" t="n">
+        <v>3637650</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -37580,6 +38065,9 @@
       <c r="M43" s="8" t="n">
         <v>155425.79</v>
       </c>
+      <c r="N43" s="8" t="n">
+        <v>155430.73</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -37623,6 +38111,9 @@
       <c r="M44" s="8" t="n">
         <v>1223498.3</v>
       </c>
+      <c r="N44" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -37666,6 +38157,9 @@
       <c r="M45" s="8" t="n">
         <v>130164.45</v>
       </c>
+      <c r="N45" s="8" t="n">
+        <v>111749.88</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -37709,6 +38203,9 @@
       <c r="M46" s="8" t="n">
         <v>270203.23</v>
       </c>
+      <c r="N46" s="8" t="n">
+        <v>270203.23</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -37752,6 +38249,9 @@
       <c r="M47" s="8" t="n">
         <v>1462989.3</v>
       </c>
+      <c r="N47" s="8" t="n">
+        <v>1745066.65</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -37783,6 +38283,9 @@
       <c r="M48" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="N48" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
@@ -37825,6 +38328,9 @@
       </c>
       <c r="M49" s="10" t="n">
         <v>11246227.62</v>
+      </c>
+      <c r="N49" s="10" t="n">
+        <v>10672082.63</v>
       </c>
     </row>
     <row r="50">
@@ -37845,6 +38351,7 @@
       <c r="K50" s="7" t="n"/>
       <c r="L50" s="7" t="n"/>
       <c r="M50" s="7" t="n"/>
+      <c r="N50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -37888,6 +38395,9 @@
       <c r="M51" s="8" t="n">
         <v>26758620.22</v>
       </c>
+      <c r="N51" s="8" t="n">
+        <v>26649270.22</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -37928,6 +38438,9 @@
       <c r="M52" s="8" t="n">
         <v>1266779.78</v>
       </c>
+      <c r="N52" s="8" t="n">
+        <v>1266779.78</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -37968,6 +38481,9 @@
       <c r="M53" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="N53" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -38015,6 +38531,9 @@
       <c r="M55" s="8" t="n">
         <v>99848.72</v>
       </c>
+      <c r="N55" s="8" t="n">
+        <v>335956.07</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
@@ -38058,6 +38577,9 @@
       <c r="M56" s="10" t="n">
         <v>28125248.72</v>
       </c>
+      <c r="N56" s="10" t="n">
+        <v>28252006.07</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
@@ -38100,6 +38622,9 @@
       </c>
       <c r="M57" s="10" t="n">
         <v>39371476.34</v>
+      </c>
+      <c r="N57" s="10" t="n">
+        <v>38924088.7</v>
       </c>
     </row>
     <row r="58">
@@ -38120,6 +38645,7 @@
       <c r="K58" s="7" t="n"/>
       <c r="L58" s="7" t="n"/>
       <c r="M58" s="7" t="n"/>
+      <c r="N58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -38163,6 +38689,9 @@
       <c r="M59" s="8" t="n">
         <v>2318181.93</v>
       </c>
+      <c r="N59" s="8" t="n">
+        <v>2318181.93</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -38191,6 +38720,9 @@
       <c r="M60" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="N60" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -38234,6 +38766,9 @@
       <c r="M61" s="8" t="n">
         <v>6835733.06</v>
       </c>
+      <c r="N61" s="8" t="n">
+        <v>6835733.06</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -38277,6 +38812,9 @@
       <c r="M62" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="N62" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -38305,6 +38843,9 @@
       <c r="M63" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="N63" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -38333,6 +38874,9 @@
       <c r="M64" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="N64" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -38376,6 +38920,9 @@
       <c r="M65" s="8" t="n">
         <v>21771437.79</v>
       </c>
+      <c r="N65" s="8" t="n">
+        <v>24034624.19</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -38433,6 +38980,9 @@
       <c r="M68" s="10" t="n">
         <v>30925352.78</v>
       </c>
+      <c r="N68" s="10" t="n">
+        <v>33188539.18</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
@@ -38475,6 +39025,9 @@
       </c>
       <c r="M69" s="10" t="n">
         <v>70296829.12</v>
+      </c>
+      <c r="N69" s="10" t="n">
+        <v>72112627.87</v>
       </c>
     </row>
     <row r="70">
@@ -38495,6 +39048,7 @@
       <c r="K70" s="7" t="n"/>
       <c r="L70" s="7" t="n"/>
       <c r="M70" s="7" t="n"/>
+      <c r="N70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -38538,6 +39092,9 @@
       <c r="M71" s="8" t="n">
         <v>25000808.23</v>
       </c>
+      <c r="N71" s="8" t="n">
+        <v>40354498.95</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -38581,6 +39138,9 @@
       <c r="M72" s="8" t="n">
         <v>11611933.13</v>
       </c>
+      <c r="N72" s="8" t="n">
+        <v>18292057.41</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
@@ -38624,6 +39184,9 @@
       <c r="M73" s="10" t="n">
         <v>13388875.1</v>
       </c>
+      <c r="N73" s="10" t="n">
+        <v>22062441.54</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -38667,6 +39230,9 @@
       <c r="M74" s="8" t="n">
         <v>981.8200000000001</v>
       </c>
+      <c r="N74" s="8" t="n">
+        <v>2236.36</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -38710,6 +39276,9 @@
       <c r="M75" s="8" t="n">
         <v>204.95</v>
       </c>
+      <c r="N75" s="8" t="n">
+        <v>334.34</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -38753,6 +39322,9 @@
       <c r="M76" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="N76" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -38796,6 +39368,9 @@
       <c r="M77" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="N77" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -38839,6 +39414,9 @@
       <c r="M78" s="8" t="n">
         <v>149809.04</v>
       </c>
+      <c r="N78" s="8" t="n">
+        <v>177912.56</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -38882,6 +39460,9 @@
       <c r="M79" s="8" t="n">
         <v>6077162.62</v>
       </c>
+      <c r="N79" s="8" t="n">
+        <v>9612022.15</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -38925,6 +39506,9 @@
       <c r="M80" s="8" t="n">
         <v>2474802.8</v>
       </c>
+      <c r="N80" s="8" t="n">
+        <v>4160111.76</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -38968,6 +39552,9 @@
       <c r="M81" s="8" t="n">
         <v>1030182.43</v>
       </c>
+      <c r="N81" s="8" t="n">
+        <v>1703006.65</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -39011,6 +39598,9 @@
       <c r="M82" s="8" t="n">
         <v>369512.42</v>
       </c>
+      <c r="N82" s="8" t="n">
+        <v>487186.98</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -39054,6 +39644,9 @@
       <c r="M83" s="8" t="n">
         <v>-54307.63</v>
       </c>
+      <c r="N83" s="8" t="n">
+        <v>-73560.92</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -39097,6 +39690,9 @@
       <c r="M84" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="N84" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -39140,6 +39736,9 @@
       <c r="M85" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="N85" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -39183,6 +39782,9 @@
       <c r="M86" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="N86" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -39240,6 +39842,9 @@
       <c r="M89" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="N89" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
@@ -39283,6 +39888,9 @@
       <c r="M90" s="10" t="n">
         <v>3533903.01</v>
       </c>
+      <c r="N90" s="10" t="n">
+        <v>6207036.33</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -39326,6 +39934,9 @@
       <c r="M91" s="8" t="n">
         <v>445756.17</v>
       </c>
+      <c r="N91" s="8" t="n">
+        <v>855703.09</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
@@ -39369,6 +39980,9 @@
       <c r="M92" s="10" t="n">
         <v>3088146.84</v>
       </c>
+      <c r="N92" s="10" t="n">
+        <v>5351333.24</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -39451,6 +40065,9 @@
       </c>
       <c r="M94" s="10" t="n">
         <v>3088146.84</v>
+      </c>
+      <c r="N94" s="10" t="n">
+        <v>5351333.24</v>
       </c>
     </row>
     <row r="95">
@@ -39598,6 +40215,7 @@
       <c r="K99" s="9" t="n"/>
       <c r="L99" s="9" t="n"/>
       <c r="M99" s="9" t="n"/>
+      <c r="N99" s="9" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
@@ -39641,6 +40259,9 @@
       <c r="M100" s="10" t="n">
         <v>3088146.84</v>
       </c>
+      <c r="N100" s="10" t="n">
+        <v>5351333.24</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
@@ -39694,6 +40315,10 @@
       </c>
       <c r="M102" s="12">
         <f>IF(AND(ISNUMBER(M36),ISNUMBER(M57),ISNUMBER(M68)),ROUND(M36-M57-M68,0),"")</f>
+        <v/>
+      </c>
+      <c r="N102" s="12">
+        <f>IF(AND(ISNUMBER(N36),ISNUMBER(N57),ISNUMBER(N68)),ROUND(N36-N57-N68,0),"")</f>
         <v/>
       </c>
     </row>
@@ -39715,6 +40340,7 @@
       <c r="K104" s="7" t="n"/>
       <c r="L104" s="7" t="n"/>
       <c r="M104" s="7" t="n"/>
+      <c r="N104" s="7" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="13" t="inlineStr">
@@ -39784,6 +40410,10 @@
         <f>IF(ISNUMBER(M$6),IFERROR(12/M$6,""),"")</f>
         <v/>
       </c>
+      <c r="N107" s="15">
+        <f>IF(ISNUMBER(N$6),IFERROR(12/N$6,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -39792,51 +40422,55 @@
         </is>
       </c>
       <c r="B108" s="8">
-        <f>IF(ISNUMBER(B36),IFERROR(IF(INDEX($B36:$M36,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$M$4,0))="",B36,(B36+INDEX($B36:$M36,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$M$4,0)))/2),B36),"")</f>
+        <f>IF(ISNUMBER(B36),IFERROR(IF(INDEX($B36:$N36,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$N$4,0))="",B36,(B36+INDEX($B36:$N36,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$N$4,0)))/2),B36),"")</f>
         <v/>
       </c>
       <c r="C108" s="8">
-        <f>IF(ISNUMBER(C36),IFERROR(IF(INDEX($B36:$M36,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$M$4,0))="",C36,(C36+INDEX($B36:$M36,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$M$4,0)))/2),C36),"")</f>
+        <f>IF(ISNUMBER(C36),IFERROR(IF(INDEX($B36:$N36,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$N$4,0))="",C36,(C36+INDEX($B36:$N36,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$N$4,0)))/2),C36),"")</f>
         <v/>
       </c>
       <c r="D108" s="8">
-        <f>IF(ISNUMBER(D36),IFERROR(IF(INDEX($B36:$M36,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$M$4,0))="",D36,(D36+INDEX($B36:$M36,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$M$4,0)))/2),D36),"")</f>
+        <f>IF(ISNUMBER(D36),IFERROR(IF(INDEX($B36:$N36,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$N$4,0))="",D36,(D36+INDEX($B36:$N36,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$N$4,0)))/2),D36),"")</f>
         <v/>
       </c>
       <c r="E108" s="8">
-        <f>IF(ISNUMBER(E36),IFERROR(IF(INDEX($B36:$M36,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$M$4,0))="",E36,(E36+INDEX($B36:$M36,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$M$4,0)))/2),E36),"")</f>
+        <f>IF(ISNUMBER(E36),IFERROR(IF(INDEX($B36:$N36,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$N$4,0))="",E36,(E36+INDEX($B36:$N36,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$N$4,0)))/2),E36),"")</f>
         <v/>
       </c>
       <c r="F108" s="8">
-        <f>IF(ISNUMBER(F36),IFERROR(IF(INDEX($B36:$M36,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$M$4,0))="",F36,(F36+INDEX($B36:$M36,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$M$4,0)))/2),F36),"")</f>
+        <f>IF(ISNUMBER(F36),IFERROR(IF(INDEX($B36:$N36,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$N$4,0))="",F36,(F36+INDEX($B36:$N36,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$N$4,0)))/2),F36),"")</f>
         <v/>
       </c>
       <c r="G108" s="8">
-        <f>IF(ISNUMBER(G36),IFERROR(IF(INDEX($B36:$M36,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$M$4,0))="",G36,(G36+INDEX($B36:$M36,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$M$4,0)))/2),G36),"")</f>
+        <f>IF(ISNUMBER(G36),IFERROR(IF(INDEX($B36:$N36,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$N$4,0))="",G36,(G36+INDEX($B36:$N36,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$N$4,0)))/2),G36),"")</f>
         <v/>
       </c>
       <c r="H108" s="8">
-        <f>IF(ISNUMBER(H36),IFERROR(IF(INDEX($B36:$M36,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$M$4,0))="",H36,(H36+INDEX($B36:$M36,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$M$4,0)))/2),H36),"")</f>
+        <f>IF(ISNUMBER(H36),IFERROR(IF(INDEX($B36:$N36,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$N$4,0))="",H36,(H36+INDEX($B36:$N36,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$N$4,0)))/2),H36),"")</f>
         <v/>
       </c>
       <c r="I108" s="8">
-        <f>IF(ISNUMBER(I36),IFERROR(IF(INDEX($B36:$M36,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$M$4,0))="",I36,(I36+INDEX($B36:$M36,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$M$4,0)))/2),I36),"")</f>
+        <f>IF(ISNUMBER(I36),IFERROR(IF(INDEX($B36:$N36,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$N$4,0))="",I36,(I36+INDEX($B36:$N36,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$N$4,0)))/2),I36),"")</f>
         <v/>
       </c>
       <c r="J108" s="8">
-        <f>IF(ISNUMBER(J36),IFERROR(IF(INDEX($B36:$M36,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$M$4,0))="",J36,(J36+INDEX($B36:$M36,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$M$4,0)))/2),J36),"")</f>
+        <f>IF(ISNUMBER(J36),IFERROR(IF(INDEX($B36:$N36,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$N$4,0))="",J36,(J36+INDEX($B36:$N36,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$N$4,0)))/2),J36),"")</f>
         <v/>
       </c>
       <c r="K108" s="8">
-        <f>IF(ISNUMBER(K36),IFERROR(IF(INDEX($B36:$M36,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$M$4,0))="",K36,(K36+INDEX($B36:$M36,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$M$4,0)))/2),K36),"")</f>
+        <f>IF(ISNUMBER(K36),IFERROR(IF(INDEX($B36:$N36,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$N$4,0))="",K36,(K36+INDEX($B36:$N36,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$N$4,0)))/2),K36),"")</f>
         <v/>
       </c>
       <c r="L108" s="8">
-        <f>IF(ISNUMBER(L36),IFERROR(IF(INDEX($B36:$M36,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$M$4,0))="",L36,(L36+INDEX($B36:$M36,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$M$4,0)))/2),L36),"")</f>
+        <f>IF(ISNUMBER(L36),IFERROR(IF(INDEX($B36:$N36,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$N$4,0))="",L36,(L36+INDEX($B36:$N36,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$N$4,0)))/2),L36),"")</f>
         <v/>
       </c>
       <c r="M108" s="8">
-        <f>IF(ISNUMBER(M36),IFERROR(IF(INDEX($B36:$M36,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$M$4,0))="",M36,(M36+INDEX($B36:$M36,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$M$4,0)))/2),M36),"")</f>
+        <f>IF(ISNUMBER(M36),IFERROR(IF(INDEX($B36:$N36,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$N$4,0))="",M36,(M36+INDEX($B36:$N36,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$N$4,0)))/2),M36),"")</f>
+        <v/>
+      </c>
+      <c r="N108" s="8">
+        <f>IF(ISNUMBER(N36),IFERROR(IF(INDEX($B36:$N36,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$N$4,0))="",N36,(N36+INDEX($B36:$N36,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$N$4,0)))/2),N36),"")</f>
         <v/>
       </c>
     </row>
@@ -39847,51 +40481,55 @@
         </is>
       </c>
       <c r="B109" s="8">
-        <f>IF(ISNUMBER(B68),IFERROR(IF(INDEX($B68:$M68,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$M$4,0))="",B68,(B68+INDEX($B68:$M68,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$M$4,0)))/2),B68),"")</f>
+        <f>IF(ISNUMBER(B68),IFERROR(IF(INDEX($B68:$N68,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$N$4,0))="",B68,(B68+INDEX($B68:$N68,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$N$4,0)))/2),B68),"")</f>
         <v/>
       </c>
       <c r="C109" s="8">
-        <f>IF(ISNUMBER(C68),IFERROR(IF(INDEX($B68:$M68,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$M$4,0))="",C68,(C68+INDEX($B68:$M68,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$M$4,0)))/2),C68),"")</f>
+        <f>IF(ISNUMBER(C68),IFERROR(IF(INDEX($B68:$N68,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$N$4,0))="",C68,(C68+INDEX($B68:$N68,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$N$4,0)))/2),C68),"")</f>
         <v/>
       </c>
       <c r="D109" s="8">
-        <f>IF(ISNUMBER(D68),IFERROR(IF(INDEX($B68:$M68,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$M$4,0))="",D68,(D68+INDEX($B68:$M68,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$M$4,0)))/2),D68),"")</f>
+        <f>IF(ISNUMBER(D68),IFERROR(IF(INDEX($B68:$N68,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$N$4,0))="",D68,(D68+INDEX($B68:$N68,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$N$4,0)))/2),D68),"")</f>
         <v/>
       </c>
       <c r="E109" s="8">
-        <f>IF(ISNUMBER(E68),IFERROR(IF(INDEX($B68:$M68,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$M$4,0))="",E68,(E68+INDEX($B68:$M68,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$M$4,0)))/2),E68),"")</f>
+        <f>IF(ISNUMBER(E68),IFERROR(IF(INDEX($B68:$N68,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$N$4,0))="",E68,(E68+INDEX($B68:$N68,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$N$4,0)))/2),E68),"")</f>
         <v/>
       </c>
       <c r="F109" s="8">
-        <f>IF(ISNUMBER(F68),IFERROR(IF(INDEX($B68:$M68,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$M$4,0))="",F68,(F68+INDEX($B68:$M68,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$M$4,0)))/2),F68),"")</f>
+        <f>IF(ISNUMBER(F68),IFERROR(IF(INDEX($B68:$N68,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$N$4,0))="",F68,(F68+INDEX($B68:$N68,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$N$4,0)))/2),F68),"")</f>
         <v/>
       </c>
       <c r="G109" s="8">
-        <f>IF(ISNUMBER(G68),IFERROR(IF(INDEX($B68:$M68,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$M$4,0))="",G68,(G68+INDEX($B68:$M68,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$M$4,0)))/2),G68),"")</f>
+        <f>IF(ISNUMBER(G68),IFERROR(IF(INDEX($B68:$N68,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$N$4,0))="",G68,(G68+INDEX($B68:$N68,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$N$4,0)))/2),G68),"")</f>
         <v/>
       </c>
       <c r="H109" s="8">
-        <f>IF(ISNUMBER(H68),IFERROR(IF(INDEX($B68:$M68,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$M$4,0))="",H68,(H68+INDEX($B68:$M68,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$M$4,0)))/2),H68),"")</f>
+        <f>IF(ISNUMBER(H68),IFERROR(IF(INDEX($B68:$N68,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$N$4,0))="",H68,(H68+INDEX($B68:$N68,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$N$4,0)))/2),H68),"")</f>
         <v/>
       </c>
       <c r="I109" s="8">
-        <f>IF(ISNUMBER(I68),IFERROR(IF(INDEX($B68:$M68,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$M$4,0))="",I68,(I68+INDEX($B68:$M68,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$M$4,0)))/2),I68),"")</f>
+        <f>IF(ISNUMBER(I68),IFERROR(IF(INDEX($B68:$N68,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$N$4,0))="",I68,(I68+INDEX($B68:$N68,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$N$4,0)))/2),I68),"")</f>
         <v/>
       </c>
       <c r="J109" s="8">
-        <f>IF(ISNUMBER(J68),IFERROR(IF(INDEX($B68:$M68,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$M$4,0))="",J68,(J68+INDEX($B68:$M68,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$M$4,0)))/2),J68),"")</f>
+        <f>IF(ISNUMBER(J68),IFERROR(IF(INDEX($B68:$N68,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$N$4,0))="",J68,(J68+INDEX($B68:$N68,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$N$4,0)))/2),J68),"")</f>
         <v/>
       </c>
       <c r="K109" s="8">
-        <f>IF(ISNUMBER(K68),IFERROR(IF(INDEX($B68:$M68,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$M$4,0))="",K68,(K68+INDEX($B68:$M68,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$M$4,0)))/2),K68),"")</f>
+        <f>IF(ISNUMBER(K68),IFERROR(IF(INDEX($B68:$N68,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$N$4,0))="",K68,(K68+INDEX($B68:$N68,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$N$4,0)))/2),K68),"")</f>
         <v/>
       </c>
       <c r="L109" s="8">
-        <f>IF(ISNUMBER(L68),IFERROR(IF(INDEX($B68:$M68,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$M$4,0))="",L68,(L68+INDEX($B68:$M68,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$M$4,0)))/2),L68),"")</f>
+        <f>IF(ISNUMBER(L68),IFERROR(IF(INDEX($B68:$N68,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$N$4,0))="",L68,(L68+INDEX($B68:$N68,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$N$4,0)))/2),L68),"")</f>
         <v/>
       </c>
       <c r="M109" s="8">
-        <f>IF(ISNUMBER(M68),IFERROR(IF(INDEX($B68:$M68,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$M$4,0))="",M68,(M68+INDEX($B68:$M68,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$M$4,0)))/2),M68),"")</f>
+        <f>IF(ISNUMBER(M68),IFERROR(IF(INDEX($B68:$N68,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$N$4,0))="",M68,(M68+INDEX($B68:$N68,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$N$4,0)))/2),M68),"")</f>
+        <v/>
+      </c>
+      <c r="N109" s="8">
+        <f>IF(ISNUMBER(N68),IFERROR(IF(INDEX($B68:$N68,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$N$4,0))="",N68,(N68+INDEX($B68:$N68,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$N$4,0)))/2),N68),"")</f>
         <v/>
       </c>
     </row>
@@ -39902,51 +40540,55 @@
         </is>
       </c>
       <c r="B110" s="8">
-        <f>IF(ISNUMBER(B17),IFERROR(IF(INDEX($B17:$M17,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$M$4,0))="",B17,(B17+INDEX($B17:$M17,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$M$4,0)))/2),B17),"")</f>
+        <f>IF(ISNUMBER(B17),IFERROR(IF(INDEX($B17:$N17,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$N$4,0))="",B17,(B17+INDEX($B17:$N17,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$N$4,0)))/2),B17),"")</f>
         <v/>
       </c>
       <c r="C110" s="8">
-        <f>IF(ISNUMBER(C17),IFERROR(IF(INDEX($B17:$M17,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$M$4,0))="",C17,(C17+INDEX($B17:$M17,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$M$4,0)))/2),C17),"")</f>
+        <f>IF(ISNUMBER(C17),IFERROR(IF(INDEX($B17:$N17,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$N$4,0))="",C17,(C17+INDEX($B17:$N17,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$N$4,0)))/2),C17),"")</f>
         <v/>
       </c>
       <c r="D110" s="8">
-        <f>IF(ISNUMBER(D17),IFERROR(IF(INDEX($B17:$M17,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$M$4,0))="",D17,(D17+INDEX($B17:$M17,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$M$4,0)))/2),D17),"")</f>
+        <f>IF(ISNUMBER(D17),IFERROR(IF(INDEX($B17:$N17,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$N$4,0))="",D17,(D17+INDEX($B17:$N17,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$N$4,0)))/2),D17),"")</f>
         <v/>
       </c>
       <c r="E110" s="8">
-        <f>IF(ISNUMBER(E17),IFERROR(IF(INDEX($B17:$M17,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$M$4,0))="",E17,(E17+INDEX($B17:$M17,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$M$4,0)))/2),E17),"")</f>
+        <f>IF(ISNUMBER(E17),IFERROR(IF(INDEX($B17:$N17,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$N$4,0))="",E17,(E17+INDEX($B17:$N17,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$N$4,0)))/2),E17),"")</f>
         <v/>
       </c>
       <c r="F110" s="8">
-        <f>IF(ISNUMBER(F17),IFERROR(IF(INDEX($B17:$M17,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$M$4,0))="",F17,(F17+INDEX($B17:$M17,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$M$4,0)))/2),F17),"")</f>
+        <f>IF(ISNUMBER(F17),IFERROR(IF(INDEX($B17:$N17,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$N$4,0))="",F17,(F17+INDEX($B17:$N17,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$N$4,0)))/2),F17),"")</f>
         <v/>
       </c>
       <c r="G110" s="8">
-        <f>IF(ISNUMBER(G17),IFERROR(IF(INDEX($B17:$M17,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$M$4,0))="",G17,(G17+INDEX($B17:$M17,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$M$4,0)))/2),G17),"")</f>
+        <f>IF(ISNUMBER(G17),IFERROR(IF(INDEX($B17:$N17,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$N$4,0))="",G17,(G17+INDEX($B17:$N17,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$N$4,0)))/2),G17),"")</f>
         <v/>
       </c>
       <c r="H110" s="8">
-        <f>IF(ISNUMBER(H17),IFERROR(IF(INDEX($B17:$M17,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$M$4,0))="",H17,(H17+INDEX($B17:$M17,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$M$4,0)))/2),H17),"")</f>
+        <f>IF(ISNUMBER(H17),IFERROR(IF(INDEX($B17:$N17,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$N$4,0))="",H17,(H17+INDEX($B17:$N17,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$N$4,0)))/2),H17),"")</f>
         <v/>
       </c>
       <c r="I110" s="8">
-        <f>IF(ISNUMBER(I17),IFERROR(IF(INDEX($B17:$M17,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$M$4,0))="",I17,(I17+INDEX($B17:$M17,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$M$4,0)))/2),I17),"")</f>
+        <f>IF(ISNUMBER(I17),IFERROR(IF(INDEX($B17:$N17,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$N$4,0))="",I17,(I17+INDEX($B17:$N17,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$N$4,0)))/2),I17),"")</f>
         <v/>
       </c>
       <c r="J110" s="8">
-        <f>IF(ISNUMBER(J17),IFERROR(IF(INDEX($B17:$M17,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$M$4,0))="",J17,(J17+INDEX($B17:$M17,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$M$4,0)))/2),J17),"")</f>
+        <f>IF(ISNUMBER(J17),IFERROR(IF(INDEX($B17:$N17,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$N$4,0))="",J17,(J17+INDEX($B17:$N17,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$N$4,0)))/2),J17),"")</f>
         <v/>
       </c>
       <c r="K110" s="8">
-        <f>IF(ISNUMBER(K17),IFERROR(IF(INDEX($B17:$M17,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$M$4,0))="",K17,(K17+INDEX($B17:$M17,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$M$4,0)))/2),K17),"")</f>
+        <f>IF(ISNUMBER(K17),IFERROR(IF(INDEX($B17:$N17,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$N$4,0))="",K17,(K17+INDEX($B17:$N17,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$N$4,0)))/2),K17),"")</f>
         <v/>
       </c>
       <c r="L110" s="8">
-        <f>IF(ISNUMBER(L17),IFERROR(IF(INDEX($B17:$M17,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$M$4,0))="",L17,(L17+INDEX($B17:$M17,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$M$4,0)))/2),L17),"")</f>
+        <f>IF(ISNUMBER(L17),IFERROR(IF(INDEX($B17:$N17,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$N$4,0))="",L17,(L17+INDEX($B17:$N17,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$N$4,0)))/2),L17),"")</f>
         <v/>
       </c>
       <c r="M110" s="8">
-        <f>IF(ISNUMBER(M17),IFERROR(IF(INDEX($B17:$M17,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$M$4,0))="",M17,(M17+INDEX($B17:$M17,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$M$4,0)))/2),M17),"")</f>
+        <f>IF(ISNUMBER(M17),IFERROR(IF(INDEX($B17:$N17,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$N$4,0))="",M17,(M17+INDEX($B17:$N17,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$N$4,0)))/2),M17),"")</f>
+        <v/>
+      </c>
+      <c r="N110" s="8">
+        <f>IF(ISNUMBER(N17),IFERROR(IF(INDEX($B17:$N17,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$N$4,0))="",N17,(N17+INDEX($B17:$N17,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$N$4,0)))/2),N17),"")</f>
         <v/>
       </c>
     </row>
@@ -39957,51 +40599,55 @@
         </is>
       </c>
       <c r="B111" s="8">
-        <f>IF(ISNUMBER(B13),IFERROR(IF(INDEX($B13:$M13,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$M$4,0))="",B13,(B13+INDEX($B13:$M13,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$M$4,0)))/2),B13),"")</f>
+        <f>IF(ISNUMBER(B13),IFERROR(IF(INDEX($B13:$N13,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$N$4,0))="",B13,(B13+INDEX($B13:$N13,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$N$4,0)))/2),B13),"")</f>
         <v/>
       </c>
       <c r="C111" s="8">
-        <f>IF(ISNUMBER(C13),IFERROR(IF(INDEX($B13:$M13,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$M$4,0))="",C13,(C13+INDEX($B13:$M13,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$M$4,0)))/2),C13),"")</f>
+        <f>IF(ISNUMBER(C13),IFERROR(IF(INDEX($B13:$N13,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$N$4,0))="",C13,(C13+INDEX($B13:$N13,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$N$4,0)))/2),C13),"")</f>
         <v/>
       </c>
       <c r="D111" s="8">
-        <f>IF(ISNUMBER(D13),IFERROR(IF(INDEX($B13:$M13,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$M$4,0))="",D13,(D13+INDEX($B13:$M13,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$M$4,0)))/2),D13),"")</f>
+        <f>IF(ISNUMBER(D13),IFERROR(IF(INDEX($B13:$N13,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$N$4,0))="",D13,(D13+INDEX($B13:$N13,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$N$4,0)))/2),D13),"")</f>
         <v/>
       </c>
       <c r="E111" s="8">
-        <f>IF(ISNUMBER(E13),IFERROR(IF(INDEX($B13:$M13,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$M$4,0))="",E13,(E13+INDEX($B13:$M13,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$M$4,0)))/2),E13),"")</f>
+        <f>IF(ISNUMBER(E13),IFERROR(IF(INDEX($B13:$N13,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$N$4,0))="",E13,(E13+INDEX($B13:$N13,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$N$4,0)))/2),E13),"")</f>
         <v/>
       </c>
       <c r="F111" s="8">
-        <f>IF(ISNUMBER(F13),IFERROR(IF(INDEX($B13:$M13,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$M$4,0))="",F13,(F13+INDEX($B13:$M13,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$M$4,0)))/2),F13),"")</f>
+        <f>IF(ISNUMBER(F13),IFERROR(IF(INDEX($B13:$N13,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$N$4,0))="",F13,(F13+INDEX($B13:$N13,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$N$4,0)))/2),F13),"")</f>
         <v/>
       </c>
       <c r="G111" s="8">
-        <f>IF(ISNUMBER(G13),IFERROR(IF(INDEX($B13:$M13,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$M$4,0))="",G13,(G13+INDEX($B13:$M13,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$M$4,0)))/2),G13),"")</f>
+        <f>IF(ISNUMBER(G13),IFERROR(IF(INDEX($B13:$N13,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$N$4,0))="",G13,(G13+INDEX($B13:$N13,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$N$4,0)))/2),G13),"")</f>
         <v/>
       </c>
       <c r="H111" s="8">
-        <f>IF(ISNUMBER(H13),IFERROR(IF(INDEX($B13:$M13,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$M$4,0))="",H13,(H13+INDEX($B13:$M13,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$M$4,0)))/2),H13),"")</f>
+        <f>IF(ISNUMBER(H13),IFERROR(IF(INDEX($B13:$N13,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$N$4,0))="",H13,(H13+INDEX($B13:$N13,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$N$4,0)))/2),H13),"")</f>
         <v/>
       </c>
       <c r="I111" s="8">
-        <f>IF(ISNUMBER(I13),IFERROR(IF(INDEX($B13:$M13,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$M$4,0))="",I13,(I13+INDEX($B13:$M13,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$M$4,0)))/2),I13),"")</f>
+        <f>IF(ISNUMBER(I13),IFERROR(IF(INDEX($B13:$N13,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$N$4,0))="",I13,(I13+INDEX($B13:$N13,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$N$4,0)))/2),I13),"")</f>
         <v/>
       </c>
       <c r="J111" s="8">
-        <f>IF(ISNUMBER(J13),IFERROR(IF(INDEX($B13:$M13,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$M$4,0))="",J13,(J13+INDEX($B13:$M13,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$M$4,0)))/2),J13),"")</f>
+        <f>IF(ISNUMBER(J13),IFERROR(IF(INDEX($B13:$N13,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$N$4,0))="",J13,(J13+INDEX($B13:$N13,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$N$4,0)))/2),J13),"")</f>
         <v/>
       </c>
       <c r="K111" s="8">
-        <f>IF(ISNUMBER(K13),IFERROR(IF(INDEX($B13:$M13,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$M$4,0))="",K13,(K13+INDEX($B13:$M13,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$M$4,0)))/2),K13),"")</f>
+        <f>IF(ISNUMBER(K13),IFERROR(IF(INDEX($B13:$N13,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$N$4,0))="",K13,(K13+INDEX($B13:$N13,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$N$4,0)))/2),K13),"")</f>
         <v/>
       </c>
       <c r="L111" s="8">
-        <f>IF(ISNUMBER(L13),IFERROR(IF(INDEX($B13:$M13,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$M$4,0))="",L13,(L13+INDEX($B13:$M13,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$M$4,0)))/2),L13),"")</f>
+        <f>IF(ISNUMBER(L13),IFERROR(IF(INDEX($B13:$N13,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$N$4,0))="",L13,(L13+INDEX($B13:$N13,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$N$4,0)))/2),L13),"")</f>
         <v/>
       </c>
       <c r="M111" s="8">
-        <f>IF(ISNUMBER(M13),IFERROR(IF(INDEX($B13:$M13,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$M$4,0))="",M13,(M13+INDEX($B13:$M13,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$M$4,0)))/2),M13),"")</f>
+        <f>IF(ISNUMBER(M13),IFERROR(IF(INDEX($B13:$N13,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$N$4,0))="",M13,(M13+INDEX($B13:$N13,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$N$4,0)))/2),M13),"")</f>
+        <v/>
+      </c>
+      <c r="N111" s="8">
+        <f>IF(ISNUMBER(N13),IFERROR(IF(INDEX($B13:$N13,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$N$4,0))="",N13,(N13+INDEX($B13:$N13,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$N$4,0)))/2),N13),"")</f>
         <v/>
       </c>
     </row>
@@ -40012,51 +40658,55 @@
         </is>
       </c>
       <c r="B112" s="8">
-        <f>IF(ISNUMBER(B38),IFERROR(IF(INDEX($B38:$M38,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$M$4,0))="",B38,(B38+INDEX($B38:$M38,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$M$4,0)))/2),B38),"")</f>
+        <f>IF(ISNUMBER(B38),IFERROR(IF(INDEX($B38:$N38,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$N$4,0))="",B38,(B38+INDEX($B38:$N38,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$N$4,0)))/2),B38),"")</f>
         <v/>
       </c>
       <c r="C112" s="8">
-        <f>IF(ISNUMBER(C38),IFERROR(IF(INDEX($B38:$M38,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$M$4,0))="",C38,(C38+INDEX($B38:$M38,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$M$4,0)))/2),C38),"")</f>
+        <f>IF(ISNUMBER(C38),IFERROR(IF(INDEX($B38:$N38,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$N$4,0))="",C38,(C38+INDEX($B38:$N38,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$N$4,0)))/2),C38),"")</f>
         <v/>
       </c>
       <c r="D112" s="8">
-        <f>IF(ISNUMBER(D38),IFERROR(IF(INDEX($B38:$M38,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$M$4,0))="",D38,(D38+INDEX($B38:$M38,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$M$4,0)))/2),D38),"")</f>
+        <f>IF(ISNUMBER(D38),IFERROR(IF(INDEX($B38:$N38,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$N$4,0))="",D38,(D38+INDEX($B38:$N38,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$N$4,0)))/2),D38),"")</f>
         <v/>
       </c>
       <c r="E112" s="8">
-        <f>IF(ISNUMBER(E38),IFERROR(IF(INDEX($B38:$M38,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$M$4,0))="",E38,(E38+INDEX($B38:$M38,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$M$4,0)))/2),E38),"")</f>
+        <f>IF(ISNUMBER(E38),IFERROR(IF(INDEX($B38:$N38,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$N$4,0))="",E38,(E38+INDEX($B38:$N38,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$N$4,0)))/2),E38),"")</f>
         <v/>
       </c>
       <c r="F112" s="8">
-        <f>IF(ISNUMBER(F38),IFERROR(IF(INDEX($B38:$M38,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$M$4,0))="",F38,(F38+INDEX($B38:$M38,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$M$4,0)))/2),F38),"")</f>
+        <f>IF(ISNUMBER(F38),IFERROR(IF(INDEX($B38:$N38,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$N$4,0))="",F38,(F38+INDEX($B38:$N38,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$N$4,0)))/2),F38),"")</f>
         <v/>
       </c>
       <c r="G112" s="8">
-        <f>IF(ISNUMBER(G38),IFERROR(IF(INDEX($B38:$M38,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$M$4,0))="",G38,(G38+INDEX($B38:$M38,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$M$4,0)))/2),G38),"")</f>
+        <f>IF(ISNUMBER(G38),IFERROR(IF(INDEX($B38:$N38,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$N$4,0))="",G38,(G38+INDEX($B38:$N38,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$N$4,0)))/2),G38),"")</f>
         <v/>
       </c>
       <c r="H112" s="8">
-        <f>IF(ISNUMBER(H38),IFERROR(IF(INDEX($B38:$M38,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$M$4,0))="",H38,(H38+INDEX($B38:$M38,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$M$4,0)))/2),H38),"")</f>
+        <f>IF(ISNUMBER(H38),IFERROR(IF(INDEX($B38:$N38,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$N$4,0))="",H38,(H38+INDEX($B38:$N38,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$N$4,0)))/2),H38),"")</f>
         <v/>
       </c>
       <c r="I112" s="8">
-        <f>IF(ISNUMBER(I38),IFERROR(IF(INDEX($B38:$M38,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$M$4,0))="",I38,(I38+INDEX($B38:$M38,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$M$4,0)))/2),I38),"")</f>
+        <f>IF(ISNUMBER(I38),IFERROR(IF(INDEX($B38:$N38,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$N$4,0))="",I38,(I38+INDEX($B38:$N38,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$N$4,0)))/2),I38),"")</f>
         <v/>
       </c>
       <c r="J112" s="8">
-        <f>IF(ISNUMBER(J38),IFERROR(IF(INDEX($B38:$M38,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$M$4,0))="",J38,(J38+INDEX($B38:$M38,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$M$4,0)))/2),J38),"")</f>
+        <f>IF(ISNUMBER(J38),IFERROR(IF(INDEX($B38:$N38,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$N$4,0))="",J38,(J38+INDEX($B38:$N38,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$N$4,0)))/2),J38),"")</f>
         <v/>
       </c>
       <c r="K112" s="8">
-        <f>IF(ISNUMBER(K38),IFERROR(IF(INDEX($B38:$M38,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$M$4,0))="",K38,(K38+INDEX($B38:$M38,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$M$4,0)))/2),K38),"")</f>
+        <f>IF(ISNUMBER(K38),IFERROR(IF(INDEX($B38:$N38,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$N$4,0))="",K38,(K38+INDEX($B38:$N38,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$N$4,0)))/2),K38),"")</f>
         <v/>
       </c>
       <c r="L112" s="8">
-        <f>IF(ISNUMBER(L38),IFERROR(IF(INDEX($B38:$M38,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$M$4,0))="",L38,(L38+INDEX($B38:$M38,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$M$4,0)))/2),L38),"")</f>
+        <f>IF(ISNUMBER(L38),IFERROR(IF(INDEX($B38:$N38,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$N$4,0))="",L38,(L38+INDEX($B38:$N38,MATCH(DATE(YEAR(L$4)-1,12,31),$B$4:$N$4,0)))/2),L38),"")</f>
         <v/>
       </c>
       <c r="M112" s="8">
-        <f>IF(ISNUMBER(M38),IFERROR(IF(INDEX($B38:$M38,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$M$4,0))="",M38,(M38+INDEX($B38:$M38,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$M$4,0)))/2),M38),"")</f>
+        <f>IF(ISNUMBER(M38),IFERROR(IF(INDEX($B38:$N38,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$N$4,0))="",M38,(M38+INDEX($B38:$N38,MATCH(DATE(YEAR(M$4)-1,12,31),$B$4:$N$4,0)))/2),M38),"")</f>
+        <v/>
+      </c>
+      <c r="N112" s="8">
+        <f>IF(ISNUMBER(N38),IFERROR(IF(INDEX($B38:$N38,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$N$4,0))="",N38,(N38+INDEX($B38:$N38,MATCH(DATE(YEAR(N$4)-1,12,31),$B$4:$N$4,0)))/2),N38),"")</f>
         <v/>
       </c>
     </row>
@@ -40121,6 +40771,10 @@
         <f>IF(AND(ISNUMBER(M73),ISNUMBER(M71)),IFERROR((M73)/(M71),""),"")</f>
         <v/>
       </c>
+      <c r="N115" s="16">
+        <f>IF(AND(ISNUMBER(N73),ISNUMBER(N71)),IFERROR((N73)/(N71),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -40176,6 +40830,10 @@
         <f>IF(AND(ISNUMBER(M72),ISNUMBER(M71)),IFERROR((M72)/(M71),""),"")</f>
         <v/>
       </c>
+      <c r="N116" s="16">
+        <f>IF(AND(ISNUMBER(N72),ISNUMBER(N71)),IFERROR((N72)/(N71),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -40231,6 +40889,10 @@
         <f>IF(AND(ISNUMBER(M79),ISNUMBER(M71)),IFERROR((M79)/(M71),""),"")</f>
         <v/>
       </c>
+      <c r="N117" s="16">
+        <f>IF(AND(ISNUMBER(N79),ISNUMBER(N71)),IFERROR((N79)/(N71),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -40286,6 +40948,10 @@
         <f>IF(AND(ISNUMBER(M80),ISNUMBER(M71)),IFERROR((M80)/(M71),""),"")</f>
         <v/>
       </c>
+      <c r="N118" s="16">
+        <f>IF(AND(ISNUMBER(N80),ISNUMBER(N71)),IFERROR((N80)/(N71),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -40341,6 +41007,10 @@
         <f>IF(AND(ISNUMBER(M94),ISNUMBER(M71)),IFERROR((M94)/(M71),""),"")</f>
         <v/>
       </c>
+      <c r="N119" s="16">
+        <f>IF(AND(ISNUMBER(N94),ISNUMBER(N71)),IFERROR((N94)/(N71),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -40396,6 +41066,10 @@
         <f>IF(AND(ISNUMBER(M94),ISNUMBER(M107),ISNUMBER(M108)),IFERROR((M94*M107)/(M108),""),"")</f>
         <v/>
       </c>
+      <c r="N120" s="16">
+        <f>IF(AND(ISNUMBER(N94),ISNUMBER(N107),ISNUMBER(N108)),IFERROR((N94*N107)/(N108),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -40451,6 +41125,10 @@
         <f>IF(AND(ISNUMBER(M94),ISNUMBER(M107),ISNUMBER(M109)),IFERROR((M94*M107)/(M109),""),"")</f>
         <v/>
       </c>
+      <c r="N121" s="16">
+        <f>IF(AND(ISNUMBER(N94),ISNUMBER(N107),ISNUMBER(N109)),IFERROR((N94*N107)/(N109),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="14" t="inlineStr">
@@ -40513,6 +41191,10 @@
         <f>IF(AND(ISNUMBER(M108),ISNUMBER(M71),ISNUMBER(M107)),IFERROR(M71*M107/M108,""),"")</f>
         <v/>
       </c>
+      <c r="N124" s="17">
+        <f>IF(AND(ISNUMBER(N108),ISNUMBER(N71),ISNUMBER(N107)),IFERROR(N71*N107/N108,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -40568,6 +41250,10 @@
         <f>IF(AND(ISNUMBER(M108),ISNUMBER(M109)),IFERROR((M108)/(M109),""),"")</f>
         <v/>
       </c>
+      <c r="N125" s="17">
+        <f>IF(AND(ISNUMBER(N108),ISNUMBER(N109)),IFERROR((N108)/(N109),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -40623,6 +41309,10 @@
         <f>IF(AND(ISNUMBER(M119),ISNUMBER(M124),ISNUMBER(M125)),IFERROR(M119*M124*M125,""),"")</f>
         <v/>
       </c>
+      <c r="N126" s="16">
+        <f>IF(AND(ISNUMBER(N119),ISNUMBER(N124),ISNUMBER(N125)),IFERROR(N119*N124*N125,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
@@ -40685,6 +41375,10 @@
         <f>IF(AND(ISNUMBER(M22),ISNUMBER(M49)),IFERROR((M22)/(M49),""),"")</f>
         <v/>
       </c>
+      <c r="N129" s="17">
+        <f>IF(AND(ISNUMBER(N22),ISNUMBER(N49)),IFERROR((N22)/(N49),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -40740,6 +41434,10 @@
         <f>IF(AND(ISNUMBER(M22),ISNUMBER(M17),ISNUMBER(M49)),IFERROR((M22-M17)/M49,""),"")</f>
         <v/>
       </c>
+      <c r="N130" s="17">
+        <f>IF(AND(ISNUMBER(N22),ISNUMBER(N17),ISNUMBER(N49)),IFERROR((N22-N17)/N49,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -40795,6 +41493,10 @@
         <f>IF(AND(ISNUMBER(M12),ISNUMBER(M49)),IFERROR((M12)/(M49),""),"")</f>
         <v/>
       </c>
+      <c r="N131" s="17">
+        <f>IF(AND(ISNUMBER(N12),ISNUMBER(N49)),IFERROR((N12)/(N49),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -40850,6 +41552,10 @@
         <f>IF(AND(ISNUMBER(M22),ISNUMBER(M49)),IFERROR((M22-M49)/1000,""),"")</f>
         <v/>
       </c>
+      <c r="N132" s="8">
+        <f>IF(AND(ISNUMBER(N22),ISNUMBER(N49)),IFERROR((N22-N49)/1000,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
@@ -40912,6 +41618,10 @@
         <f>IF(AND(ISNUMBER(M57),ISNUMBER(M68)),IFERROR((M57)/(M68),""),"")</f>
         <v/>
       </c>
+      <c r="N135" s="17">
+        <f>IF(AND(ISNUMBER(N57),ISNUMBER(N68)),IFERROR((N57)/(N68),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -40967,6 +41677,10 @@
         <f>IF(AND(ISNUMBER(M57),ISNUMBER(M36)),IFERROR((M57)/(M36),""),"")</f>
         <v/>
       </c>
+      <c r="N136" s="16">
+        <f>IF(AND(ISNUMBER(N57),ISNUMBER(N36)),IFERROR((N57)/(N36),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -41022,6 +41736,10 @@
         <f>IF(AND(ISNUMBER(M90),ISNUMBER(M81)),IFERROR((M90+ABS(M81))/ABS(M81),""),"")</f>
         <v/>
       </c>
+      <c r="N137" s="17">
+        <f>IF(AND(ISNUMBER(N90),ISNUMBER(N81)),IFERROR((N90+ABS(N81))/ABS(N81),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="14" t="inlineStr">
@@ -41084,6 +41802,10 @@
         <f>IF(AND(ISNUMBER(M110),ISNUMBER(M72),ISNUMBER(M107)),IFERROR(M72*M107/M110,""),"")</f>
         <v/>
       </c>
+      <c r="N140" s="17">
+        <f>IF(AND(ISNUMBER(N110),ISNUMBER(N72),ISNUMBER(N107)),IFERROR(N72*N107/N110,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -41139,6 +41861,10 @@
         <f>IF(AND(ISNUMBER(M110),ISNUMBER(M72),ISNUMBER(M107)),IFERROR(M110/(M72*M107)*365,""),"")</f>
         <v/>
       </c>
+      <c r="N141" s="18">
+        <f>IF(AND(ISNUMBER(N110),ISNUMBER(N72),ISNUMBER(N107)),IFERROR(N110/(N72*N107)*365,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -41194,6 +41920,10 @@
         <f>IF(AND(ISNUMBER(M111),ISNUMBER(M71),ISNUMBER(M107)),IFERROR(M71*M107/M111,""),"")</f>
         <v/>
       </c>
+      <c r="N142" s="17">
+        <f>IF(AND(ISNUMBER(N111),ISNUMBER(N71),ISNUMBER(N107)),IFERROR(N71*N107/N111,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -41249,6 +41979,10 @@
         <f>IF(AND(ISNUMBER(M111),ISNUMBER(M71),ISNUMBER(M107)),IFERROR(M111/(M71*M107)*365,""),"")</f>
         <v/>
       </c>
+      <c r="N143" s="18">
+        <f>IF(AND(ISNUMBER(N111),ISNUMBER(N71),ISNUMBER(N107)),IFERROR(N111/(N71*N107)*365,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -41304,6 +42038,10 @@
         <f>IF(AND(ISNUMBER(M112),ISNUMBER(M72),ISNUMBER(M107)),IFERROR(M72*M107/M112,""),"")</f>
         <v/>
       </c>
+      <c r="N144" s="17">
+        <f>IF(AND(ISNUMBER(N112),ISNUMBER(N72),ISNUMBER(N107)),IFERROR(N72*N107/N112,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -41359,6 +42097,10 @@
         <f>IF(AND(ISNUMBER(M112),ISNUMBER(M72),ISNUMBER(M107)),IFERROR(M112/(M72*M107)*365,""),"")</f>
         <v/>
       </c>
+      <c r="N145" s="18">
+        <f>IF(AND(ISNUMBER(N112),ISNUMBER(N72),ISNUMBER(N107)),IFERROR(N112/(N72*N107)*365,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -41414,6 +42156,10 @@
         <f>IF(AND(ISNUMBER(M141),ISNUMBER(M143),ISNUMBER(M145)),IFERROR(M141+M143-M145,""),"")</f>
         <v/>
       </c>
+      <c r="N146" s="18">
+        <f>IF(AND(ISNUMBER(N141),ISNUMBER(N143),ISNUMBER(N145)),IFERROR(N141+N143-N145,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
@@ -41429,51 +42175,55 @@
         </is>
       </c>
       <c r="B149" s="16">
-        <f>IF(ISNUMBER(B71),IFERROR(IF(INDEX($B71:$M71,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$M$4,0))&gt;0,B71/INDEX($B71:$M71,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(B71),IFERROR(IF(INDEX($B71:$N71,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$N$4,0))&gt;0,B71/INDEX($B71:$N71,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="C149" s="16">
-        <f>IF(ISNUMBER(C71),IFERROR(IF(INDEX($B71:$M71,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$M$4,0))&gt;0,C71/INDEX($B71:$M71,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(C71),IFERROR(IF(INDEX($B71:$N71,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$N$4,0))&gt;0,C71/INDEX($B71:$N71,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="D149" s="16">
-        <f>IF(ISNUMBER(D71),IFERROR(IF(INDEX($B71:$M71,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$M$4,0))&gt;0,D71/INDEX($B71:$M71,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(D71),IFERROR(IF(INDEX($B71:$N71,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$N$4,0))&gt;0,D71/INDEX($B71:$N71,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="E149" s="16">
-        <f>IF(ISNUMBER(E71),IFERROR(IF(INDEX($B71:$M71,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$M$4,0))&gt;0,E71/INDEX($B71:$M71,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(E71),IFERROR(IF(INDEX($B71:$N71,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$N$4,0))&gt;0,E71/INDEX($B71:$N71,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="F149" s="16">
-        <f>IF(ISNUMBER(F71),IFERROR(IF(INDEX($B71:$M71,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$M$4,0))&gt;0,F71/INDEX($B71:$M71,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(F71),IFERROR(IF(INDEX($B71:$N71,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$N$4,0))&gt;0,F71/INDEX($B71:$N71,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="G149" s="16">
-        <f>IF(ISNUMBER(G71),IFERROR(IF(INDEX($B71:$M71,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$M$4,0))&gt;0,G71/INDEX($B71:$M71,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(G71),IFERROR(IF(INDEX($B71:$N71,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$N$4,0))&gt;0,G71/INDEX($B71:$N71,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="H149" s="16">
-        <f>IF(ISNUMBER(H71),IFERROR(IF(INDEX($B71:$M71,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$M$4,0))&gt;0,H71/INDEX($B71:$M71,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(H71),IFERROR(IF(INDEX($B71:$N71,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$N$4,0))&gt;0,H71/INDEX($B71:$N71,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="I149" s="16">
-        <f>IF(ISNUMBER(I71),IFERROR(IF(INDEX($B71:$M71,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$M$4,0))&gt;0,I71/INDEX($B71:$M71,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(I71),IFERROR(IF(INDEX($B71:$N71,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$N$4,0))&gt;0,I71/INDEX($B71:$N71,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="J149" s="16">
-        <f>IF(ISNUMBER(J71),IFERROR(IF(INDEX($B71:$M71,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$M$4,0))&gt;0,J71/INDEX($B71:$M71,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(J71),IFERROR(IF(INDEX($B71:$N71,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$N$4,0))&gt;0,J71/INDEX($B71:$N71,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="K149" s="16">
-        <f>IF(ISNUMBER(K71),IFERROR(IF(INDEX($B71:$M71,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$M$4,0))&gt;0,K71/INDEX($B71:$M71,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(K71),IFERROR(IF(INDEX($B71:$N71,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$N$4,0))&gt;0,K71/INDEX($B71:$N71,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="L149" s="16">
-        <f>IF(ISNUMBER(L71),IFERROR(IF(INDEX($B71:$M71,MATCH(DATE(YEAR(L$4)-1,MONTH(L$4),DAY(L$4)),$B$4:$M$4,0))&gt;0,L71/INDEX($B71:$M71,MATCH(DATE(YEAR(L$4)-1,MONTH(L$4),DAY(L$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(L71),IFERROR(IF(INDEX($B71:$N71,MATCH(DATE(YEAR(L$4)-1,MONTH(L$4),DAY(L$4)),$B$4:$N$4,0))&gt;0,L71/INDEX($B71:$N71,MATCH(DATE(YEAR(L$4)-1,MONTH(L$4),DAY(L$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="M149" s="16">
-        <f>IF(ISNUMBER(M71),IFERROR(IF(INDEX($B71:$M71,MATCH(DATE(YEAR(M$4)-1,MONTH(M$4),DAY(M$4)),$B$4:$M$4,0))&gt;0,M71/INDEX($B71:$M71,MATCH(DATE(YEAR(M$4)-1,MONTH(M$4),DAY(M$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(M71),IFERROR(IF(INDEX($B71:$N71,MATCH(DATE(YEAR(M$4)-1,MONTH(M$4),DAY(M$4)),$B$4:$N$4,0))&gt;0,M71/INDEX($B71:$N71,MATCH(DATE(YEAR(M$4)-1,MONTH(M$4),DAY(M$4)),$B$4:$N$4,0))-1,""),""),"")</f>
+        <v/>
+      </c>
+      <c r="N149" s="16">
+        <f>IF(ISNUMBER(N71),IFERROR(IF(INDEX($B71:$N71,MATCH(DATE(YEAR(N$4)-1,MONTH(N$4),DAY(N$4)),$B$4:$N$4,0))&gt;0,N71/INDEX($B71:$N71,MATCH(DATE(YEAR(N$4)-1,MONTH(N$4),DAY(N$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
     </row>
@@ -41484,51 +42234,55 @@
         </is>
       </c>
       <c r="B150" s="16">
-        <f>IF(ISNUMBER(B73),IFERROR(IF(INDEX($B73:$M73,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$M$4,0))&gt;0,B73/INDEX($B73:$M73,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(B73),IFERROR(IF(INDEX($B73:$N73,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$N$4,0))&gt;0,B73/INDEX($B73:$N73,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="C150" s="16">
-        <f>IF(ISNUMBER(C73),IFERROR(IF(INDEX($B73:$M73,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$M$4,0))&gt;0,C73/INDEX($B73:$M73,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(C73),IFERROR(IF(INDEX($B73:$N73,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$N$4,0))&gt;0,C73/INDEX($B73:$N73,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="D150" s="16">
-        <f>IF(ISNUMBER(D73),IFERROR(IF(INDEX($B73:$M73,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$M$4,0))&gt;0,D73/INDEX($B73:$M73,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(D73),IFERROR(IF(INDEX($B73:$N73,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$N$4,0))&gt;0,D73/INDEX($B73:$N73,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="E150" s="16">
-        <f>IF(ISNUMBER(E73),IFERROR(IF(INDEX($B73:$M73,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$M$4,0))&gt;0,E73/INDEX($B73:$M73,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(E73),IFERROR(IF(INDEX($B73:$N73,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$N$4,0))&gt;0,E73/INDEX($B73:$N73,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="F150" s="16">
-        <f>IF(ISNUMBER(F73),IFERROR(IF(INDEX($B73:$M73,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$M$4,0))&gt;0,F73/INDEX($B73:$M73,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(F73),IFERROR(IF(INDEX($B73:$N73,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$N$4,0))&gt;0,F73/INDEX($B73:$N73,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="G150" s="16">
-        <f>IF(ISNUMBER(G73),IFERROR(IF(INDEX($B73:$M73,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$M$4,0))&gt;0,G73/INDEX($B73:$M73,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(G73),IFERROR(IF(INDEX($B73:$N73,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$N$4,0))&gt;0,G73/INDEX($B73:$N73,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="H150" s="16">
-        <f>IF(ISNUMBER(H73),IFERROR(IF(INDEX($B73:$M73,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$M$4,0))&gt;0,H73/INDEX($B73:$M73,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(H73),IFERROR(IF(INDEX($B73:$N73,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$N$4,0))&gt;0,H73/INDEX($B73:$N73,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="I150" s="16">
-        <f>IF(ISNUMBER(I73),IFERROR(IF(INDEX($B73:$M73,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$M$4,0))&gt;0,I73/INDEX($B73:$M73,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(I73),IFERROR(IF(INDEX($B73:$N73,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$N$4,0))&gt;0,I73/INDEX($B73:$N73,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="J150" s="16">
-        <f>IF(ISNUMBER(J73),IFERROR(IF(INDEX($B73:$M73,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$M$4,0))&gt;0,J73/INDEX($B73:$M73,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(J73),IFERROR(IF(INDEX($B73:$N73,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$N$4,0))&gt;0,J73/INDEX($B73:$N73,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="K150" s="16">
-        <f>IF(ISNUMBER(K73),IFERROR(IF(INDEX($B73:$M73,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$M$4,0))&gt;0,K73/INDEX($B73:$M73,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(K73),IFERROR(IF(INDEX($B73:$N73,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$N$4,0))&gt;0,K73/INDEX($B73:$N73,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="L150" s="16">
-        <f>IF(ISNUMBER(L73),IFERROR(IF(INDEX($B73:$M73,MATCH(DATE(YEAR(L$4)-1,MONTH(L$4),DAY(L$4)),$B$4:$M$4,0))&gt;0,L73/INDEX($B73:$M73,MATCH(DATE(YEAR(L$4)-1,MONTH(L$4),DAY(L$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(L73),IFERROR(IF(INDEX($B73:$N73,MATCH(DATE(YEAR(L$4)-1,MONTH(L$4),DAY(L$4)),$B$4:$N$4,0))&gt;0,L73/INDEX($B73:$N73,MATCH(DATE(YEAR(L$4)-1,MONTH(L$4),DAY(L$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="M150" s="16">
-        <f>IF(ISNUMBER(M73),IFERROR(IF(INDEX($B73:$M73,MATCH(DATE(YEAR(M$4)-1,MONTH(M$4),DAY(M$4)),$B$4:$M$4,0))&gt;0,M73/INDEX($B73:$M73,MATCH(DATE(YEAR(M$4)-1,MONTH(M$4),DAY(M$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(M73),IFERROR(IF(INDEX($B73:$N73,MATCH(DATE(YEAR(M$4)-1,MONTH(M$4),DAY(M$4)),$B$4:$N$4,0))&gt;0,M73/INDEX($B73:$N73,MATCH(DATE(YEAR(M$4)-1,MONTH(M$4),DAY(M$4)),$B$4:$N$4,0))-1,""),""),"")</f>
+        <v/>
+      </c>
+      <c r="N150" s="16">
+        <f>IF(ISNUMBER(N73),IFERROR(IF(INDEX($B73:$N73,MATCH(DATE(YEAR(N$4)-1,MONTH(N$4),DAY(N$4)),$B$4:$N$4,0))&gt;0,N73/INDEX($B73:$N73,MATCH(DATE(YEAR(N$4)-1,MONTH(N$4),DAY(N$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
     </row>
@@ -41539,51 +42293,55 @@
         </is>
       </c>
       <c r="B151" s="16">
-        <f>IF(ISNUMBER(B94),IFERROR(IF(INDEX($B94:$M94,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$M$4,0))&gt;0,B94/INDEX($B94:$M94,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(B94),IFERROR(IF(INDEX($B94:$N94,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$N$4,0))&gt;0,B94/INDEX($B94:$N94,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="C151" s="16">
-        <f>IF(ISNUMBER(C94),IFERROR(IF(INDEX($B94:$M94,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$M$4,0))&gt;0,C94/INDEX($B94:$M94,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(C94),IFERROR(IF(INDEX($B94:$N94,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$N$4,0))&gt;0,C94/INDEX($B94:$N94,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="D151" s="16">
-        <f>IF(ISNUMBER(D94),IFERROR(IF(INDEX($B94:$M94,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$M$4,0))&gt;0,D94/INDEX($B94:$M94,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(D94),IFERROR(IF(INDEX($B94:$N94,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$N$4,0))&gt;0,D94/INDEX($B94:$N94,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="E151" s="16">
-        <f>IF(ISNUMBER(E94),IFERROR(IF(INDEX($B94:$M94,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$M$4,0))&gt;0,E94/INDEX($B94:$M94,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(E94),IFERROR(IF(INDEX($B94:$N94,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$N$4,0))&gt;0,E94/INDEX($B94:$N94,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="F151" s="16">
-        <f>IF(ISNUMBER(F94),IFERROR(IF(INDEX($B94:$M94,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$M$4,0))&gt;0,F94/INDEX($B94:$M94,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(F94),IFERROR(IF(INDEX($B94:$N94,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$N$4,0))&gt;0,F94/INDEX($B94:$N94,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="G151" s="16">
-        <f>IF(ISNUMBER(G94),IFERROR(IF(INDEX($B94:$M94,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$M$4,0))&gt;0,G94/INDEX($B94:$M94,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(G94),IFERROR(IF(INDEX($B94:$N94,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$N$4,0))&gt;0,G94/INDEX($B94:$N94,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="H151" s="16">
-        <f>IF(ISNUMBER(H94),IFERROR(IF(INDEX($B94:$M94,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$M$4,0))&gt;0,H94/INDEX($B94:$M94,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(H94),IFERROR(IF(INDEX($B94:$N94,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$N$4,0))&gt;0,H94/INDEX($B94:$N94,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="I151" s="16">
-        <f>IF(ISNUMBER(I94),IFERROR(IF(INDEX($B94:$M94,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$M$4,0))&gt;0,I94/INDEX($B94:$M94,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(I94),IFERROR(IF(INDEX($B94:$N94,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$N$4,0))&gt;0,I94/INDEX($B94:$N94,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="J151" s="16">
-        <f>IF(ISNUMBER(J94),IFERROR(IF(INDEX($B94:$M94,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$M$4,0))&gt;0,J94/INDEX($B94:$M94,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(J94),IFERROR(IF(INDEX($B94:$N94,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$N$4,0))&gt;0,J94/INDEX($B94:$N94,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="K151" s="16">
-        <f>IF(ISNUMBER(K94),IFERROR(IF(INDEX($B94:$M94,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$M$4,0))&gt;0,K94/INDEX($B94:$M94,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(K94),IFERROR(IF(INDEX($B94:$N94,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$N$4,0))&gt;0,K94/INDEX($B94:$N94,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="L151" s="16">
-        <f>IF(ISNUMBER(L94),IFERROR(IF(INDEX($B94:$M94,MATCH(DATE(YEAR(L$4)-1,MONTH(L$4),DAY(L$4)),$B$4:$M$4,0))&gt;0,L94/INDEX($B94:$M94,MATCH(DATE(YEAR(L$4)-1,MONTH(L$4),DAY(L$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(L94),IFERROR(IF(INDEX($B94:$N94,MATCH(DATE(YEAR(L$4)-1,MONTH(L$4),DAY(L$4)),$B$4:$N$4,0))&gt;0,L94/INDEX($B94:$N94,MATCH(DATE(YEAR(L$4)-1,MONTH(L$4),DAY(L$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="M151" s="16">
-        <f>IF(ISNUMBER(M94),IFERROR(IF(INDEX($B94:$M94,MATCH(DATE(YEAR(M$4)-1,MONTH(M$4),DAY(M$4)),$B$4:$M$4,0))&gt;0,M94/INDEX($B94:$M94,MATCH(DATE(YEAR(M$4)-1,MONTH(M$4),DAY(M$4)),$B$4:$M$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(M94),IFERROR(IF(INDEX($B94:$N94,MATCH(DATE(YEAR(M$4)-1,MONTH(M$4),DAY(M$4)),$B$4:$N$4,0))&gt;0,M94/INDEX($B94:$N94,MATCH(DATE(YEAR(M$4)-1,MONTH(M$4),DAY(M$4)),$B$4:$N$4,0))-1,""),""),"")</f>
+        <v/>
+      </c>
+      <c r="N151" s="16">
+        <f>IF(ISNUMBER(N94),IFERROR(IF(INDEX($B94:$N94,MATCH(DATE(YEAR(N$4)-1,MONTH(N$4),DAY(N$4)),$B$4:$N$4,0))&gt;0,N94/INDEX($B94:$N94,MATCH(DATE(YEAR(N$4)-1,MONTH(N$4),DAY(N$4)),$B$4:$N$4,0))-1,""),""),"")</f>
         <v/>
       </c>
     </row>
@@ -41598,7 +42356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J151"/>
+  <dimension ref="A1:K151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -41611,6 +42369,7 @@
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -41652,12 +42411,15 @@
         <v>45657</v>
       </c>
       <c r="H4" s="4" t="n">
+        <v>45838</v>
+      </c>
+      <c r="I4" s="4" t="n">
         <v>45930</v>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="J4" s="4" t="n">
         <v>46022</v>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="K4" s="4" t="n">
         <v>46203</v>
       </c>
     </row>
@@ -41699,15 +42461,20 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
+          <t>2025 Q2</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
           <t>2025 Q3</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>2025 Q4</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>2026 Q2</t>
         </is>
@@ -41738,12 +42505,15 @@
         <v>12</v>
       </c>
       <c r="H6" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="J6" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="K6" s="5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -41759,9 +42529,12 @@
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="n"/>
       <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
+      <c r="H7" s="4" t="n">
+        <v>45870</v>
+      </c>
       <c r="I7" s="4" t="n"/>
       <c r="J7" s="4" t="n"/>
+      <c r="K7" s="4" t="n"/>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -41801,15 +42574,20 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
+          <t>728ce6bd-_565_20252report.pdf</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
           <t>GAZR 565 20253report.xls</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>GAZR 565 20254.xls</t>
         </is>
       </c>
-      <c r="J8" s="6" t="inlineStr">
+      <c r="K8" s="6" t="inlineStr">
         <is>
           <t>GAZR 56520262report.xlsx</t>
         </is>
@@ -41834,6 +42612,7 @@
       <c r="H9" s="6" t="inlineStr"/>
       <c r="I9" s="6" t="inlineStr"/>
       <c r="J9" s="6" t="inlineStr"/>
+      <c r="K9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -41850,6 +42629,7 @@
       <c r="H10" s="7" t="n"/>
       <c r="I10" s="7" t="n"/>
       <c r="J10" s="7" t="n"/>
+      <c r="K10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -41866,6 +42646,7 @@
       <c r="H11" s="7" t="n"/>
       <c r="I11" s="7" t="n"/>
       <c r="J11" s="7" t="n"/>
+      <c r="K11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -41892,12 +42673,15 @@
         <v>5883196.5</v>
       </c>
       <c r="H12" s="8" t="n">
+        <v>6210238.76</v>
+      </c>
+      <c r="I12" s="8" t="n">
         <v>4946752.09</v>
       </c>
-      <c r="I12" s="8" t="n">
+      <c r="J12" s="8" t="n">
         <v>4024069.91</v>
       </c>
-      <c r="J12" s="8" t="n">
+      <c r="K12" s="8" t="n">
         <v>4851655</v>
       </c>
     </row>
@@ -41926,12 +42710,15 @@
         <v>5717493.02</v>
       </c>
       <c r="H13" s="8" t="n">
+        <v>6362483.22</v>
+      </c>
+      <c r="I13" s="8" t="n">
         <v>5707239.06</v>
       </c>
-      <c r="I13" s="8" t="n">
+      <c r="J13" s="8" t="n">
         <v>7194286.12</v>
       </c>
-      <c r="J13" s="8" t="n">
+      <c r="K13" s="8" t="n">
         <v>7299692.31</v>
       </c>
     </row>
@@ -41960,12 +42747,15 @@
         <v>3981.32</v>
       </c>
       <c r="H14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="8" t="n">
         <v>256645.87</v>
       </c>
-      <c r="I14" s="8" t="n">
+      <c r="J14" s="8" t="n">
         <v>10172.36</v>
       </c>
-      <c r="J14" s="8" t="n">
+      <c r="K14" s="8" t="n">
         <v>42.64</v>
       </c>
     </row>
@@ -41994,12 +42784,15 @@
         <v>936594.73</v>
       </c>
       <c r="H15" s="8" t="n">
+        <v>923179.6</v>
+      </c>
+      <c r="I15" s="8" t="n">
         <v>535999.17</v>
       </c>
-      <c r="I15" s="8" t="n">
+      <c r="J15" s="8" t="n">
         <v>405448.17</v>
       </c>
-      <c r="J15" s="8" t="n">
+      <c r="K15" s="8" t="n">
         <v>500271.78</v>
       </c>
     </row>
@@ -42018,7 +42811,10 @@
       <c r="G16" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="8" t="n">
+      <c r="H16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42047,12 +42843,15 @@
         <v>12427270.3</v>
       </c>
       <c r="H17" s="8" t="n">
+        <v>12878565.95</v>
+      </c>
+      <c r="I17" s="8" t="n">
         <v>14368457.18</v>
       </c>
-      <c r="I17" s="8" t="n">
+      <c r="J17" s="8" t="n">
         <v>14933492.52</v>
       </c>
-      <c r="J17" s="8" t="n">
+      <c r="K17" s="8" t="n">
         <v>14022006.57</v>
       </c>
     </row>
@@ -42081,12 +42880,15 @@
         <v>5905084.2</v>
       </c>
       <c r="H18" s="8" t="n">
+        <v>7285386.14</v>
+      </c>
+      <c r="I18" s="8" t="n">
         <v>4563029.74</v>
       </c>
-      <c r="I18" s="8" t="n">
+      <c r="J18" s="8" t="n">
         <v>4722987.31</v>
       </c>
-      <c r="J18" s="8" t="n">
+      <c r="K18" s="8" t="n">
         <v>3877658.99</v>
       </c>
     </row>
@@ -42114,6 +42916,9 @@
       <c r="J19" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="K19" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -42139,6 +42944,9 @@
       <c r="J20" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="K20" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -42172,12 +42980,15 @@
         <v>30873027.94</v>
       </c>
       <c r="H22" s="10" t="n">
+        <v>33659853.67</v>
+      </c>
+      <c r="I22" s="10" t="n">
         <v>30378123.12</v>
       </c>
-      <c r="I22" s="10" t="n">
+      <c r="J22" s="10" t="n">
         <v>31290456.39</v>
       </c>
-      <c r="J22" s="10" t="n">
+      <c r="K22" s="10" t="n">
         <v>30551327.3</v>
       </c>
     </row>
@@ -42196,6 +43007,7 @@
       <c r="H23" s="7" t="n"/>
       <c r="I23" s="7" t="n"/>
       <c r="J23" s="7" t="n"/>
+      <c r="K23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -42222,12 +43034,15 @@
         <v>22542740.98</v>
       </c>
       <c r="H24" s="8" t="n">
+        <v>23200607.66</v>
+      </c>
+      <c r="I24" s="8" t="n">
         <v>23519847.95</v>
       </c>
-      <c r="I24" s="8" t="n">
+      <c r="J24" s="8" t="n">
         <v>23676541.66</v>
       </c>
-      <c r="J24" s="8" t="n">
+      <c r="K24" s="8" t="n">
         <v>23994411.85</v>
       </c>
     </row>
@@ -42256,12 +43071,15 @@
         <v>3319751.99</v>
       </c>
       <c r="H25" s="8" t="n">
+        <v>3315816.39</v>
+      </c>
+      <c r="I25" s="8" t="n">
         <v>3318132.97</v>
       </c>
-      <c r="I25" s="8" t="n">
+      <c r="J25" s="8" t="n">
         <v>3316695.63</v>
       </c>
-      <c r="J25" s="8" t="n">
+      <c r="K25" s="8" t="n">
         <v>3312903.32</v>
       </c>
     </row>
@@ -42280,7 +43098,10 @@
       <c r="G26" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="8" t="n">
+      <c r="H26" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42299,7 +43120,10 @@
       <c r="G27" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="8" t="n">
+      <c r="H27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42318,7 +43142,10 @@
       <c r="G28" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="8" t="n">
+      <c r="H28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42337,7 +43164,10 @@
       <c r="G29" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="8" t="n">
+      <c r="H29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42356,7 +43186,10 @@
       <c r="G30" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="8" t="n">
+      <c r="H30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42383,12 +43216,15 @@
         <v>4725484.1</v>
       </c>
       <c r="H32" s="8" t="n">
+        <v>5366703.8</v>
+      </c>
+      <c r="I32" s="8" t="n">
         <v>6414130.99</v>
       </c>
-      <c r="I32" s="8" t="n">
+      <c r="J32" s="8" t="n">
         <v>7584961.04</v>
       </c>
-      <c r="J32" s="8" t="n">
+      <c r="K32" s="8" t="n">
         <v>8050461.64</v>
       </c>
     </row>
@@ -42398,7 +43234,10 @@
           <t>Бусад эргэлтийн бус хөрөнгө</t>
         </is>
       </c>
-      <c r="J33" s="8" t="n">
+      <c r="H33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42434,12 +43273,15 @@
         <v>30587977.07</v>
       </c>
       <c r="H35" s="10" t="n">
+        <v>31883127.85</v>
+      </c>
+      <c r="I35" s="10" t="n">
         <v>33252111.91</v>
       </c>
-      <c r="I35" s="10" t="n">
+      <c r="J35" s="10" t="n">
         <v>34578198.33</v>
       </c>
-      <c r="J35" s="10" t="n">
+      <c r="K35" s="10" t="n">
         <v>35357776.81</v>
       </c>
     </row>
@@ -42468,12 +43310,15 @@
         <v>61461597.14</v>
       </c>
       <c r="H36" s="10" t="n">
+        <v>65542981.52</v>
+      </c>
+      <c r="I36" s="10" t="n">
         <v>63630235.02</v>
       </c>
-      <c r="I36" s="10" t="n">
+      <c r="J36" s="10" t="n">
         <v>65868654.73</v>
       </c>
-      <c r="J36" s="10" t="n">
+      <c r="K36" s="10" t="n">
         <v>65909104.1</v>
       </c>
     </row>
@@ -42492,6 +43337,7 @@
       <c r="H37" s="7" t="n"/>
       <c r="I37" s="7" t="n"/>
       <c r="J37" s="7" t="n"/>
+      <c r="K37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -42518,12 +43364,15 @@
         <v>423840.71</v>
       </c>
       <c r="H38" s="8" t="n">
+        <v>648646.23</v>
+      </c>
+      <c r="I38" s="8" t="n">
         <v>840416.75</v>
       </c>
-      <c r="I38" s="8" t="n">
+      <c r="J38" s="8" t="n">
         <v>1275871.2</v>
       </c>
-      <c r="J38" s="8" t="n">
+      <c r="K38" s="8" t="n">
         <v>698006.3100000001</v>
       </c>
     </row>
@@ -42552,12 +43401,15 @@
         <v>339000.09</v>
       </c>
       <c r="H39" s="8" t="n">
+        <v>380711.09</v>
+      </c>
+      <c r="I39" s="8" t="n">
         <v>299527.4</v>
       </c>
-      <c r="I39" s="8" t="n">
+      <c r="J39" s="8" t="n">
         <v>403372.16</v>
       </c>
-      <c r="J39" s="8" t="n">
+      <c r="K39" s="8" t="n">
         <v>449100.31</v>
       </c>
     </row>
@@ -42586,12 +43438,15 @@
         <v>1067755.2</v>
       </c>
       <c r="H40" s="8" t="n">
+        <v>339277.03</v>
+      </c>
+      <c r="I40" s="8" t="n">
         <v>585863.76</v>
       </c>
-      <c r="I40" s="8" t="n">
+      <c r="J40" s="8" t="n">
         <v>1091975.47</v>
       </c>
-      <c r="J40" s="8" t="n">
+      <c r="K40" s="8" t="n">
         <v>431630.14</v>
       </c>
     </row>
@@ -42611,12 +43466,15 @@
         <v>0</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>0</v>
+        <v>4353.05</v>
       </c>
       <c r="I41" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42639,12 +43497,15 @@
         <v>2550000</v>
       </c>
       <c r="H42" s="8" t="n">
+        <v>3458333.33</v>
+      </c>
+      <c r="I42" s="8" t="n">
         <v>375010</v>
       </c>
-      <c r="I42" s="8" t="n">
+      <c r="J42" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="J42" s="8" t="n">
+      <c r="K42" s="8" t="n">
         <v>1328394.98</v>
       </c>
     </row>
@@ -42667,9 +43528,12 @@
         <v>0</v>
       </c>
       <c r="I43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="8" t="n">
         <v>8883.559999999999</v>
       </c>
-      <c r="J43" s="8" t="n">
+      <c r="K43" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42698,12 +43562,15 @@
         <v>0</v>
       </c>
       <c r="H44" s="8" t="n">
+        <v>335500</v>
+      </c>
+      <c r="I44" s="8" t="n">
         <v>100000</v>
       </c>
-      <c r="I44" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="J44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="8" t="n">
         <v>301000</v>
       </c>
     </row>
@@ -42722,10 +43589,13 @@
       <c r="G45" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I45" s="8" t="n">
+      <c r="H45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="8" t="n">
         <v>1416.49</v>
       </c>
-      <c r="J45" s="8" t="n">
+      <c r="K45" s="8" t="n">
         <v>3918.71</v>
       </c>
     </row>
@@ -42744,7 +43614,10 @@
       <c r="G46" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J46" s="8" t="n">
+      <c r="H46" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42770,12 +43643,15 @@
         <v>56303.01</v>
       </c>
       <c r="H47" s="8" t="n">
+        <v>234225.23</v>
+      </c>
+      <c r="I47" s="8" t="n">
         <v>238695.94</v>
       </c>
-      <c r="I47" s="8" t="n">
+      <c r="J47" s="8" t="n">
         <v>112105.88</v>
       </c>
-      <c r="J47" s="8" t="n">
+      <c r="K47" s="8" t="n">
         <v>340115.27</v>
       </c>
     </row>
@@ -42794,7 +43670,10 @@
       <c r="G48" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="8" t="n">
+      <c r="H48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42823,12 +43702,15 @@
         <v>4447455.22</v>
       </c>
       <c r="H49" s="10" t="n">
+        <v>5401045.97</v>
+      </c>
+      <c r="I49" s="10" t="n">
         <v>2439513.85</v>
       </c>
-      <c r="I49" s="10" t="n">
+      <c r="J49" s="10" t="n">
         <v>2893634.77</v>
       </c>
-      <c r="J49" s="10" t="n">
+      <c r="K49" s="10" t="n">
         <v>3552165.72</v>
       </c>
     </row>
@@ -42847,6 +43729,7 @@
       <c r="H50" s="7" t="n"/>
       <c r="I50" s="7" t="n"/>
       <c r="J50" s="7" t="n"/>
+      <c r="K50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -42873,12 +43756,15 @@
         <v>4250000</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>6708333.33</v>
+        <v>7000000</v>
       </c>
       <c r="I51" s="8" t="n">
         <v>6708333.33</v>
       </c>
       <c r="J51" s="8" t="n">
+        <v>6708333.33</v>
+      </c>
+      <c r="K51" s="8" t="n">
         <v>7541666.67</v>
       </c>
     </row>
@@ -42906,6 +43792,9 @@
       <c r="J52" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="K52" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -42923,12 +43812,15 @@
         <v>48220.3</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>48220.31</v>
+        <v>0</v>
       </c>
       <c r="I53" s="8" t="n">
         <v>48220.31</v>
       </c>
       <c r="J53" s="8" t="n">
+        <v>48220.31</v>
+      </c>
+      <c r="K53" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42961,12 +43853,15 @@
         <v>0</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>0</v>
+        <v>48220.31</v>
       </c>
       <c r="I55" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="8" t="n">
         <v>96289.89</v>
       </c>
     </row>
@@ -42995,12 +43890,15 @@
         <v>4298220.3</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>6756553.64</v>
+        <v>7048220.31</v>
       </c>
       <c r="I56" s="10" t="n">
         <v>6756553.64</v>
       </c>
       <c r="J56" s="10" t="n">
+        <v>6756553.64</v>
+      </c>
+      <c r="K56" s="10" t="n">
         <v>7637956.56</v>
       </c>
     </row>
@@ -43029,12 +43927,15 @@
         <v>8745675.52</v>
       </c>
       <c r="H57" s="10" t="n">
+        <v>12449266.29</v>
+      </c>
+      <c r="I57" s="10" t="n">
         <v>9196067.5</v>
       </c>
-      <c r="I57" s="10" t="n">
+      <c r="J57" s="10" t="n">
         <v>9650188.41</v>
       </c>
-      <c r="J57" s="10" t="n">
+      <c r="K57" s="10" t="n">
         <v>11190122.27</v>
       </c>
     </row>
@@ -43053,6 +43954,7 @@
       <c r="H58" s="7" t="n"/>
       <c r="I58" s="7" t="n"/>
       <c r="J58" s="7" t="n"/>
+      <c r="K58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -43079,9 +43981,12 @@
         <v>0</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>0</v>
+        <v>131792.45</v>
       </c>
       <c r="I59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -43097,7 +44002,10 @@
       <c r="F60" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J60" s="8" t="n">
+      <c r="H60" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -43125,6 +44033,9 @@
       <c r="J61" s="8" t="n">
         <v>9848102.470000001</v>
       </c>
+      <c r="K61" s="8" t="n">
+        <v>9848102.470000001</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -43148,6 +44059,9 @@
         <v>12308611.91</v>
       </c>
       <c r="J62" s="8" t="n">
+        <v>12308611.91</v>
+      </c>
+      <c r="K62" s="8" t="n">
         <v>12189209.33</v>
       </c>
     </row>
@@ -43166,7 +44080,10 @@
       <c r="G63" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J63" s="8" t="n">
+      <c r="H63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -43194,7 +44111,10 @@
       <c r="G64" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="8" t="n">
+      <c r="H64" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -43223,12 +44143,15 @@
         <v>30427414.8</v>
       </c>
       <c r="H65" s="8" t="n">
+        <v>30805208.4</v>
+      </c>
+      <c r="I65" s="8" t="n">
         <v>32145660.69</v>
       </c>
-      <c r="I65" s="8" t="n">
+      <c r="J65" s="8" t="n">
         <v>33929959.48</v>
       </c>
-      <c r="J65" s="8" t="n">
+      <c r="K65" s="8" t="n">
         <v>32549877.58</v>
       </c>
     </row>
@@ -43271,12 +44194,15 @@
         <v>52715921.63</v>
       </c>
       <c r="H68" s="10" t="n">
+        <v>53093715.23</v>
+      </c>
+      <c r="I68" s="10" t="n">
         <v>54434167.52</v>
       </c>
-      <c r="I68" s="10" t="n">
+      <c r="J68" s="10" t="n">
         <v>56218466.31</v>
       </c>
-      <c r="J68" s="10" t="n">
+      <c r="K68" s="10" t="n">
         <v>54718981.83</v>
       </c>
     </row>
@@ -43298,9 +44224,12 @@
       <c r="E69" s="9" t="n"/>
       <c r="F69" s="9" t="n"/>
       <c r="G69" s="9" t="n"/>
-      <c r="H69" s="9" t="n"/>
+      <c r="H69" s="10" t="n">
+        <v>65542981.52</v>
+      </c>
       <c r="I69" s="9" t="n"/>
-      <c r="J69" s="10" t="n">
+      <c r="J69" s="9" t="n"/>
+      <c r="K69" s="10" t="n">
         <v>65909104.1</v>
       </c>
     </row>
@@ -43319,6 +44248,7 @@
       <c r="H70" s="7" t="n"/>
       <c r="I70" s="7" t="n"/>
       <c r="J70" s="7" t="n"/>
+      <c r="K70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -43345,12 +44275,15 @@
         <v>41071890.19</v>
       </c>
       <c r="H71" s="8" t="n">
+        <v>23375174.61</v>
+      </c>
+      <c r="I71" s="8" t="n">
         <v>34183968.82</v>
       </c>
-      <c r="I71" s="8" t="n">
+      <c r="J71" s="8" t="n">
         <v>47197953.53</v>
       </c>
-      <c r="J71" s="8" t="n">
+      <c r="K71" s="8" t="n">
         <v>23274549.23</v>
       </c>
     </row>
@@ -43379,12 +44312,15 @@
         <v>23609900.13</v>
       </c>
       <c r="H72" s="8" t="n">
+        <v>13509133.11</v>
+      </c>
+      <c r="I72" s="8" t="n">
         <v>20219161.8</v>
       </c>
-      <c r="I72" s="8" t="n">
+      <c r="J72" s="8" t="n">
         <v>28252420.68</v>
       </c>
-      <c r="J72" s="8" t="n">
+      <c r="K72" s="8" t="n">
         <v>14575868.83</v>
       </c>
     </row>
@@ -43413,12 +44349,15 @@
         <v>17461990.06</v>
       </c>
       <c r="H73" s="10" t="n">
+        <v>9866041.49</v>
+      </c>
+      <c r="I73" s="10" t="n">
         <v>13964807.02</v>
       </c>
-      <c r="I73" s="10" t="n">
+      <c r="J73" s="10" t="n">
         <v>18945532.86</v>
       </c>
-      <c r="J73" s="10" t="n">
+      <c r="K73" s="10" t="n">
         <v>8698680.4</v>
       </c>
     </row>
@@ -43446,6 +44385,9 @@
       <c r="J74" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="K74" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -43472,12 +44414,15 @@
         <v>723465.9</v>
       </c>
       <c r="H75" s="8" t="n">
+        <v>26383.04</v>
+      </c>
+      <c r="I75" s="8" t="n">
         <v>301523.8</v>
       </c>
-      <c r="I75" s="8" t="n">
+      <c r="J75" s="8" t="n">
         <v>325382.1</v>
       </c>
-      <c r="J75" s="8" t="n">
+      <c r="K75" s="8" t="n">
         <v>73135.69</v>
       </c>
     </row>
@@ -43496,7 +44441,10 @@
       <c r="G76" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J76" s="8" t="n">
+      <c r="H76" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -43515,7 +44463,10 @@
       <c r="G77" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J77" s="8" t="n">
+      <c r="H77" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -43544,12 +44495,15 @@
         <v>805840.9</v>
       </c>
       <c r="H78" s="8" t="n">
+        <v>10900.88</v>
+      </c>
+      <c r="I78" s="8" t="n">
         <v>17080.51</v>
       </c>
-      <c r="I78" s="8" t="n">
+      <c r="J78" s="8" t="n">
         <v>664651.71</v>
       </c>
-      <c r="J78" s="8" t="n">
+      <c r="K78" s="8" t="n">
         <v>307198.92</v>
       </c>
     </row>
@@ -43578,12 +44532,15 @@
         <v>5177813.15</v>
       </c>
       <c r="H79" s="8" t="n">
+        <v>3908907.77</v>
+      </c>
+      <c r="I79" s="8" t="n">
         <v>5641064.2</v>
       </c>
-      <c r="I79" s="8" t="n">
+      <c r="J79" s="8" t="n">
         <v>7448269.38</v>
       </c>
-      <c r="J79" s="8" t="n">
+      <c r="K79" s="8" t="n">
         <v>3921934.8</v>
       </c>
     </row>
@@ -43612,12 +44569,15 @@
         <v>2928770.4</v>
       </c>
       <c r="H80" s="8" t="n">
+        <v>1848222.16</v>
+      </c>
+      <c r="I80" s="8" t="n">
         <v>2706848.37</v>
       </c>
-      <c r="I80" s="8" t="n">
+      <c r="J80" s="8" t="n">
         <v>3596584.59</v>
       </c>
-      <c r="J80" s="8" t="n">
+      <c r="K80" s="8" t="n">
         <v>2524936.98</v>
       </c>
     </row>
@@ -43643,12 +44603,15 @@
         <v>715788.7</v>
       </c>
       <c r="H81" s="8" t="n">
+        <v>99384.72</v>
+      </c>
+      <c r="I81" s="8" t="n">
         <v>246703.43</v>
       </c>
-      <c r="I81" s="8" t="n">
+      <c r="J81" s="8" t="n">
         <v>662976.03</v>
       </c>
-      <c r="J81" s="8" t="n">
+      <c r="K81" s="8" t="n">
         <v>499307.56</v>
       </c>
     </row>
@@ -43677,12 +44640,15 @@
         <v>513003.8</v>
       </c>
       <c r="H82" s="8" t="n">
+        <v>89538.77</v>
+      </c>
+      <c r="I82" s="8" t="n">
         <v>125692.92</v>
       </c>
-      <c r="I82" s="8" t="n">
+      <c r="J82" s="8" t="n">
         <v>312001.61</v>
       </c>
-      <c r="J82" s="8" t="n">
+      <c r="K82" s="8" t="n">
         <v>255181.92</v>
       </c>
     </row>
@@ -43711,12 +44677,15 @@
         <v>-48165.02</v>
       </c>
       <c r="H83" s="8" t="n">
+        <v>-53295.88</v>
+      </c>
+      <c r="I83" s="8" t="n">
         <v>-99520.02</v>
       </c>
-      <c r="I83" s="8" t="n">
+      <c r="J83" s="8" t="n">
         <v>-78061.41</v>
       </c>
-      <c r="J83" s="8" t="n">
+      <c r="K83" s="8" t="n">
         <v>-96144.08</v>
       </c>
     </row>
@@ -43745,12 +44714,15 @@
         <v>-36373.05</v>
       </c>
       <c r="H84" s="8" t="n">
+        <v>-6906.83</v>
+      </c>
+      <c r="I84" s="8" t="n">
         <v>-67968.55</v>
       </c>
-      <c r="I84" s="8" t="n">
+      <c r="J84" s="8" t="n">
         <v>-148634.54</v>
       </c>
-      <c r="J84" s="8" t="n">
+      <c r="K84" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -43769,7 +44741,10 @@
       <c r="G85" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J85" s="8" t="n">
+      <c r="H85" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -43788,7 +44763,10 @@
       <c r="G86" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J86" s="8" t="n">
+      <c r="H86" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -43830,6 +44808,9 @@
       <c r="J89" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="K89" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
@@ -43856,12 +44837,15 @@
         <v>8991233.800000001</v>
       </c>
       <c r="H90" s="10" t="n">
+        <v>3897069.28</v>
+      </c>
+      <c r="I90" s="10" t="n">
         <v>5395613.85</v>
       </c>
-      <c r="I90" s="10" t="n">
+      <c r="J90" s="10" t="n">
         <v>7689039.11</v>
       </c>
-      <c r="J90" s="10" t="n">
+      <c r="K90" s="10" t="n">
         <v>1781509.67</v>
       </c>
     </row>
@@ -43890,12 +44874,15 @@
         <v>1432271.5</v>
       </c>
       <c r="H91" s="8" t="n">
+        <v>404181.36</v>
+      </c>
+      <c r="I91" s="8" t="n">
         <v>562273.65</v>
       </c>
-      <c r="I91" s="8" t="n">
+      <c r="J91" s="8" t="n">
         <v>1071445.63</v>
       </c>
-      <c r="J91" s="8" t="n">
+      <c r="K91" s="8" t="n">
         <v>213283.57</v>
       </c>
     </row>
@@ -43924,12 +44911,15 @@
         <v>7558962.3</v>
       </c>
       <c r="H92" s="10" t="n">
+        <v>3492887.92</v>
+      </c>
+      <c r="I92" s="10" t="n">
         <v>4833340.2</v>
       </c>
-      <c r="I92" s="10" t="n">
+      <c r="J92" s="10" t="n">
         <v>6617593.48</v>
       </c>
-      <c r="J92" s="10" t="n">
+      <c r="K92" s="10" t="n">
         <v>1568226.11</v>
       </c>
     </row>
@@ -43948,7 +44938,10 @@
       <c r="G93" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J93" s="8" t="n">
+      <c r="H93" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -43977,12 +44970,15 @@
         <v>7558962.3</v>
       </c>
       <c r="H94" s="10" t="n">
+        <v>3492887.92</v>
+      </c>
+      <c r="I94" s="10" t="n">
         <v>4833340.2</v>
       </c>
-      <c r="I94" s="10" t="n">
+      <c r="J94" s="10" t="n">
         <v>6617593.48</v>
       </c>
-      <c r="J94" s="10" t="n">
+      <c r="K94" s="10" t="n">
         <v>1568226.11</v>
       </c>
     </row>
@@ -44010,6 +45006,9 @@
       <c r="J95" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="K95" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -44026,7 +45025,10 @@
       <c r="G96" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J96" s="8" t="n">
+      <c r="H96" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -44052,6 +45054,9 @@
         <v>0</v>
       </c>
       <c r="J97" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -44077,6 +45082,7 @@
       <c r="H99" s="9" t="n"/>
       <c r="I99" s="9" t="n"/>
       <c r="J99" s="9" t="n"/>
+      <c r="K99" s="9" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
@@ -44103,12 +45109,15 @@
         <v>19867574.21</v>
       </c>
       <c r="H100" s="10" t="n">
+        <v>3492887.92</v>
+      </c>
+      <c r="I100" s="10" t="n">
         <v>4833340.2</v>
       </c>
-      <c r="I100" s="10" t="n">
+      <c r="J100" s="10" t="n">
         <v>6617593.48</v>
       </c>
-      <c r="J100" s="10" t="n">
+      <c r="K100" s="10" t="n">
         <v>1568226.11</v>
       </c>
     </row>
@@ -44152,6 +45161,10 @@
       </c>
       <c r="J102" s="12">
         <f>IF(AND(ISNUMBER(J36),ISNUMBER(J57),ISNUMBER(J68)),ROUND(J36-J57-J68,0),"")</f>
+        <v/>
+      </c>
+      <c r="K102" s="12">
+        <f>IF(AND(ISNUMBER(K36),ISNUMBER(K57),ISNUMBER(K68)),ROUND(K36-K57-K68,0),"")</f>
         <v/>
       </c>
     </row>
@@ -44170,6 +45183,7 @@
       <c r="H104" s="7" t="n"/>
       <c r="I104" s="7" t="n"/>
       <c r="J104" s="7" t="n"/>
+      <c r="K104" s="7" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="13" t="inlineStr">
@@ -44227,6 +45241,10 @@
         <f>IF(ISNUMBER(J$6),IFERROR(12/J$6,""),"")</f>
         <v/>
       </c>
+      <c r="K107" s="15">
+        <f>IF(ISNUMBER(K$6),IFERROR(12/K$6,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -44235,39 +45253,43 @@
         </is>
       </c>
       <c r="B108" s="8">
-        <f>IF(ISNUMBER(B36),IFERROR(IF(INDEX($B36:$J36,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$J$4,0))="",B36,(B36+INDEX($B36:$J36,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$J$4,0)))/2),B36),"")</f>
+        <f>IF(ISNUMBER(B36),IFERROR(IF(INDEX($B36:$K36,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$K$4,0))="",B36,(B36+INDEX($B36:$K36,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$K$4,0)))/2),B36),"")</f>
         <v/>
       </c>
       <c r="C108" s="8">
-        <f>IF(ISNUMBER(C36),IFERROR(IF(INDEX($B36:$J36,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$J$4,0))="",C36,(C36+INDEX($B36:$J36,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$J$4,0)))/2),C36),"")</f>
+        <f>IF(ISNUMBER(C36),IFERROR(IF(INDEX($B36:$K36,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$K$4,0))="",C36,(C36+INDEX($B36:$K36,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$K$4,0)))/2),C36),"")</f>
         <v/>
       </c>
       <c r="D108" s="8">
-        <f>IF(ISNUMBER(D36),IFERROR(IF(INDEX($B36:$J36,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$J$4,0))="",D36,(D36+INDEX($B36:$J36,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$J$4,0)))/2),D36),"")</f>
+        <f>IF(ISNUMBER(D36),IFERROR(IF(INDEX($B36:$K36,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$K$4,0))="",D36,(D36+INDEX($B36:$K36,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$K$4,0)))/2),D36),"")</f>
         <v/>
       </c>
       <c r="E108" s="8">
-        <f>IF(ISNUMBER(E36),IFERROR(IF(INDEX($B36:$J36,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$J$4,0))="",E36,(E36+INDEX($B36:$J36,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$J$4,0)))/2),E36),"")</f>
+        <f>IF(ISNUMBER(E36),IFERROR(IF(INDEX($B36:$K36,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$K$4,0))="",E36,(E36+INDEX($B36:$K36,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$K$4,0)))/2),E36),"")</f>
         <v/>
       </c>
       <c r="F108" s="8">
-        <f>IF(ISNUMBER(F36),IFERROR(IF(INDEX($B36:$J36,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$J$4,0))="",F36,(F36+INDEX($B36:$J36,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$J$4,0)))/2),F36),"")</f>
+        <f>IF(ISNUMBER(F36),IFERROR(IF(INDEX($B36:$K36,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$K$4,0))="",F36,(F36+INDEX($B36:$K36,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$K$4,0)))/2),F36),"")</f>
         <v/>
       </c>
       <c r="G108" s="8">
-        <f>IF(ISNUMBER(G36),IFERROR(IF(INDEX($B36:$J36,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$J$4,0))="",G36,(G36+INDEX($B36:$J36,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$J$4,0)))/2),G36),"")</f>
+        <f>IF(ISNUMBER(G36),IFERROR(IF(INDEX($B36:$K36,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$K$4,0))="",G36,(G36+INDEX($B36:$K36,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$K$4,0)))/2),G36),"")</f>
         <v/>
       </c>
       <c r="H108" s="8">
-        <f>IF(ISNUMBER(H36),IFERROR(IF(INDEX($B36:$J36,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$J$4,0))="",H36,(H36+INDEX($B36:$J36,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$J$4,0)))/2),H36),"")</f>
+        <f>IF(ISNUMBER(H36),IFERROR(IF(INDEX($B36:$K36,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$K$4,0))="",H36,(H36+INDEX($B36:$K36,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$K$4,0)))/2),H36),"")</f>
         <v/>
       </c>
       <c r="I108" s="8">
-        <f>IF(ISNUMBER(I36),IFERROR(IF(INDEX($B36:$J36,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$J$4,0))="",I36,(I36+INDEX($B36:$J36,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$J$4,0)))/2),I36),"")</f>
+        <f>IF(ISNUMBER(I36),IFERROR(IF(INDEX($B36:$K36,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$K$4,0))="",I36,(I36+INDEX($B36:$K36,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$K$4,0)))/2),I36),"")</f>
         <v/>
       </c>
       <c r="J108" s="8">
-        <f>IF(ISNUMBER(J36),IFERROR(IF(INDEX($B36:$J36,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$J$4,0))="",J36,(J36+INDEX($B36:$J36,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$J$4,0)))/2),J36),"")</f>
+        <f>IF(ISNUMBER(J36),IFERROR(IF(INDEX($B36:$K36,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$K$4,0))="",J36,(J36+INDEX($B36:$K36,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$K$4,0)))/2),J36),"")</f>
+        <v/>
+      </c>
+      <c r="K108" s="8">
+        <f>IF(ISNUMBER(K36),IFERROR(IF(INDEX($B36:$K36,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$K$4,0))="",K36,(K36+INDEX($B36:$K36,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$K$4,0)))/2),K36),"")</f>
         <v/>
       </c>
     </row>
@@ -44278,39 +45300,43 @@
         </is>
       </c>
       <c r="B109" s="8">
-        <f>IF(ISNUMBER(B68),IFERROR(IF(INDEX($B68:$J68,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$J$4,0))="",B68,(B68+INDEX($B68:$J68,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$J$4,0)))/2),B68),"")</f>
+        <f>IF(ISNUMBER(B68),IFERROR(IF(INDEX($B68:$K68,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$K$4,0))="",B68,(B68+INDEX($B68:$K68,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$K$4,0)))/2),B68),"")</f>
         <v/>
       </c>
       <c r="C109" s="8">
-        <f>IF(ISNUMBER(C68),IFERROR(IF(INDEX($B68:$J68,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$J$4,0))="",C68,(C68+INDEX($B68:$J68,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$J$4,0)))/2),C68),"")</f>
+        <f>IF(ISNUMBER(C68),IFERROR(IF(INDEX($B68:$K68,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$K$4,0))="",C68,(C68+INDEX($B68:$K68,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$K$4,0)))/2),C68),"")</f>
         <v/>
       </c>
       <c r="D109" s="8">
-        <f>IF(ISNUMBER(D68),IFERROR(IF(INDEX($B68:$J68,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$J$4,0))="",D68,(D68+INDEX($B68:$J68,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$J$4,0)))/2),D68),"")</f>
+        <f>IF(ISNUMBER(D68),IFERROR(IF(INDEX($B68:$K68,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$K$4,0))="",D68,(D68+INDEX($B68:$K68,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$K$4,0)))/2),D68),"")</f>
         <v/>
       </c>
       <c r="E109" s="8">
-        <f>IF(ISNUMBER(E68),IFERROR(IF(INDEX($B68:$J68,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$J$4,0))="",E68,(E68+INDEX($B68:$J68,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$J$4,0)))/2),E68),"")</f>
+        <f>IF(ISNUMBER(E68),IFERROR(IF(INDEX($B68:$K68,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$K$4,0))="",E68,(E68+INDEX($B68:$K68,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$K$4,0)))/2),E68),"")</f>
         <v/>
       </c>
       <c r="F109" s="8">
-        <f>IF(ISNUMBER(F68),IFERROR(IF(INDEX($B68:$J68,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$J$4,0))="",F68,(F68+INDEX($B68:$J68,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$J$4,0)))/2),F68),"")</f>
+        <f>IF(ISNUMBER(F68),IFERROR(IF(INDEX($B68:$K68,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$K$4,0))="",F68,(F68+INDEX($B68:$K68,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$K$4,0)))/2),F68),"")</f>
         <v/>
       </c>
       <c r="G109" s="8">
-        <f>IF(ISNUMBER(G68),IFERROR(IF(INDEX($B68:$J68,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$J$4,0))="",G68,(G68+INDEX($B68:$J68,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$J$4,0)))/2),G68),"")</f>
+        <f>IF(ISNUMBER(G68),IFERROR(IF(INDEX($B68:$K68,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$K$4,0))="",G68,(G68+INDEX($B68:$K68,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$K$4,0)))/2),G68),"")</f>
         <v/>
       </c>
       <c r="H109" s="8">
-        <f>IF(ISNUMBER(H68),IFERROR(IF(INDEX($B68:$J68,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$J$4,0))="",H68,(H68+INDEX($B68:$J68,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$J$4,0)))/2),H68),"")</f>
+        <f>IF(ISNUMBER(H68),IFERROR(IF(INDEX($B68:$K68,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$K$4,0))="",H68,(H68+INDEX($B68:$K68,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$K$4,0)))/2),H68),"")</f>
         <v/>
       </c>
       <c r="I109" s="8">
-        <f>IF(ISNUMBER(I68),IFERROR(IF(INDEX($B68:$J68,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$J$4,0))="",I68,(I68+INDEX($B68:$J68,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$J$4,0)))/2),I68),"")</f>
+        <f>IF(ISNUMBER(I68),IFERROR(IF(INDEX($B68:$K68,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$K$4,0))="",I68,(I68+INDEX($B68:$K68,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$K$4,0)))/2),I68),"")</f>
         <v/>
       </c>
       <c r="J109" s="8">
-        <f>IF(ISNUMBER(J68),IFERROR(IF(INDEX($B68:$J68,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$J$4,0))="",J68,(J68+INDEX($B68:$J68,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$J$4,0)))/2),J68),"")</f>
+        <f>IF(ISNUMBER(J68),IFERROR(IF(INDEX($B68:$K68,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$K$4,0))="",J68,(J68+INDEX($B68:$K68,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$K$4,0)))/2),J68),"")</f>
+        <v/>
+      </c>
+      <c r="K109" s="8">
+        <f>IF(ISNUMBER(K68),IFERROR(IF(INDEX($B68:$K68,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$K$4,0))="",K68,(K68+INDEX($B68:$K68,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$K$4,0)))/2),K68),"")</f>
         <v/>
       </c>
     </row>
@@ -44321,39 +45347,43 @@
         </is>
       </c>
       <c r="B110" s="8">
-        <f>IF(ISNUMBER(B17),IFERROR(IF(INDEX($B17:$J17,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$J$4,0))="",B17,(B17+INDEX($B17:$J17,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$J$4,0)))/2),B17),"")</f>
+        <f>IF(ISNUMBER(B17),IFERROR(IF(INDEX($B17:$K17,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$K$4,0))="",B17,(B17+INDEX($B17:$K17,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$K$4,0)))/2),B17),"")</f>
         <v/>
       </c>
       <c r="C110" s="8">
-        <f>IF(ISNUMBER(C17),IFERROR(IF(INDEX($B17:$J17,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$J$4,0))="",C17,(C17+INDEX($B17:$J17,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$J$4,0)))/2),C17),"")</f>
+        <f>IF(ISNUMBER(C17),IFERROR(IF(INDEX($B17:$K17,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$K$4,0))="",C17,(C17+INDEX($B17:$K17,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$K$4,0)))/2),C17),"")</f>
         <v/>
       </c>
       <c r="D110" s="8">
-        <f>IF(ISNUMBER(D17),IFERROR(IF(INDEX($B17:$J17,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$J$4,0))="",D17,(D17+INDEX($B17:$J17,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$J$4,0)))/2),D17),"")</f>
+        <f>IF(ISNUMBER(D17),IFERROR(IF(INDEX($B17:$K17,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$K$4,0))="",D17,(D17+INDEX($B17:$K17,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$K$4,0)))/2),D17),"")</f>
         <v/>
       </c>
       <c r="E110" s="8">
-        <f>IF(ISNUMBER(E17),IFERROR(IF(INDEX($B17:$J17,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$J$4,0))="",E17,(E17+INDEX($B17:$J17,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$J$4,0)))/2),E17),"")</f>
+        <f>IF(ISNUMBER(E17),IFERROR(IF(INDEX($B17:$K17,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$K$4,0))="",E17,(E17+INDEX($B17:$K17,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$K$4,0)))/2),E17),"")</f>
         <v/>
       </c>
       <c r="F110" s="8">
-        <f>IF(ISNUMBER(F17),IFERROR(IF(INDEX($B17:$J17,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$J$4,0))="",F17,(F17+INDEX($B17:$J17,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$J$4,0)))/2),F17),"")</f>
+        <f>IF(ISNUMBER(F17),IFERROR(IF(INDEX($B17:$K17,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$K$4,0))="",F17,(F17+INDEX($B17:$K17,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$K$4,0)))/2),F17),"")</f>
         <v/>
       </c>
       <c r="G110" s="8">
-        <f>IF(ISNUMBER(G17),IFERROR(IF(INDEX($B17:$J17,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$J$4,0))="",G17,(G17+INDEX($B17:$J17,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$J$4,0)))/2),G17),"")</f>
+        <f>IF(ISNUMBER(G17),IFERROR(IF(INDEX($B17:$K17,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$K$4,0))="",G17,(G17+INDEX($B17:$K17,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$K$4,0)))/2),G17),"")</f>
         <v/>
       </c>
       <c r="H110" s="8">
-        <f>IF(ISNUMBER(H17),IFERROR(IF(INDEX($B17:$J17,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$J$4,0))="",H17,(H17+INDEX($B17:$J17,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$J$4,0)))/2),H17),"")</f>
+        <f>IF(ISNUMBER(H17),IFERROR(IF(INDEX($B17:$K17,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$K$4,0))="",H17,(H17+INDEX($B17:$K17,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$K$4,0)))/2),H17),"")</f>
         <v/>
       </c>
       <c r="I110" s="8">
-        <f>IF(ISNUMBER(I17),IFERROR(IF(INDEX($B17:$J17,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$J$4,0))="",I17,(I17+INDEX($B17:$J17,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$J$4,0)))/2),I17),"")</f>
+        <f>IF(ISNUMBER(I17),IFERROR(IF(INDEX($B17:$K17,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$K$4,0))="",I17,(I17+INDEX($B17:$K17,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$K$4,0)))/2),I17),"")</f>
         <v/>
       </c>
       <c r="J110" s="8">
-        <f>IF(ISNUMBER(J17),IFERROR(IF(INDEX($B17:$J17,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$J$4,0))="",J17,(J17+INDEX($B17:$J17,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$J$4,0)))/2),J17),"")</f>
+        <f>IF(ISNUMBER(J17),IFERROR(IF(INDEX($B17:$K17,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$K$4,0))="",J17,(J17+INDEX($B17:$K17,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$K$4,0)))/2),J17),"")</f>
+        <v/>
+      </c>
+      <c r="K110" s="8">
+        <f>IF(ISNUMBER(K17),IFERROR(IF(INDEX($B17:$K17,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$K$4,0))="",K17,(K17+INDEX($B17:$K17,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$K$4,0)))/2),K17),"")</f>
         <v/>
       </c>
     </row>
@@ -44364,39 +45394,43 @@
         </is>
       </c>
       <c r="B111" s="8">
-        <f>IF(ISNUMBER(B13),IFERROR(IF(INDEX($B13:$J13,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$J$4,0))="",B13,(B13+INDEX($B13:$J13,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$J$4,0)))/2),B13),"")</f>
+        <f>IF(ISNUMBER(B13),IFERROR(IF(INDEX($B13:$K13,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$K$4,0))="",B13,(B13+INDEX($B13:$K13,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$K$4,0)))/2),B13),"")</f>
         <v/>
       </c>
       <c r="C111" s="8">
-        <f>IF(ISNUMBER(C13),IFERROR(IF(INDEX($B13:$J13,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$J$4,0))="",C13,(C13+INDEX($B13:$J13,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$J$4,0)))/2),C13),"")</f>
+        <f>IF(ISNUMBER(C13),IFERROR(IF(INDEX($B13:$K13,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$K$4,0))="",C13,(C13+INDEX($B13:$K13,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$K$4,0)))/2),C13),"")</f>
         <v/>
       </c>
       <c r="D111" s="8">
-        <f>IF(ISNUMBER(D13),IFERROR(IF(INDEX($B13:$J13,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$J$4,0))="",D13,(D13+INDEX($B13:$J13,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$J$4,0)))/2),D13),"")</f>
+        <f>IF(ISNUMBER(D13),IFERROR(IF(INDEX($B13:$K13,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$K$4,0))="",D13,(D13+INDEX($B13:$K13,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$K$4,0)))/2),D13),"")</f>
         <v/>
       </c>
       <c r="E111" s="8">
-        <f>IF(ISNUMBER(E13),IFERROR(IF(INDEX($B13:$J13,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$J$4,0))="",E13,(E13+INDEX($B13:$J13,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$J$4,0)))/2),E13),"")</f>
+        <f>IF(ISNUMBER(E13),IFERROR(IF(INDEX($B13:$K13,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$K$4,0))="",E13,(E13+INDEX($B13:$K13,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$K$4,0)))/2),E13),"")</f>
         <v/>
       </c>
       <c r="F111" s="8">
-        <f>IF(ISNUMBER(F13),IFERROR(IF(INDEX($B13:$J13,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$J$4,0))="",F13,(F13+INDEX($B13:$J13,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$J$4,0)))/2),F13),"")</f>
+        <f>IF(ISNUMBER(F13),IFERROR(IF(INDEX($B13:$K13,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$K$4,0))="",F13,(F13+INDEX($B13:$K13,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$K$4,0)))/2),F13),"")</f>
         <v/>
       </c>
       <c r="G111" s="8">
-        <f>IF(ISNUMBER(G13),IFERROR(IF(INDEX($B13:$J13,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$J$4,0))="",G13,(G13+INDEX($B13:$J13,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$J$4,0)))/2),G13),"")</f>
+        <f>IF(ISNUMBER(G13),IFERROR(IF(INDEX($B13:$K13,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$K$4,0))="",G13,(G13+INDEX($B13:$K13,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$K$4,0)))/2),G13),"")</f>
         <v/>
       </c>
       <c r="H111" s="8">
-        <f>IF(ISNUMBER(H13),IFERROR(IF(INDEX($B13:$J13,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$J$4,0))="",H13,(H13+INDEX($B13:$J13,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$J$4,0)))/2),H13),"")</f>
+        <f>IF(ISNUMBER(H13),IFERROR(IF(INDEX($B13:$K13,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$K$4,0))="",H13,(H13+INDEX($B13:$K13,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$K$4,0)))/2),H13),"")</f>
         <v/>
       </c>
       <c r="I111" s="8">
-        <f>IF(ISNUMBER(I13),IFERROR(IF(INDEX($B13:$J13,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$J$4,0))="",I13,(I13+INDEX($B13:$J13,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$J$4,0)))/2),I13),"")</f>
+        <f>IF(ISNUMBER(I13),IFERROR(IF(INDEX($B13:$K13,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$K$4,0))="",I13,(I13+INDEX($B13:$K13,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$K$4,0)))/2),I13),"")</f>
         <v/>
       </c>
       <c r="J111" s="8">
-        <f>IF(ISNUMBER(J13),IFERROR(IF(INDEX($B13:$J13,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$J$4,0))="",J13,(J13+INDEX($B13:$J13,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$J$4,0)))/2),J13),"")</f>
+        <f>IF(ISNUMBER(J13),IFERROR(IF(INDEX($B13:$K13,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$K$4,0))="",J13,(J13+INDEX($B13:$K13,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$K$4,0)))/2),J13),"")</f>
+        <v/>
+      </c>
+      <c r="K111" s="8">
+        <f>IF(ISNUMBER(K13),IFERROR(IF(INDEX($B13:$K13,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$K$4,0))="",K13,(K13+INDEX($B13:$K13,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$K$4,0)))/2),K13),"")</f>
         <v/>
       </c>
     </row>
@@ -44407,39 +45441,43 @@
         </is>
       </c>
       <c r="B112" s="8">
-        <f>IF(ISNUMBER(B38),IFERROR(IF(INDEX($B38:$J38,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$J$4,0))="",B38,(B38+INDEX($B38:$J38,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$J$4,0)))/2),B38),"")</f>
+        <f>IF(ISNUMBER(B38),IFERROR(IF(INDEX($B38:$K38,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$K$4,0))="",B38,(B38+INDEX($B38:$K38,MATCH(DATE(YEAR(B$4)-1,12,31),$B$4:$K$4,0)))/2),B38),"")</f>
         <v/>
       </c>
       <c r="C112" s="8">
-        <f>IF(ISNUMBER(C38),IFERROR(IF(INDEX($B38:$J38,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$J$4,0))="",C38,(C38+INDEX($B38:$J38,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$J$4,0)))/2),C38),"")</f>
+        <f>IF(ISNUMBER(C38),IFERROR(IF(INDEX($B38:$K38,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$K$4,0))="",C38,(C38+INDEX($B38:$K38,MATCH(DATE(YEAR(C$4)-1,12,31),$B$4:$K$4,0)))/2),C38),"")</f>
         <v/>
       </c>
       <c r="D112" s="8">
-        <f>IF(ISNUMBER(D38),IFERROR(IF(INDEX($B38:$J38,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$J$4,0))="",D38,(D38+INDEX($B38:$J38,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$J$4,0)))/2),D38),"")</f>
+        <f>IF(ISNUMBER(D38),IFERROR(IF(INDEX($B38:$K38,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$K$4,0))="",D38,(D38+INDEX($B38:$K38,MATCH(DATE(YEAR(D$4)-1,12,31),$B$4:$K$4,0)))/2),D38),"")</f>
         <v/>
       </c>
       <c r="E112" s="8">
-        <f>IF(ISNUMBER(E38),IFERROR(IF(INDEX($B38:$J38,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$J$4,0))="",E38,(E38+INDEX($B38:$J38,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$J$4,0)))/2),E38),"")</f>
+        <f>IF(ISNUMBER(E38),IFERROR(IF(INDEX($B38:$K38,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$K$4,0))="",E38,(E38+INDEX($B38:$K38,MATCH(DATE(YEAR(E$4)-1,12,31),$B$4:$K$4,0)))/2),E38),"")</f>
         <v/>
       </c>
       <c r="F112" s="8">
-        <f>IF(ISNUMBER(F38),IFERROR(IF(INDEX($B38:$J38,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$J$4,0))="",F38,(F38+INDEX($B38:$J38,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$J$4,0)))/2),F38),"")</f>
+        <f>IF(ISNUMBER(F38),IFERROR(IF(INDEX($B38:$K38,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$K$4,0))="",F38,(F38+INDEX($B38:$K38,MATCH(DATE(YEAR(F$4)-1,12,31),$B$4:$K$4,0)))/2),F38),"")</f>
         <v/>
       </c>
       <c r="G112" s="8">
-        <f>IF(ISNUMBER(G38),IFERROR(IF(INDEX($B38:$J38,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$J$4,0))="",G38,(G38+INDEX($B38:$J38,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$J$4,0)))/2),G38),"")</f>
+        <f>IF(ISNUMBER(G38),IFERROR(IF(INDEX($B38:$K38,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$K$4,0))="",G38,(G38+INDEX($B38:$K38,MATCH(DATE(YEAR(G$4)-1,12,31),$B$4:$K$4,0)))/2),G38),"")</f>
         <v/>
       </c>
       <c r="H112" s="8">
-        <f>IF(ISNUMBER(H38),IFERROR(IF(INDEX($B38:$J38,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$J$4,0))="",H38,(H38+INDEX($B38:$J38,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$J$4,0)))/2),H38),"")</f>
+        <f>IF(ISNUMBER(H38),IFERROR(IF(INDEX($B38:$K38,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$K$4,0))="",H38,(H38+INDEX($B38:$K38,MATCH(DATE(YEAR(H$4)-1,12,31),$B$4:$K$4,0)))/2),H38),"")</f>
         <v/>
       </c>
       <c r="I112" s="8">
-        <f>IF(ISNUMBER(I38),IFERROR(IF(INDEX($B38:$J38,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$J$4,0))="",I38,(I38+INDEX($B38:$J38,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$J$4,0)))/2),I38),"")</f>
+        <f>IF(ISNUMBER(I38),IFERROR(IF(INDEX($B38:$K38,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$K$4,0))="",I38,(I38+INDEX($B38:$K38,MATCH(DATE(YEAR(I$4)-1,12,31),$B$4:$K$4,0)))/2),I38),"")</f>
         <v/>
       </c>
       <c r="J112" s="8">
-        <f>IF(ISNUMBER(J38),IFERROR(IF(INDEX($B38:$J38,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$J$4,0))="",J38,(J38+INDEX($B38:$J38,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$J$4,0)))/2),J38),"")</f>
+        <f>IF(ISNUMBER(J38),IFERROR(IF(INDEX($B38:$K38,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$K$4,0))="",J38,(J38+INDEX($B38:$K38,MATCH(DATE(YEAR(J$4)-1,12,31),$B$4:$K$4,0)))/2),J38),"")</f>
+        <v/>
+      </c>
+      <c r="K112" s="8">
+        <f>IF(ISNUMBER(K38),IFERROR(IF(INDEX($B38:$K38,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$K$4,0))="",K38,(K38+INDEX($B38:$K38,MATCH(DATE(YEAR(K$4)-1,12,31),$B$4:$K$4,0)))/2),K38),"")</f>
         <v/>
       </c>
     </row>
@@ -44492,6 +45530,10 @@
         <f>IF(AND(ISNUMBER(J73),ISNUMBER(J71)),IFERROR((J73)/(J71),""),"")</f>
         <v/>
       </c>
+      <c r="K115" s="16">
+        <f>IF(AND(ISNUMBER(K73),ISNUMBER(K71)),IFERROR((K73)/(K71),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -44535,6 +45577,10 @@
         <f>IF(AND(ISNUMBER(J72),ISNUMBER(J71)),IFERROR((J72)/(J71),""),"")</f>
         <v/>
       </c>
+      <c r="K116" s="16">
+        <f>IF(AND(ISNUMBER(K72),ISNUMBER(K71)),IFERROR((K72)/(K71),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -44578,6 +45624,10 @@
         <f>IF(AND(ISNUMBER(J79),ISNUMBER(J71)),IFERROR((J79)/(J71),""),"")</f>
         <v/>
       </c>
+      <c r="K117" s="16">
+        <f>IF(AND(ISNUMBER(K79),ISNUMBER(K71)),IFERROR((K79)/(K71),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -44621,6 +45671,10 @@
         <f>IF(AND(ISNUMBER(J80),ISNUMBER(J71)),IFERROR((J80)/(J71),""),"")</f>
         <v/>
       </c>
+      <c r="K118" s="16">
+        <f>IF(AND(ISNUMBER(K80),ISNUMBER(K71)),IFERROR((K80)/(K71),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -44664,6 +45718,10 @@
         <f>IF(AND(ISNUMBER(J94),ISNUMBER(J71)),IFERROR((J94)/(J71),""),"")</f>
         <v/>
       </c>
+      <c r="K119" s="16">
+        <f>IF(AND(ISNUMBER(K94),ISNUMBER(K71)),IFERROR((K94)/(K71),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -44707,6 +45765,10 @@
         <f>IF(AND(ISNUMBER(J94),ISNUMBER(J107),ISNUMBER(J108)),IFERROR((J94*J107)/(J108),""),"")</f>
         <v/>
       </c>
+      <c r="K120" s="16">
+        <f>IF(AND(ISNUMBER(K94),ISNUMBER(K107),ISNUMBER(K108)),IFERROR((K94*K107)/(K108),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -44750,6 +45812,10 @@
         <f>IF(AND(ISNUMBER(J94),ISNUMBER(J107),ISNUMBER(J109)),IFERROR((J94*J107)/(J109),""),"")</f>
         <v/>
       </c>
+      <c r="K121" s="16">
+        <f>IF(AND(ISNUMBER(K94),ISNUMBER(K107),ISNUMBER(K109)),IFERROR((K94*K107)/(K109),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="14" t="inlineStr">
@@ -44800,6 +45866,10 @@
         <f>IF(AND(ISNUMBER(J108),ISNUMBER(J71),ISNUMBER(J107)),IFERROR(J71*J107/J108,""),"")</f>
         <v/>
       </c>
+      <c r="K124" s="17">
+        <f>IF(AND(ISNUMBER(K108),ISNUMBER(K71),ISNUMBER(K107)),IFERROR(K71*K107/K108,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -44843,6 +45913,10 @@
         <f>IF(AND(ISNUMBER(J108),ISNUMBER(J109)),IFERROR((J108)/(J109),""),"")</f>
         <v/>
       </c>
+      <c r="K125" s="17">
+        <f>IF(AND(ISNUMBER(K108),ISNUMBER(K109)),IFERROR((K108)/(K109),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -44886,6 +45960,10 @@
         <f>IF(AND(ISNUMBER(J119),ISNUMBER(J124),ISNUMBER(J125)),IFERROR(J119*J124*J125,""),"")</f>
         <v/>
       </c>
+      <c r="K126" s="16">
+        <f>IF(AND(ISNUMBER(K119),ISNUMBER(K124),ISNUMBER(K125)),IFERROR(K119*K124*K125,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
@@ -44936,6 +46014,10 @@
         <f>IF(AND(ISNUMBER(J22),ISNUMBER(J49)),IFERROR((J22)/(J49),""),"")</f>
         <v/>
       </c>
+      <c r="K129" s="17">
+        <f>IF(AND(ISNUMBER(K22),ISNUMBER(K49)),IFERROR((K22)/(K49),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -44979,6 +46061,10 @@
         <f>IF(AND(ISNUMBER(J22),ISNUMBER(J17),ISNUMBER(J49)),IFERROR((J22-J17)/J49,""),"")</f>
         <v/>
       </c>
+      <c r="K130" s="17">
+        <f>IF(AND(ISNUMBER(K22),ISNUMBER(K17),ISNUMBER(K49)),IFERROR((K22-K17)/K49,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -45022,6 +46108,10 @@
         <f>IF(AND(ISNUMBER(J12),ISNUMBER(J49)),IFERROR((J12)/(J49),""),"")</f>
         <v/>
       </c>
+      <c r="K131" s="17">
+        <f>IF(AND(ISNUMBER(K12),ISNUMBER(K49)),IFERROR((K12)/(K49),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -45065,6 +46155,10 @@
         <f>IF(AND(ISNUMBER(J22),ISNUMBER(J49)),IFERROR((J22-J49)/1000,""),"")</f>
         <v/>
       </c>
+      <c r="K132" s="8">
+        <f>IF(AND(ISNUMBER(K22),ISNUMBER(K49)),IFERROR((K22-K49)/1000,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
@@ -45115,6 +46209,10 @@
         <f>IF(AND(ISNUMBER(J57),ISNUMBER(J68)),IFERROR((J57)/(J68),""),"")</f>
         <v/>
       </c>
+      <c r="K135" s="17">
+        <f>IF(AND(ISNUMBER(K57),ISNUMBER(K68)),IFERROR((K57)/(K68),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -45158,6 +46256,10 @@
         <f>IF(AND(ISNUMBER(J57),ISNUMBER(J36)),IFERROR((J57)/(J36),""),"")</f>
         <v/>
       </c>
+      <c r="K136" s="16">
+        <f>IF(AND(ISNUMBER(K57),ISNUMBER(K36)),IFERROR((K57)/(K36),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -45201,6 +46303,10 @@
         <f>IF(AND(ISNUMBER(J90),ISNUMBER(J81)),IFERROR((J90+ABS(J81))/ABS(J81),""),"")</f>
         <v/>
       </c>
+      <c r="K137" s="17">
+        <f>IF(AND(ISNUMBER(K90),ISNUMBER(K81)),IFERROR((K90+ABS(K81))/ABS(K81),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="14" t="inlineStr">
@@ -45251,6 +46357,10 @@
         <f>IF(AND(ISNUMBER(J110),ISNUMBER(J72),ISNUMBER(J107)),IFERROR(J72*J107/J110,""),"")</f>
         <v/>
       </c>
+      <c r="K140" s="17">
+        <f>IF(AND(ISNUMBER(K110),ISNUMBER(K72),ISNUMBER(K107)),IFERROR(K72*K107/K110,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -45294,6 +46404,10 @@
         <f>IF(AND(ISNUMBER(J110),ISNUMBER(J72),ISNUMBER(J107)),IFERROR(J110/(J72*J107)*365,""),"")</f>
         <v/>
       </c>
+      <c r="K141" s="18">
+        <f>IF(AND(ISNUMBER(K110),ISNUMBER(K72),ISNUMBER(K107)),IFERROR(K110/(K72*K107)*365,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -45337,6 +46451,10 @@
         <f>IF(AND(ISNUMBER(J111),ISNUMBER(J71),ISNUMBER(J107)),IFERROR(J71*J107/J111,""),"")</f>
         <v/>
       </c>
+      <c r="K142" s="17">
+        <f>IF(AND(ISNUMBER(K111),ISNUMBER(K71),ISNUMBER(K107)),IFERROR(K71*K107/K111,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -45380,6 +46498,10 @@
         <f>IF(AND(ISNUMBER(J111),ISNUMBER(J71),ISNUMBER(J107)),IFERROR(J111/(J71*J107)*365,""),"")</f>
         <v/>
       </c>
+      <c r="K143" s="18">
+        <f>IF(AND(ISNUMBER(K111),ISNUMBER(K71),ISNUMBER(K107)),IFERROR(K111/(K71*K107)*365,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -45423,6 +46545,10 @@
         <f>IF(AND(ISNUMBER(J112),ISNUMBER(J72),ISNUMBER(J107)),IFERROR(J72*J107/J112,""),"")</f>
         <v/>
       </c>
+      <c r="K144" s="17">
+        <f>IF(AND(ISNUMBER(K112),ISNUMBER(K72),ISNUMBER(K107)),IFERROR(K72*K107/K112,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -45466,6 +46592,10 @@
         <f>IF(AND(ISNUMBER(J112),ISNUMBER(J72),ISNUMBER(J107)),IFERROR(J112/(J72*J107)*365,""),"")</f>
         <v/>
       </c>
+      <c r="K145" s="18">
+        <f>IF(AND(ISNUMBER(K112),ISNUMBER(K72),ISNUMBER(K107)),IFERROR(K112/(K72*K107)*365,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -45509,6 +46639,10 @@
         <f>IF(AND(ISNUMBER(J141),ISNUMBER(J143),ISNUMBER(J145)),IFERROR(J141+J143-J145,""),"")</f>
         <v/>
       </c>
+      <c r="K146" s="18">
+        <f>IF(AND(ISNUMBER(K141),ISNUMBER(K143),ISNUMBER(K145)),IFERROR(K141+K143-K145,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
@@ -45524,39 +46658,43 @@
         </is>
       </c>
       <c r="B149" s="16">
-        <f>IF(ISNUMBER(B71),IFERROR(IF(INDEX($B71:$J71,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$J$4,0))&gt;0,B71/INDEX($B71:$J71,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$J$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(B71),IFERROR(IF(INDEX($B71:$K71,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$K$4,0))&gt;0,B71/INDEX($B71:$K71,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$K$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="C149" s="16">
-        <f>IF(ISNUMBER(C71),IFERROR(IF(INDEX($B71:$J71,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$J$4,0))&gt;0,C71/INDEX($B71:$J71,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$J$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(C71),IFERROR(IF(INDEX($B71:$K71,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$K$4,0))&gt;0,C71/INDEX($B71:$K71,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$K$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="D149" s="16">
-        <f>IF(ISNUMBER(D71),IFERROR(IF(INDEX($B71:$J71,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$J$4,0))&gt;0,D71/INDEX($B71:$J71,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$J$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(D71),IFERROR(IF(INDEX($B71:$K71,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$K$4,0))&gt;0,D71/INDEX($B71:$K71,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$K$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="E149" s="16">
-        <f>IF(ISNUMBER(E71),IFERROR(IF(INDEX($B71:$J71,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$J$4,0))&gt;0,E71/INDEX($B71:$J71,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$J$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(E71),IFERROR(IF(INDEX($B71:$K71,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$K$4,0))&gt;0,E71/INDEX($B71:$K71,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$K$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="F149" s="16">
-        <f>IF(ISNUMBER(F71),IFERROR(IF(INDEX($B71:$J71,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$J$4,0))&gt;0,F71/INDEX($B71:$J71,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$J$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(F71),IFERROR(IF(INDEX($B71:$K71,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$K$4,0))&gt;0,F71/INDEX($B71:$K71,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$K$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="G149" s="16">
-        <f>IF(ISNUMBER(G71),IFERROR(IF(INDEX($B71:$J71,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$J$4,0))&gt;0,G71/INDEX($B71:$J71,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$J$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(G71),IFERROR(IF(INDEX($B71:$K71,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$K$4,0))&gt;0,G71/INDEX($B71:$K71,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$K$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="H149" s="16">
-        <f>IF(ISNUMBER(H71),IFERROR(IF(INDEX($B71:$J71,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$J$4,0))&gt;0,H71/INDEX($B71:$J71,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$J$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(H71),IFERROR(IF(INDEX($B71:$K71,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$K$4,0))&gt;0,H71/INDEX($B71:$K71,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$K$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="I149" s="16">
-        <f>IF(ISNUMBER(I71),IFERROR(IF(INDEX($B71:$J71,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$J$4,0))&gt;0,I71/INDEX($B71:$J71,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$J$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(I71),IFERROR(IF(INDEX($B71:$K71,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$K$4,0))&gt;0,I71/INDEX($B71:$K71,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$K$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="J149" s="16">
-        <f>IF(ISNUMBER(J71),IFERROR(IF(INDEX($B71:$J71,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$J$4,0))&gt;0,J71/INDEX($B71:$J71,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$J$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(J71),IFERROR(IF(INDEX($B71:$K71,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$K$4,0))&gt;0,J71/INDEX($B71:$K71,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$K$4,0))-1,""),""),"")</f>
+        <v/>
+      </c>
+      <c r="K149" s="16">
+        <f>IF(ISNUMBER(K71),IFERROR(IF(INDEX($B71:$K71,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$K$4,0))&gt;0,K71/INDEX($B71:$K71,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$K$4,0))-1,""),""),"")</f>
         <v/>
       </c>
     </row>
@@ -45567,39 +46705,43 @@
         </is>
       </c>
       <c r="B150" s="16">
-        <f>IF(ISNUMBER(B73),IFERROR(IF(INDEX($B73:$J73,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$J$4,0))&gt;0,B73/INDEX($B73:$J73,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$J$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(B73),IFERROR(IF(INDEX($B73:$K73,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$K$4,0))&gt;0,B73/INDEX($B73:$K73,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$K$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="C150" s="16">
-        <f>IF(ISNUMBER(C73),IFERROR(IF(INDEX($B73:$J73,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$J$4,0))&gt;0,C73/INDEX($B73:$J73,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$J$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(C73),IFERROR(IF(INDEX($B73:$K73,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$K$4,0))&gt;0,C73/INDEX($B73:$K73,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$K$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="D150" s="16">
-        <f>IF(ISNUMBER(D73),IFERROR(IF(INDEX($B73:$J73,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$J$4,0))&gt;0,D73/INDEX($B73:$J73,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$J$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(D73),IFERROR(IF(INDEX($B73:$K73,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$K$4,0))&gt;0,D73/INDEX($B73:$K73,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$K$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="E150" s="16">
-        <f>IF(ISNUMBER(E73),IFERROR(IF(INDEX($B73:$J73,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$J$4,0))&gt;0,E73/INDEX($B73:$J73,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$J$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(E73),IFERROR(IF(INDEX($B73:$K73,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$K$4,0))&gt;0,E73/INDEX($B73:$K73,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$K$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="F150" s="16">
-        <f>IF(ISNUMBER(F73),IFERROR(IF(INDEX($B73:$J73,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$J$4,0))&gt;0,F73/INDEX($B73:$J73,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$J$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(F73),IFERROR(IF(INDEX($B73:$K73,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$K$4,0))&gt;0,F73/INDEX($B73:$K73,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$K$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="G150" s="16">
-        <f>IF(ISNUMBER(G73),IFERROR(IF(INDEX($B73:$J73,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$J$4,0))&gt;0,G73/INDEX($B73:$J73,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$J$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(G73),IFERROR(IF(INDEX($B73:$K73,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$K$4,0))&gt;0,G73/INDEX($B73:$K73,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$K$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="H150" s="16">
-        <f>IF(ISNUMBER(H73),IFERROR(IF(INDEX($B73:$J73,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$J$4,0))&gt;0,H73/INDEX($B73:$J73,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$J$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(H73),IFERROR(IF(INDEX($B73:$K73,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$K$4,0))&gt;0,H73/INDEX($B73:$K73,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$K$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="I150" s="16">
-        <f>IF(ISNUMBER(I73),IFERROR(IF(INDEX($B73:$J73,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$J$4,0))&gt;0,I73/INDEX($B73:$J73,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$J$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(I73),IFERROR(IF(INDEX($B73:$K73,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$K$4,0))&gt;0,I73/INDEX($B73:$K73,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$K$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="J150" s="16">
-        <f>IF(ISNUMBER(J73),IFERROR(IF(INDEX($B73:$J73,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$J$4,0))&gt;0,J73/INDEX($B73:$J73,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$J$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(J73),IFERROR(IF(INDEX($B73:$K73,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$K$4,0))&gt;0,J73/INDEX($B73:$K73,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$K$4,0))-1,""),""),"")</f>
+        <v/>
+      </c>
+      <c r="K150" s="16">
+        <f>IF(ISNUMBER(K73),IFERROR(IF(INDEX($B73:$K73,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$K$4,0))&gt;0,K73/INDEX($B73:$K73,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$K$4,0))-1,""),""),"")</f>
         <v/>
       </c>
     </row>
@@ -45610,39 +46752,43 @@
         </is>
       </c>
       <c r="B151" s="16">
-        <f>IF(ISNUMBER(B94),IFERROR(IF(INDEX($B94:$J94,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$J$4,0))&gt;0,B94/INDEX($B94:$J94,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$J$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(B94),IFERROR(IF(INDEX($B94:$K94,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$K$4,0))&gt;0,B94/INDEX($B94:$K94,MATCH(DATE(YEAR(B$4)-1,MONTH(B$4),DAY(B$4)),$B$4:$K$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="C151" s="16">
-        <f>IF(ISNUMBER(C94),IFERROR(IF(INDEX($B94:$J94,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$J$4,0))&gt;0,C94/INDEX($B94:$J94,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$J$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(C94),IFERROR(IF(INDEX($B94:$K94,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$K$4,0))&gt;0,C94/INDEX($B94:$K94,MATCH(DATE(YEAR(C$4)-1,MONTH(C$4),DAY(C$4)),$B$4:$K$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="D151" s="16">
-        <f>IF(ISNUMBER(D94),IFERROR(IF(INDEX($B94:$J94,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$J$4,0))&gt;0,D94/INDEX($B94:$J94,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$J$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(D94),IFERROR(IF(INDEX($B94:$K94,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$K$4,0))&gt;0,D94/INDEX($B94:$K94,MATCH(DATE(YEAR(D$4)-1,MONTH(D$4),DAY(D$4)),$B$4:$K$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="E151" s="16">
-        <f>IF(ISNUMBER(E94),IFERROR(IF(INDEX($B94:$J94,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$J$4,0))&gt;0,E94/INDEX($B94:$J94,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$J$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(E94),IFERROR(IF(INDEX($B94:$K94,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$K$4,0))&gt;0,E94/INDEX($B94:$K94,MATCH(DATE(YEAR(E$4)-1,MONTH(E$4),DAY(E$4)),$B$4:$K$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="F151" s="16">
-        <f>IF(ISNUMBER(F94),IFERROR(IF(INDEX($B94:$J94,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$J$4,0))&gt;0,F94/INDEX($B94:$J94,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$J$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(F94),IFERROR(IF(INDEX($B94:$K94,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$K$4,0))&gt;0,F94/INDEX($B94:$K94,MATCH(DATE(YEAR(F$4)-1,MONTH(F$4),DAY(F$4)),$B$4:$K$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="G151" s="16">
-        <f>IF(ISNUMBER(G94),IFERROR(IF(INDEX($B94:$J94,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$J$4,0))&gt;0,G94/INDEX($B94:$J94,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$J$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(G94),IFERROR(IF(INDEX($B94:$K94,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$K$4,0))&gt;0,G94/INDEX($B94:$K94,MATCH(DATE(YEAR(G$4)-1,MONTH(G$4),DAY(G$4)),$B$4:$K$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="H151" s="16">
-        <f>IF(ISNUMBER(H94),IFERROR(IF(INDEX($B94:$J94,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$J$4,0))&gt;0,H94/INDEX($B94:$J94,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$J$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(H94),IFERROR(IF(INDEX($B94:$K94,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$K$4,0))&gt;0,H94/INDEX($B94:$K94,MATCH(DATE(YEAR(H$4)-1,MONTH(H$4),DAY(H$4)),$B$4:$K$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="I151" s="16">
-        <f>IF(ISNUMBER(I94),IFERROR(IF(INDEX($B94:$J94,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$J$4,0))&gt;0,I94/INDEX($B94:$J94,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$J$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(I94),IFERROR(IF(INDEX($B94:$K94,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$K$4,0))&gt;0,I94/INDEX($B94:$K94,MATCH(DATE(YEAR(I$4)-1,MONTH(I$4),DAY(I$4)),$B$4:$K$4,0))-1,""),""),"")</f>
         <v/>
       </c>
       <c r="J151" s="16">
-        <f>IF(ISNUMBER(J94),IFERROR(IF(INDEX($B94:$J94,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$J$4,0))&gt;0,J94/INDEX($B94:$J94,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$J$4,0))-1,""),""),"")</f>
+        <f>IF(ISNUMBER(J94),IFERROR(IF(INDEX($B94:$K94,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$K$4,0))&gt;0,J94/INDEX($B94:$K94,MATCH(DATE(YEAR(J$4)-1,MONTH(J$4),DAY(J$4)),$B$4:$K$4,0))-1,""),""),"")</f>
+        <v/>
+      </c>
+      <c r="K151" s="16">
+        <f>IF(ISNUMBER(K94),IFERROR(IF(INDEX($B94:$K94,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$K$4,0))&gt;0,K94/INDEX($B94:$K94,MATCH(DATE(YEAR(K$4)-1,MONTH(K$4),DAY(K$4)),$B$4:$K$4,0))-1,""),""),"")</f>
         <v/>
       </c>
     </row>
